--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Inventory" sheetId="1" r:id="R342212fb4bde4547"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to edit" sheetId="2" r:id="Rf7ca8d7044904c02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locker Photos" sheetId="3" r:id="R037f6a989140461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34P Location Photos" sheetId="4" r:id="R6ff4255acd474e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAFS 24 Location Photos" sheetId="5" r:id="R48e124c1ccb04c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appliance_Config" sheetId="6" r:id="Rcce00d8e55794ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Inventory" sheetId="1" r:id="R638ddb224dd04e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to edit" sheetId="2" r:id="R718b6435d0ff4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locker Photos" sheetId="3" r:id="R68118d0d35614757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34P Location Photos" sheetId="4" r:id="R8a0c98de81fd4af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAFS 24 Location Photos" sheetId="5" r:id="R3658c1e88e79486d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Appliance_Config" sheetId="6" r:id="R7e3bfd87682441d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2848,93 +2848,6 @@
   <x:si>
     <x:t xml:space="preserve">locker_7.jpg</x:t>
   </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Location</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_cabin.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Main photo shown at top of this location page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p1.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p2.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p3.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_d1.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_d3.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p4.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p5.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_p_reel.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_pump_panel.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_d_reel.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_d4.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_d5.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">34p_crew_deck.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PhotoFile</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Source sheet/photo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">IMG_20260519_140942500_HDR.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cabin inventory page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Drivers Side 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">IMG_20260519_140924212_HDR.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Driver side first page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Drivers Side 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">IMG_20260519_140929826_HDR.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Driver side second page</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Officers Side</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">IMG_20260519_140936817_HDR.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Officer side page</x:t>
-  </x:si>
 </x:sst>
 </file>
 
@@ -2949,13 +2862,13 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
     <x:font>
@@ -2964,7 +2877,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2973,17 +2886,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F4E78"/>
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="B22222"/>
+        <x:fgColor rgb="FFB22222"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="0F766E"/>
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -2993,7 +2906,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="0F172A"/>
+        <x:fgColor rgb="FF0F172A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B2A44"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -3001,21 +2919,21 @@
     <x:border/>
     <x:border>
       <x:bottom style="thin">
-        <x:color rgb="DDDDDD"/>
+        <x:color rgb="FFDDDDDD"/>
       </x:bottom>
     </x:border>
     <x:border/>
     <x:border/>
     <x:border>
       <x:bottom style="thin">
-        <x:color rgb="DDDDDD"/>
+        <x:color rgb="FFDDDDDD"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -3097,6 +3015,33 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -15639,264 +15584,602 @@
   <x:sheetFormatPr defaultRowHeight="14.399999618530273"/>
   <x:cols>
     <x:col min="1" max="3" width="18" customWidth="1"/>
-    <x:col min="4" max="4" width="30" customWidth="1"/>
-    <x:col min="5" max="5" width="22" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B1" s="7" t="s">
-        <x:v>887</x:v>
-      </x:c>
-      <x:c r="C1" s="7" t="s">
-        <x:v>854</x:v>
-      </x:c>
-      <x:c r="D1" s="7" t="s">
-        <x:v>877</x:v>
-      </x:c>
-      <x:c r="E1" s="7" t="s">
-        <x:v>7</x:v>
+      <x:c r="A1" s="44" t="str">
+        <x:v>Appliance</x:v>
+      </x:c>
+      <x:c r="B1" s="44" t="str">
+        <x:v>Location</x:v>
+      </x:c>
+      <x:c r="C1" s="44" t="str">
+        <x:v>Photo_File</x:v>
+      </x:c>
+      <x:c r="D1" s="44" t="str">
+        <x:v>Display_Title</x:v>
+      </x:c>
+      <x:c r="E1" s="44" t="str">
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28.799999237060547">
-      <x:c r="A2" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>888</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A2" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Cabin</x:v>
+      </x:c>
+      <x:c r="C2" s="31" t="str">
+        <x:v>34p_cabin_front.jpg</x:v>
+      </x:c>
+      <x:c r="D2" s="31" t="str">
+        <x:v>Cabin</x:v>
+      </x:c>
+      <x:c r="E2" s="31" t="str">
+        <x:v>Cabin front/rear photos shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28.799999237060547">
-      <x:c r="A3" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>890</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A3" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Cabin Rear</x:v>
+      </x:c>
+      <x:c r="C3" s="31" t="str">
+        <x:v>34p_cabin_rear.jpg</x:v>
+      </x:c>
+      <x:c r="D3" s="31" t="str">
+        <x:v>Cabin Rear</x:v>
+      </x:c>
+      <x:c r="E3" s="31" t="str">
+        <x:v>Secondary cabin rear photo used on the Cabin page</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28.799999237060547">
-      <x:c r="A4" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>891</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A4" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C4" s="31" t="str">
+        <x:v>34p_p1.jpg</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E4" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28.799999237060547">
-      <x:c r="A5" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>892</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A5" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>34p_p2.jpg</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28.799999237060547">
-      <x:c r="A6" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>893</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A6" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>34p_p3.jpg</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28.799999237060547">
-      <x:c r="A7" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>894</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="E7" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A7" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>34p_p4.jpg</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>P4</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28.799999237060547">
-      <x:c r="A8" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>895</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A8" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>P5</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>34p_p5.jpg</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>P5</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28.799999237060547">
-      <x:c r="A9" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>896</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A9" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>P Reel</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>34p_p_reel.jpg</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>P Reel</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28.799999237060547">
-      <x:c r="A10" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="s">
-        <x:v>897</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A10" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>34p_d1.jpg</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="E10" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28.799999237060547">
-      <x:c r="A11" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>898</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A11" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>34p_d2.jpg</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="E11" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28.799999237060547">
-      <x:c r="A12" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>899</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="E12" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A12" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>D3</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>34p_d3.jpg</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>D3</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28.799999237060547">
-      <x:c r="A13" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="s">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="E13" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A13" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B13" s="31" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="str">
+        <x:v>34p_d4.jpg</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="str">
+        <x:v>D4</x:v>
+      </x:c>
+      <x:c r="E13" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28.799999237060547">
-      <x:c r="A14" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="s">
-        <x:v>901</x:v>
-      </x:c>
-      <x:c r="D14" s="6" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="E14" s="6" t="s">
-        <x:v>889</x:v>
+      <x:c r="A14" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B14" s="31" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="C14" s="31" t="str">
+        <x:v>34p_d5.jpg</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="E14" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28.799999237060547">
-      <x:c r="A15" s="6" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>902</x:v>
-      </x:c>
-      <x:c r="D15" s="6" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E15" s="6" t="s">
-        <x:v>889</x:v>
-      </x:c>
+      <x:c r="A15" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B15" s="31" t="str">
+        <x:v>D Reel</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="str">
+        <x:v>34p_d_reel.jpg</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="str">
+        <x:v>D Reel</x:v>
+      </x:c>
+      <x:c r="E15" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B16" s="31" t="str">
+        <x:v>Pump Panel</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="str">
+        <x:v>34p_pump_panel.jpg</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="str">
+        <x:v>Pump Panel</x:v>
+      </x:c>
+      <x:c r="E16" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31" t="str">
+        <x:v>34P</x:v>
+      </x:c>
+      <x:c r="B17" s="31" t="str">
+        <x:v>Crew Deck</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="str">
+        <x:v>34p_crew_deck.jpg</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="str">
+        <x:v>Crew Deck</x:v>
+      </x:c>
+      <x:c r="E17" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31"/>
+      <x:c r="B20" s="31"/>
+      <x:c r="C20" s="31"/>
+      <x:c r="D20" s="31"/>
+      <x:c r="E20" s="31"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31"/>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31"/>
+      <x:c r="B23" s="31"/>
+      <x:c r="C23" s="31"/>
+      <x:c r="D23" s="31"/>
+      <x:c r="E23" s="31"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31"/>
+      <x:c r="B24" s="31"/>
+      <x:c r="C24" s="31"/>
+      <x:c r="D24" s="31"/>
+      <x:c r="E24" s="31"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
+      <x:c r="E25" s="31"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31"/>
+      <x:c r="B26" s="31"/>
+      <x:c r="C26" s="31"/>
+      <x:c r="D26" s="31"/>
+      <x:c r="E26" s="31"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="31"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
+      <x:c r="E29" s="31"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31"/>
+      <x:c r="B30" s="31"/>
+      <x:c r="C30" s="31"/>
+      <x:c r="D30" s="31"/>
+      <x:c r="E30" s="31"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31"/>
+      <x:c r="B32" s="31"/>
+      <x:c r="C32" s="31"/>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31"/>
+      <x:c r="B33" s="31"/>
+      <x:c r="C33" s="31"/>
+      <x:c r="D33" s="31"/>
+      <x:c r="E33" s="31"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31"/>
+      <x:c r="B34" s="31"/>
+      <x:c r="C34" s="31"/>
+      <x:c r="D34" s="31"/>
+      <x:c r="E34" s="31"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="31"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="31"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31"/>
+      <x:c r="B38" s="31"/>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31"/>
+      <x:c r="B39" s="31"/>
+      <x:c r="C39" s="31"/>
+      <x:c r="D39" s="31"/>
+      <x:c r="E39" s="31"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31"/>
+      <x:c r="B40" s="31"/>
+      <x:c r="C40" s="31"/>
+      <x:c r="D40" s="31"/>
+      <x:c r="E40" s="31"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31"/>
+      <x:c r="B41" s="31"/>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31"/>
+      <x:c r="B42" s="31"/>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31"/>
+      <x:c r="B43" s="31"/>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31"/>
+      <x:c r="B44" s="31"/>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31"/>
+      <x:c r="B45" s="31"/>
+      <x:c r="C45" s="31"/>
+      <x:c r="D45" s="31"/>
+      <x:c r="E45" s="31"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31"/>
+      <x:c r="B46" s="31"/>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31"/>
+      <x:c r="E46" s="31"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="31"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31"/>
+      <x:c r="B48" s="31"/>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31"/>
+      <x:c r="E48" s="31"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31"/>
+      <x:c r="B49" s="31"/>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31"/>
+      <x:c r="E49" s="31"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31"/>
+      <x:c r="B50" s="31"/>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31"/>
+      <x:c r="E50" s="31"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="31"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="31"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31"/>
+      <x:c r="B53" s="31"/>
+      <x:c r="C53" s="31"/>
+      <x:c r="D53" s="31"/>
+      <x:c r="E53" s="31"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31"/>
+      <x:c r="B54" s="31"/>
+      <x:c r="C54" s="31"/>
+      <x:c r="D54" s="31"/>
+      <x:c r="E54" s="31"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31"/>
+      <x:c r="B55" s="31"/>
+      <x:c r="C55" s="31"/>
+      <x:c r="D55" s="31"/>
+      <x:c r="E55" s="31"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31"/>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="31"/>
+      <x:c r="B57" s="31"/>
+      <x:c r="C57" s="31"/>
+      <x:c r="D57" s="31"/>
+      <x:c r="E57" s="31"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="31"/>
+      <x:c r="B58" s="31"/>
+      <x:c r="C58" s="31"/>
+      <x:c r="D58" s="31"/>
+      <x:c r="E58" s="31"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="31"/>
+      <x:c r="B59" s="31"/>
+      <x:c r="C59" s="31"/>
+      <x:c r="D59" s="31"/>
+      <x:c r="E59" s="31"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="31"/>
+      <x:c r="B60" s="31"/>
+      <x:c r="C60" s="31"/>
+      <x:c r="D60" s="31"/>
+      <x:c r="E60" s="31"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15908,94 +16191,552 @@
   <x:sheetFormatPr defaultRowHeight="14.399999618530273"/>
   <x:cols>
     <x:col min="1" max="3" width="18" customWidth="1"/>
-    <x:col min="4" max="4" width="30" customWidth="1"/>
-    <x:col min="5" max="5" width="22" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B1" s="7" t="s">
-        <x:v>887</x:v>
-      </x:c>
-      <x:c r="C1" s="7" t="s">
-        <x:v>903</x:v>
-      </x:c>
-      <x:c r="D1" s="7" t="s">
-        <x:v>904</x:v>
-      </x:c>
-      <x:c r="E1" s="7" t="s">
-        <x:v>869</x:v>
+      <x:c r="A1" s="44" t="str">
+        <x:v>Appliance</x:v>
+      </x:c>
+      <x:c r="B1" s="44" t="str">
+        <x:v>Location</x:v>
+      </x:c>
+      <x:c r="C1" s="44" t="str">
+        <x:v>Photo_File</x:v>
+      </x:c>
+      <x:c r="D1" s="44" t="str">
+        <x:v>Display_Title</x:v>
+      </x:c>
+      <x:c r="E1" s="44" t="str">
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28.799999237060547">
-      <x:c r="A2" s="6" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>905</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>906</x:v>
+      <x:c r="A2" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B2" s="31" t="str">
+        <x:v>Cabin</x:v>
+      </x:c>
+      <x:c r="C2" s="31" t="str">
+        <x:v>cafs24_cabin_front.jpg</x:v>
+      </x:c>
+      <x:c r="D2" s="31" t="str">
+        <x:v>Cabin</x:v>
+      </x:c>
+      <x:c r="E2" s="31" t="str">
+        <x:v>Cabin front/rear photos shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28.799999237060547">
-      <x:c r="A3" s="6" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="s">
-        <x:v>907</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>908</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>907</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>909</x:v>
+      <x:c r="A3" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B3" s="31" t="str">
+        <x:v>Cabin Rear</x:v>
+      </x:c>
+      <x:c r="C3" s="31" t="str">
+        <x:v>cafs24_cabin_rear.jpg</x:v>
+      </x:c>
+      <x:c r="D3" s="31" t="str">
+        <x:v>Cabin Rear</x:v>
+      </x:c>
+      <x:c r="E3" s="31" t="str">
+        <x:v>Secondary cabin rear photo used on the Cabin page</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28.799999237060547">
-      <x:c r="A4" s="6" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>910</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>911</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="s">
-        <x:v>910</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="s">
-        <x:v>912</x:v>
+      <x:c r="A4" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="C4" s="31" t="str">
+        <x:v>cafs24_p1.jpg</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E4" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28.799999237060547">
-      <x:c r="A5" s="6" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>913</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>914</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="s">
-        <x:v>913</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="s">
-        <x:v>915</x:v>
-      </x:c>
+      <x:c r="A5" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>cafs24_p2.jpg</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Pump Panel</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>cafs24_pump_panel.jpg</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>Pump Panel</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>P-Tube</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>cafs24_p_tube.jpg</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>P-Tube</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>cafs24_p3.jpg</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>D-Tube</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>cafs24_d_tube.jpg</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>D-Tube</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B10" s="31" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>cafs24_d1.jpg</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="E10" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B11" s="31" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>cafs24_d2.jpg</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="E11" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31" t="str">
+        <x:v>CAFS 24</x:v>
+      </x:c>
+      <x:c r="B12" s="31" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>cafs24_rear.jpg</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>Rear</x:v>
+      </x:c>
+      <x:c r="E12" s="31" t="str">
+        <x:v>Main photo shown at top of this location page</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31"/>
+      <x:c r="B13" s="31"/>
+      <x:c r="C13" s="31"/>
+      <x:c r="D13" s="31"/>
+      <x:c r="E13" s="31"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="31"/>
+      <x:c r="B14" s="31"/>
+      <x:c r="C14" s="31"/>
+      <x:c r="D14" s="31"/>
+      <x:c r="E14" s="31"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="31"/>
+      <x:c r="B15" s="31"/>
+      <x:c r="C15" s="31"/>
+      <x:c r="D15" s="31"/>
+      <x:c r="E15" s="31"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="31"/>
+      <x:c r="B16" s="31"/>
+      <x:c r="C16" s="31"/>
+      <x:c r="D16" s="31"/>
+      <x:c r="E16" s="31"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31"/>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31"/>
+      <x:c r="B20" s="31"/>
+      <x:c r="C20" s="31"/>
+      <x:c r="D20" s="31"/>
+      <x:c r="E20" s="31"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31"/>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31"/>
+      <x:c r="B23" s="31"/>
+      <x:c r="C23" s="31"/>
+      <x:c r="D23" s="31"/>
+      <x:c r="E23" s="31"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31"/>
+      <x:c r="B24" s="31"/>
+      <x:c r="C24" s="31"/>
+      <x:c r="D24" s="31"/>
+      <x:c r="E24" s="31"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
+      <x:c r="E25" s="31"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31"/>
+      <x:c r="B26" s="31"/>
+      <x:c r="C26" s="31"/>
+      <x:c r="D26" s="31"/>
+      <x:c r="E26" s="31"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="31"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
+      <x:c r="E29" s="31"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31"/>
+      <x:c r="B30" s="31"/>
+      <x:c r="C30" s="31"/>
+      <x:c r="D30" s="31"/>
+      <x:c r="E30" s="31"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31"/>
+      <x:c r="B32" s="31"/>
+      <x:c r="C32" s="31"/>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31"/>
+      <x:c r="B33" s="31"/>
+      <x:c r="C33" s="31"/>
+      <x:c r="D33" s="31"/>
+      <x:c r="E33" s="31"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31"/>
+      <x:c r="B34" s="31"/>
+      <x:c r="C34" s="31"/>
+      <x:c r="D34" s="31"/>
+      <x:c r="E34" s="31"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="31"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="31"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31"/>
+      <x:c r="B38" s="31"/>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31"/>
+      <x:c r="B39" s="31"/>
+      <x:c r="C39" s="31"/>
+      <x:c r="D39" s="31"/>
+      <x:c r="E39" s="31"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31"/>
+      <x:c r="B40" s="31"/>
+      <x:c r="C40" s="31"/>
+      <x:c r="D40" s="31"/>
+      <x:c r="E40" s="31"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31"/>
+      <x:c r="B41" s="31"/>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31"/>
+      <x:c r="B42" s="31"/>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31"/>
+      <x:c r="B43" s="31"/>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31"/>
+      <x:c r="B44" s="31"/>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31"/>
+      <x:c r="B45" s="31"/>
+      <x:c r="C45" s="31"/>
+      <x:c r="D45" s="31"/>
+      <x:c r="E45" s="31"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31"/>
+      <x:c r="B46" s="31"/>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31"/>
+      <x:c r="E46" s="31"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="31"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31"/>
+      <x:c r="B48" s="31"/>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31"/>
+      <x:c r="E48" s="31"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31"/>
+      <x:c r="B49" s="31"/>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31"/>
+      <x:c r="E49" s="31"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31"/>
+      <x:c r="B50" s="31"/>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31"/>
+      <x:c r="E50" s="31"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="31"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="31"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31"/>
+      <x:c r="B53" s="31"/>
+      <x:c r="C53" s="31"/>
+      <x:c r="D53" s="31"/>
+      <x:c r="E53" s="31"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31"/>
+      <x:c r="B54" s="31"/>
+      <x:c r="C54" s="31"/>
+      <x:c r="D54" s="31"/>
+      <x:c r="E54" s="31"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31"/>
+      <x:c r="B55" s="31"/>
+      <x:c r="C55" s="31"/>
+      <x:c r="D55" s="31"/>
+      <x:c r="E55" s="31"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31"/>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="31"/>
+      <x:c r="B57" s="31"/>
+      <x:c r="C57" s="31"/>
+      <x:c r="D57" s="31"/>
+      <x:c r="E57" s="31"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="31"/>
+      <x:c r="B58" s="31"/>
+      <x:c r="C58" s="31"/>
+      <x:c r="D58" s="31"/>
+      <x:c r="E58" s="31"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="31"/>
+      <x:c r="B59" s="31"/>
+      <x:c r="C59" s="31"/>
+      <x:c r="D59" s="31"/>
+      <x:c r="E59" s="31"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="31"/>
+      <x:c r="B60" s="31"/>
+      <x:c r="C60" s="31"/>
+      <x:c r="D60" s="31"/>
+      <x:c r="E60" s="31"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16718,7 +17459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77e538054d945ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31e86d48669b49f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0E8F33-561E-4B85-AB95-AF3C7D520678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFA0110-98AE-4566-A82D-4DCB2BBA0251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Inventory" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="925">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2970,6 +2970,9 @@
   </si>
   <si>
     <t>Home, Starred, Out of Service are app-generated; do not add here</t>
+  </si>
+  <si>
+    <t>cafs24_p4.jpg</t>
   </si>
 </sst>
 </file>
@@ -3113,7 +3116,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ApplianceConfigTable" displayName="ApplianceConfigTable" ref="A1:F43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ApplianceConfigTable" displayName="ApplianceConfigTable" ref="A1:F44">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Appliance"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Location"/>
@@ -16254,7 +16257,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -16404,13 +16407,13 @@
         <v>614</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>748</v>
+        <v>463</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>748</v>
+        <v>463</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>894</v>
@@ -16421,13 +16424,13 @@
         <v>614</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>507</v>
+        <v>748</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>507</v>
+        <v>748</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>894</v>
@@ -16438,13 +16441,13 @@
         <v>614</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>894</v>
@@ -16455,24 +16458,34 @@
         <v>614</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>830</v>
+        <v>525</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>830</v>
+        <v>525</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>894</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
@@ -16802,6 +16815,13 @@
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16810,7 +16830,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -17350,7 +17370,7 @@
         <v>614</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>748</v>
+        <v>463</v>
       </c>
       <c r="C30" s="2">
         <v>7</v>
@@ -17368,7 +17388,7 @@
         <v>614</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>507</v>
+        <v>748</v>
       </c>
       <c r="C31" s="2">
         <v>8</v>
@@ -17386,7 +17406,7 @@
         <v>614</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="C32" s="2">
         <v>9</v>
@@ -17404,7 +17424,7 @@
         <v>614</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>830</v>
+        <v>525</v>
       </c>
       <c r="C33" s="2">
         <v>10</v>
@@ -17417,15 +17437,23 @@
         <v>923</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C34" s="2">
+        <v>11</v>
+      </c>
       <c r="D34" s="2" t="s">
         <v>922</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -17517,9 +17545,19 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D43" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="D2:D44" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFA0110-98AE-4566-A82D-4DCB2BBA0251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Inventory" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
   <si>
     <t>Item_ID</t>
   </si>
@@ -1486,15 +1486,6 @@
     <t>BA ENTRY CONTROL BOARD</t>
   </si>
   <si>
-    <t>ECO Tabard
-Pen
-Whiteboard marker
-Entry Control sheets A4
-Atmospheric Monitoring log book sheets A4
-Clock
-Light</t>
-  </si>
-  <si>
     <t>34P-0164</t>
   </si>
   <si>
@@ -2288,14 +2279,6 @@
     <t>CAFS24-0172</t>
   </si>
   <si>
-    <t>ECO tabard
-Chinagraph pencil
-Whiteboard
-Light
-Clock
-Entry Control sheets</t>
-  </si>
-  <si>
     <t>CAFS24-0178</t>
   </si>
   <si>
@@ -2973,6 +2956,31 @@
   </si>
   <si>
     <t>cafs24_p4.jpg</t>
+  </si>
+  <si>
+    <t>(Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Keyword: Positive Pressure Ventilation) </t>
+  </si>
+  <si>
+    <t>ECO Tabard
+Pen
+Whiteboard marker
+Entry Control sheets A4
+Atmospheric Monitoring log book sheets A4
+Clock
+Light
+(Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t>ECO tabard
+Chinagraph pencil
+Whiteboard
+Light
+Clock
+Entry Control sheets
+(Keyword: Breathing Apparatus)</t>
   </si>
 </sst>
 </file>
@@ -6545,7 +6553,9 @@
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
+      <c r="I110" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="J110" s="5" t="s">
         <v>14</v>
       </c>
@@ -8460,7 +8470,9 @@
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
+      <c r="I189" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J189" s="6" t="s">
         <v>14</v>
       </c>
@@ -9229,7 +9241,9 @@
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
-      <c r="I226" s="6"/>
+      <c r="I226" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J226" s="6" t="s">
         <v>14</v>
       </c>
@@ -9383,7 +9397,9 @@
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
-      <c r="I233" s="6"/>
+      <c r="I233" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J233" s="6" t="s">
         <v>14</v>
       </c>
@@ -9405,7 +9421,9 @@
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
-      <c r="I234" s="6"/>
+      <c r="I234" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J234" s="6" t="s">
         <v>14</v>
       </c>
@@ -9537,7 +9555,9 @@
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
-      <c r="I240" s="6"/>
+      <c r="I240" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J240" s="6" t="s">
         <v>14</v>
       </c>
@@ -9559,12 +9579,14 @@
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
-      <c r="I241" s="6"/>
+      <c r="I241" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J241" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>459</v>
       </c>
@@ -9582,7 +9604,7 @@
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6" t="s">
-        <v>461</v>
+        <v>925</v>
       </c>
       <c r="J242" s="6" t="s">
         <v>14</v>
@@ -9662,18 +9684,18 @@
     </row>
     <row r="249" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
@@ -9684,18 +9706,18 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
@@ -9706,22 +9728,22 @@
     </row>
     <row r="251" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
       <c r="I251" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J251" s="6" t="s">
         <v>14</v>
@@ -9765,18 +9787,18 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
@@ -9787,18 +9809,18 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
@@ -9809,18 +9831,18 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9831,18 +9853,18 @@
     </row>
     <row r="258" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9853,18 +9875,18 @@
     </row>
     <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9875,18 +9897,18 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9897,18 +9919,18 @@
     </row>
     <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9919,18 +9941,18 @@
     </row>
     <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9941,18 +9963,18 @@
     </row>
     <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -9963,18 +9985,18 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -9985,18 +10007,18 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
@@ -10007,18 +10029,18 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10029,18 +10051,18 @@
     </row>
     <row r="267" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10051,18 +10073,18 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10073,18 +10095,18 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10095,18 +10117,18 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10117,18 +10139,18 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10139,18 +10161,18 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10161,18 +10183,18 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10183,18 +10205,18 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10205,13 +10227,13 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
@@ -10227,18 +10249,18 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10249,18 +10271,18 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10271,18 +10293,18 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10293,18 +10315,18 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10315,18 +10337,18 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10337,22 +10359,22 @@
     </row>
     <row r="281" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
       <c r="I281" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J281" s="6" t="s">
         <v>14</v>
@@ -10372,18 +10394,18 @@
     </row>
     <row r="283" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A283" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
       <c r="F283" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
@@ -10394,18 +10416,18 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
       <c r="F284" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
@@ -10416,18 +10438,18 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10438,18 +10460,18 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10460,18 +10482,18 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10482,18 +10504,18 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10504,18 +10526,18 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10526,18 +10548,18 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10548,18 +10570,18 @@
     </row>
     <row r="291" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10570,18 +10592,18 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10592,18 +10614,18 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
@@ -10614,18 +10636,18 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
@@ -10636,22 +10658,22 @@
     </row>
     <row r="295" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
       <c r="I295" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J295" s="6" t="s">
         <v>14</v>
@@ -10719,23 +10741,23 @@
     </row>
     <row r="301" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A301" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D301" s="6"/>
       <c r="E301" s="6"/>
       <c r="F301" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
       <c r="I301" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J301" s="6" t="s">
         <v>14</v>
@@ -11067,18 +11089,18 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B329" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
       <c r="F329" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
@@ -11089,13 +11111,13 @@
     </row>
     <row r="330" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B330" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
@@ -11111,18 +11133,18 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11133,18 +11155,18 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11155,18 +11177,18 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11177,18 +11199,18 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11199,18 +11221,18 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11221,18 +11243,18 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11243,18 +11265,18 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11265,18 +11287,18 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11287,18 +11309,18 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11309,18 +11331,18 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11331,13 +11353,13 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
@@ -11353,18 +11375,18 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11375,18 +11397,18 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11397,18 +11419,18 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11419,18 +11441,18 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11441,18 +11463,18 @@
     </row>
     <row r="346" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11463,18 +11485,18 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11485,18 +11507,18 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11507,18 +11529,18 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11529,18 +11551,18 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11551,18 +11573,18 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11573,18 +11595,18 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11595,18 +11617,18 @@
     </row>
     <row r="353" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11617,18 +11639,18 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11651,10 +11673,10 @@
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B356" s="6" t="s">
         <v>613</v>
-      </c>
-      <c r="B356" s="6" t="s">
-        <v>614</v>
       </c>
       <c r="C356" s="6" t="s">
         <v>11</v>
@@ -11675,10 +11697,10 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C357" s="6" t="s">
         <v>11</v>
@@ -11699,10 +11721,10 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C358" s="6" t="s">
         <v>11</v>
@@ -11712,7 +11734,7 @@
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11723,10 +11745,10 @@
     </row>
     <row r="359" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C359" s="6" t="s">
         <v>11</v>
@@ -11736,12 +11758,12 @@
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
       <c r="I359" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J359" s="6" t="s">
         <v>14</v>
@@ -11809,10 +11831,10 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C365" s="6" t="s">
         <v>11</v>
@@ -11822,7 +11844,7 @@
       </c>
       <c r="E365" s="6"/>
       <c r="F365" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
@@ -11833,10 +11855,10 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C366" s="6" t="s">
         <v>11</v>
@@ -11846,7 +11868,7 @@
       </c>
       <c r="E366" s="6"/>
       <c r="F366" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -11857,10 +11879,10 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C367" s="6" t="s">
         <v>11</v>
@@ -11881,10 +11903,10 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C368" s="6" t="s">
         <v>11</v>
@@ -11894,7 +11916,7 @@
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11905,10 +11927,10 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C369" s="6" t="s">
         <v>11</v>
@@ -11918,7 +11940,7 @@
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11929,10 +11951,10 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C370" s="6" t="s">
         <v>11</v>
@@ -11942,7 +11964,7 @@
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11953,10 +11975,10 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C371" s="6" t="s">
         <v>11</v>
@@ -11966,7 +11988,7 @@
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -11977,10 +11999,10 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C372" s="6" t="s">
         <v>11</v>
@@ -12001,10 +12023,10 @@
     </row>
     <row r="373" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>11</v>
@@ -12014,7 +12036,7 @@
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12025,10 +12047,10 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C374" s="6" t="s">
         <v>11</v>
@@ -12049,10 +12071,10 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C375" s="6" t="s">
         <v>11</v>
@@ -12062,7 +12084,7 @@
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12073,10 +12095,10 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C376" s="6" t="s">
         <v>11</v>
@@ -12086,7 +12108,7 @@
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12097,10 +12119,10 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C377" s="6" t="s">
         <v>11</v>
@@ -12110,7 +12132,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12121,10 +12143,10 @@
     </row>
     <row r="379" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C379" s="6" t="s">
         <v>11</v>
@@ -12134,7 +12156,7 @@
       </c>
       <c r="E379" s="6"/>
       <c r="F379" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G379" s="6"/>
       <c r="H379" s="6"/>
@@ -12145,10 +12167,10 @@
     </row>
     <row r="380" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A380" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C380" s="6" t="s">
         <v>11</v>
@@ -12163,7 +12185,7 @@
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
       <c r="I380" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J380" s="6" t="s">
         <v>14</v>
@@ -12207,10 +12229,10 @@
     </row>
     <row r="384" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A384" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C384" s="6" t="s">
         <v>11</v>
@@ -12225,7 +12247,7 @@
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
       <c r="I384" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J384" s="6" t="s">
         <v>14</v>
@@ -12317,25 +12339,25 @@
     </row>
     <row r="392" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A392" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C392" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D392" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E392" s="6"/>
       <c r="F392" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
       <c r="I392" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J392" s="6" t="s">
         <v>14</v>
@@ -12403,16 +12425,16 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C398" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D398" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E398" s="6"/>
       <c r="F398" s="6" t="s">
@@ -12427,20 +12449,20 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C399" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D399" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E399" s="6"/>
       <c r="F399" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
@@ -12451,20 +12473,20 @@
     </row>
     <row r="400" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C400" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D400" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12475,20 +12497,20 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C401" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12499,44 +12521,46 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C402" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D402" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
-      <c r="I402" s="6"/>
+      <c r="I402" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J402" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C403" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D403" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
@@ -12547,20 +12571,20 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C404" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D404" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
@@ -12571,20 +12595,20 @@
     </row>
     <row r="405" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C405" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12595,20 +12619,20 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C406" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D406" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12619,20 +12643,20 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C407" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12643,16 +12667,16 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C408" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
@@ -12667,16 +12691,16 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C409" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
@@ -12691,20 +12715,20 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C410" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E410" s="6"/>
       <c r="F410" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12715,16 +12739,16 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C411" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E411" s="6"/>
       <c r="F411" s="6" t="s">
@@ -12739,16 +12763,16 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C412" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="6" t="s">
@@ -12763,20 +12787,20 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C413" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D413" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E413" s="6"/>
       <c r="F413" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12787,16 +12811,16 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C414" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E414" s="6"/>
       <c r="F414" s="6" t="s">
@@ -12859,10 +12883,10 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C419" s="10" t="s">
         <v>399</v>
@@ -12881,10 +12905,10 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C420" s="10" t="s">
         <v>399</v>
@@ -12892,7 +12916,7 @@
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
@@ -12903,10 +12927,10 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C421" s="10" t="s">
         <v>399</v>
@@ -12914,7 +12938,7 @@
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12925,10 +12949,10 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C422" s="10" t="s">
         <v>399</v>
@@ -12936,7 +12960,7 @@
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
       <c r="F422" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12947,10 +12971,10 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C423" s="10" t="s">
         <v>399</v>
@@ -12958,7 +12982,7 @@
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -12969,10 +12993,10 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C424" s="10" t="s">
         <v>407</v>
@@ -12980,7 +13004,7 @@
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -12991,18 +13015,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13013,18 +13037,18 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13035,18 +13059,18 @@
     </row>
     <row r="427" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13057,32 +13081,34 @@
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B428" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C428" s="10" t="s">
         <v>700</v>
-      </c>
-      <c r="B428" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="C428" s="10" t="s">
-        <v>701</v>
       </c>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
-      <c r="I428" s="6"/>
+      <c r="I428" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J428" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C429" s="6" t="s">
         <v>437</v>
@@ -13090,21 +13116,23 @@
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
-      <c r="I429" s="6"/>
+      <c r="I429" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J429" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C430" s="6" t="s">
         <v>437</v>
@@ -13121,12 +13149,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C431" s="6" t="s">
         <v>437</v>
@@ -13139,7 +13167,7 @@
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
       <c r="I431" s="10" t="s">
-        <v>707</v>
+        <v>926</v>
       </c>
       <c r="J431" s="6" t="s">
         <v>14</v>
@@ -13207,10 +13235,10 @@
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C437" s="6" t="s">
         <v>437</v>
@@ -13218,7 +13246,7 @@
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
       <c r="F437" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
@@ -13229,10 +13257,10 @@
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C438" s="6" t="s">
         <v>437</v>
@@ -13240,7 +13268,7 @@
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
@@ -13251,10 +13279,10 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C439" s="6" t="s">
         <v>437</v>
@@ -13262,7 +13290,7 @@
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13273,10 +13301,10 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C440" s="6" t="s">
         <v>437</v>
@@ -13284,7 +13312,7 @@
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13295,10 +13323,10 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C441" s="6" t="s">
         <v>437</v>
@@ -13306,7 +13334,7 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13317,18 +13345,18 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13339,18 +13367,18 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13361,18 +13389,18 @@
     </row>
     <row r="444" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
@@ -13383,18 +13411,18 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B445" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
       <c r="F445" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
@@ -13405,18 +13433,18 @@
     </row>
     <row r="446" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B446" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
       <c r="F446" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
@@ -13427,18 +13455,18 @@
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
       <c r="F447" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
@@ -13449,18 +13477,18 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B448" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
       <c r="F448" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
@@ -13471,18 +13499,18 @@
     </row>
     <row r="449" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13493,18 +13521,18 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B450" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13515,18 +13543,18 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13537,23 +13565,23 @@
     </row>
     <row r="452" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
       <c r="F452" s="10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
       <c r="I452" s="10" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="J452" s="6" t="s">
         <v>14</v>
@@ -13585,18 +13613,18 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D455" s="6"/>
       <c r="E455" s="6"/>
       <c r="F455" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G455" s="6"/>
       <c r="H455" s="6"/>
@@ -13607,18 +13635,18 @@
     </row>
     <row r="456" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A456" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
       <c r="F456" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
@@ -13629,18 +13657,18 @@
     </row>
     <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13651,18 +13679,18 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C458" s="10" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13673,40 +13701,42 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C459" s="10" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
-      <c r="I459" s="6"/>
+      <c r="I459" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J459" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
@@ -13717,18 +13747,18 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -13739,13 +13769,13 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C462" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
@@ -13761,13 +13791,13 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B463" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C463" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
@@ -13783,18 +13813,18 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B464" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C464" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
       <c r="F464" s="10" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
@@ -13805,13 +13835,13 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B465" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C465" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
@@ -13827,18 +13857,18 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B466" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C466" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
       <c r="F466" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13849,18 +13879,18 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B467" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C467" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13871,18 +13901,18 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C468" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13893,18 +13923,18 @@
     </row>
     <row r="469" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B469" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C469" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13915,18 +13945,18 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B470" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13937,18 +13967,18 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B471" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
@@ -13959,18 +13989,18 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B472" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -13981,18 +14011,18 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B473" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14003,18 +14033,18 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14025,18 +14055,18 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B475" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14047,18 +14077,18 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B476" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
       <c r="F476" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14069,18 +14099,18 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B477" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14091,18 +14121,18 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B478" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14113,18 +14143,18 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B479" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14135,18 +14165,18 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B480" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14157,18 +14187,18 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B481" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14179,18 +14209,18 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B482" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14201,18 +14231,18 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B483" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14223,18 +14253,18 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B484" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14245,18 +14275,18 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B485" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14267,18 +14297,18 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B486" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14289,23 +14319,23 @@
     </row>
     <row r="487" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B487" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
       <c r="F487" s="10" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
       <c r="I487" s="10" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="J487" s="6" t="s">
         <v>14</v>
@@ -14565,18 +14595,18 @@
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B509" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D509" s="6"/>
       <c r="E509" s="6"/>
       <c r="F509" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G509" s="6"/>
       <c r="H509" s="6"/>
@@ -14587,18 +14617,18 @@
     </row>
     <row r="510" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A510" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B510" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
       <c r="F510" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
@@ -14609,18 +14639,18 @@
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B511" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
       <c r="F511" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
@@ -14631,13 +14661,13 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B512" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
@@ -14653,23 +14683,23 @@
     </row>
     <row r="513" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B513" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C513" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
       <c r="F513" s="10" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
       <c r="I513" s="10" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="J513" s="6" t="s">
         <v>14</v>
@@ -14929,18 +14959,18 @@
     </row>
     <row r="535" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A535" s="6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B535" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C535" s="10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D535" s="6"/>
       <c r="E535" s="6"/>
       <c r="F535" s="10" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G535" s="6"/>
       <c r="H535" s="6"/>
@@ -15049,18 +15079,18 @@
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B544" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C544" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D544" s="6"/>
       <c r="E544" s="6"/>
       <c r="F544" s="6" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G544" s="6"/>
       <c r="H544" s="6"/>
@@ -15071,13 +15101,13 @@
     </row>
     <row r="545" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A545" s="6" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B545" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
@@ -15093,18 +15123,18 @@
     </row>
     <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B546" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15115,13 +15145,13 @@
     </row>
     <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B547" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
@@ -15137,18 +15167,18 @@
     </row>
     <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B548" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C548" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="6" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
@@ -15159,18 +15189,18 @@
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B549" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C549" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
       <c r="F549" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
@@ -15181,23 +15211,23 @@
     </row>
     <row r="550" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B550" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C550" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
       <c r="F550" s="10" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
       <c r="I550" s="10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="J550" s="6" t="s">
         <v>14</v>
@@ -15217,18 +15247,18 @@
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B552" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
       <c r="F552" s="6" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
@@ -15239,23 +15269,23 @@
     </row>
     <row r="553" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A553" s="6" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B553" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
       <c r="F553" s="6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
       <c r="I553" s="10" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J553" s="6" t="s">
         <v>14</v>
@@ -15292,13 +15322,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -15306,10 +15336,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -15317,7 +15347,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -15328,7 +15358,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>185</v>
@@ -15339,21 +15369,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -15361,10 +15391,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -15372,10 +15402,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -15383,10 +15413,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -15394,10 +15424,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -15405,7 +15435,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>14</v>
@@ -15413,68 +15443,68 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>860</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -15484,21 +15514,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -15523,10 +15553,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>7</v>
@@ -15537,13 +15567,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -15551,13 +15581,13 @@
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -15565,13 +15595,13 @@
         <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C4" t="s">
         <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -15579,13 +15609,13 @@
         <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C5" t="s">
         <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -15593,13 +15623,13 @@
         <v>185</v>
       </c>
       <c r="B6" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C6" t="s">
         <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -15607,13 +15637,13 @@
         <v>243</v>
       </c>
       <c r="B7" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C7" t="s">
         <v>243</v>
       </c>
       <c r="D7" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -15621,27 +15651,27 @@
         <v>296</v>
       </c>
       <c r="B8" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C8" t="s">
         <v>296</v>
       </c>
       <c r="D8" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B9" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C9" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D9" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
   </sheetData>
@@ -15665,13 +15695,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>7</v>
@@ -15685,13 +15715,13 @@
         <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -15699,16 +15729,16 @@
         <v>321</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -15719,13 +15749,13 @@
         <v>399</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>399</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -15736,13 +15766,13 @@
         <v>407</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>407</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -15753,13 +15783,13 @@
         <v>437</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>437</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -15767,16 +15797,16 @@
         <v>321</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -15784,16 +15814,16 @@
         <v>321</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -15801,16 +15831,16 @@
         <v>321</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -15818,16 +15848,16 @@
         <v>321</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -15835,16 +15865,16 @@
         <v>321</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -15852,16 +15882,16 @@
         <v>321</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -15869,16 +15899,16 @@
         <v>321</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -15886,16 +15916,16 @@
         <v>321</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -15903,16 +15933,16 @@
         <v>321</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -15920,16 +15950,16 @@
         <v>321</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -15937,16 +15967,16 @@
         <v>321</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -16271,13 +16301,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>7</v>
@@ -16285,206 +16315,206 @@
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>399</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>399</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>407</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>407</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>437</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>437</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -16846,19 +16876,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>919</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>920</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16872,11 +16902,11 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16890,11 +16920,11 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16908,11 +16938,11 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16926,11 +16956,11 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16944,11 +16974,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16962,11 +16992,11 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16980,11 +17010,11 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -16998,11 +17028,11 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17016,11 +17046,11 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17034,11 +17064,11 @@
         <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17052,11 +17082,11 @@
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17064,17 +17094,17 @@
         <v>321</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17082,17 +17112,17 @@
         <v>321</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C14" s="2">
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17100,17 +17130,17 @@
         <v>321</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C15" s="2">
         <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17118,17 +17148,17 @@
         <v>321</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C16" s="2">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17136,17 +17166,17 @@
         <v>321</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C17" s="2">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17154,17 +17184,17 @@
         <v>321</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C18" s="2">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17172,17 +17202,17 @@
         <v>321</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2">
         <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17190,17 +17220,17 @@
         <v>321</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C20" s="2">
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17208,17 +17238,17 @@
         <v>321</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C21" s="2">
         <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17226,17 +17256,17 @@
         <v>321</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C22" s="2">
         <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -17244,22 +17274,22 @@
         <v>321</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C23" s="2">
         <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
@@ -17268,16 +17298,16 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>399</v>
@@ -17286,16 +17316,16 @@
         <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>407</v>
@@ -17304,52 +17334,52 @@
         <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C27" s="2">
         <v>4</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C28" s="2">
         <v>5</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>437</v>
@@ -17358,101 +17388,101 @@
         <v>6</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C30" s="2">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C31" s="2">
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C32" s="2">
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C33" s="2">
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C34" s="2">
         <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -17460,7 +17490,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -17470,7 +17500,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -17480,7 +17510,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -17490,7 +17520,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -17500,7 +17530,7 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -17510,7 +17540,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -17520,7 +17550,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -17530,7 +17560,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -17540,7 +17570,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -17550,7 +17580,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE1E814-09F6-45FC-B481-3E6AAE67E1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="928">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,6 +2981,9 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t>Test Edit.</t>
   </si>
 </sst>
 </file>
@@ -3387,7 +3390,9 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>927</v>
+      </c>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE1E814-09F6-45FC-B481-3E6AAE67E1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B60C4E-0B7E-47C6-818A-01B2D83D53D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,9 +2981,6 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
-  </si>
-  <si>
-    <t>Test Edit.</t>
   </si>
 </sst>
 </file>
@@ -3390,9 +3387,7 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
-        <v>927</v>
-      </c>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B60C4E-0B7E-47C6-818A-01B2D83D53D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082B74C-4455-45E0-8FC6-6481AB9DF975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="928">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,6 +2981,9 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test 2 up </t>
   </si>
 </sst>
 </file>
@@ -3387,7 +3390,9 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>927</v>
+      </c>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7082B74C-4455-45E0-8FC6-6481AB9DF975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D4B1DE-F0E4-4FD4-8154-0CA04634561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,9 +2981,6 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test 2 up </t>
   </si>
 </sst>
 </file>
@@ -3390,9 +3387,7 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
-        <v>927</v>
-      </c>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D4B1DE-F0E4-4FD4-8154-0CA04634561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9E75DA-58A5-480B-805F-626301365D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="929">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,6 +2981,12 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t>CAFS24-0177</t>
+  </si>
+  <si>
+    <t>PUMP RADIO HEADSET #2</t>
   </si>
 </sst>
 </file>
@@ -13174,16 +13180,26 @@
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A432" s="6"/>
-      <c r="B432" s="6"/>
-      <c r="C432" s="6"/>
+      <c r="A432" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
-      <c r="F432" s="6"/>
+      <c r="F432" s="6" t="s">
+        <v>928</v>
+      </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
       <c r="I432" s="6"/>
-      <c r="J432" s="6"/>
+      <c r="J432" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
@@ -15293,7 +15309,7 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C379:C414 C554:C946 C2:C377 C458:C470 C433:C436" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H2:H377 H379:H946" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -15302,7 +15318,7 @@
     <dataValidation type="list" allowBlank="1" sqref="J2:J377 J379:J946" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C379:C414 C554:C946 C2:C377 C458:C470 C433:C436" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9E75DA-58A5-480B-805F-626301365D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B157FA-5490-426F-9C77-744F3A5E08B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,12 +2981,6 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
-  </si>
-  <si>
-    <t>CAFS24-0177</t>
-  </si>
-  <si>
-    <t>PUMP RADIO HEADSET #2</t>
   </si>
 </sst>
 </file>
@@ -13180,26 +13174,16 @@
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A432" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="B432" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C432" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A432" s="6"/>
+      <c r="B432" s="6"/>
+      <c r="C432" s="6"/>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
-      <c r="F432" s="6" t="s">
-        <v>928</v>
-      </c>
+      <c r="F432" s="6"/>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
       <c r="I432" s="6"/>
-      <c r="J432" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J432" s="6"/>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B157FA-5490-426F-9C77-744F3A5E08B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15293,7 +15293,7 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C379:C414 C554:C946 C2:C377 C458:C470 C433:C436" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H2:H377 H379:H946" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -15302,7 +15302,7 @@
     <dataValidation type="list" allowBlank="1" sqref="J2:J377 J379:J946" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C379:C414 C554:C946 C2:C377 C458:C470 C433:C436" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F9CFCB-28C5-470F-A6E6-C029E2AA151E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="929">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,6 +2981,12 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t>BR-022.1</t>
+  </si>
+  <si>
+    <t>Chock Tray Layout Photo</t>
   </si>
 </sst>
 </file>
@@ -3313,7 +3319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P553"/>
+  <dimension ref="A1:P554"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5332,7 +5338,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>150</v>
+        <v>927</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
@@ -5345,7 +5351,7 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>152</v>
+        <v>928</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5362,7 +5368,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
@@ -5375,7 +5381,7 @@
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5392,7 +5398,7 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -5401,11 +5407,11 @@
         <v>126</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5422,7 +5428,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
@@ -5435,7 +5441,7 @@
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5452,7 +5458,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
@@ -5465,7 +5471,7 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5482,7 +5488,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
@@ -5495,7 +5501,7 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5512,7 +5518,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
@@ -5525,7 +5531,7 @@
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5542,7 +5548,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
@@ -5555,7 +5561,7 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5572,7 +5578,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
@@ -5585,7 +5591,7 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5602,7 +5608,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
@@ -5611,11 +5617,11 @@
         <v>126</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5632,7 +5638,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
@@ -5645,7 +5651,7 @@
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5662,7 +5668,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
@@ -5675,7 +5681,7 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5692,7 +5698,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
@@ -5705,7 +5711,7 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5722,7 +5728,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
@@ -5735,7 +5741,7 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5752,18 +5758,20 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D82" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5780,18 +5788,18 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5808,7 +5816,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
@@ -5819,7 +5827,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5836,7 +5844,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
@@ -5847,7 +5855,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5864,7 +5872,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
@@ -5875,7 +5883,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5892,7 +5900,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>10</v>
@@ -5903,7 +5911,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5920,7 +5928,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
@@ -5931,7 +5939,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5948,7 +5956,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>10</v>
@@ -5959,7 +5967,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5976,7 +5984,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>10</v>
@@ -5987,7 +5995,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -6004,7 +6012,7 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>10</v>
@@ -6015,7 +6023,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -6032,7 +6040,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>10</v>
@@ -6043,7 +6051,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6058,9 +6066,9 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
     </row>
-    <row r="93" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
@@ -6071,7 +6079,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -6086,9 +6094,9 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>10</v>
@@ -6099,7 +6107,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -6116,7 +6124,7 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>10</v>
@@ -6127,7 +6135,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -6144,7 +6152,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>10</v>
@@ -6155,7 +6163,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -6172,7 +6180,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>10</v>
@@ -6183,7 +6191,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -6200,7 +6208,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>10</v>
@@ -6211,7 +6219,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -6228,7 +6236,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>10</v>
@@ -6239,7 +6247,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -6256,7 +6264,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
@@ -6267,7 +6275,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -6284,7 +6292,7 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>10</v>
@@ -6295,7 +6303,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -6312,7 +6320,7 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
@@ -6323,7 +6331,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -6340,7 +6348,7 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
@@ -6351,7 +6359,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -6368,7 +6376,7 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
@@ -6379,7 +6387,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -6396,7 +6404,7 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
@@ -6407,7 +6415,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -6424,7 +6432,7 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
@@ -6435,7 +6443,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -6452,7 +6460,7 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
@@ -6463,7 +6471,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6480,7 +6488,7 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -6491,7 +6499,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6506,9 +6514,9 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
     </row>
-    <row r="109" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -6519,13 +6527,11 @@
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
-      <c r="I109" s="5" t="s">
-        <v>239</v>
-      </c>
+      <c r="I109" s="5"/>
       <c r="J109" s="5" t="s">
         <v>14</v>
       </c>
@@ -6536,9 +6542,9 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -6549,12 +6555,12 @@
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5" t="s">
-        <v>923</v>
+        <v>239</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>14</v>
@@ -6568,24 +6574,24 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>244</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
+      <c r="I111" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="J111" s="5" t="s">
         <v>14</v>
       </c>
@@ -6598,7 +6604,7 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
@@ -6611,7 +6617,7 @@
       </c>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
@@ -6628,7 +6634,7 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
@@ -6641,7 +6647,7 @@
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6658,7 +6664,7 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>10</v>
@@ -6671,7 +6677,7 @@
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6688,7 +6694,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>10</v>
@@ -6701,7 +6707,7 @@
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6716,9 +6722,9 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
     </row>
-    <row r="116" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
@@ -6731,7 +6737,7 @@
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6746,9 +6752,9 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>10</v>
@@ -6757,11 +6763,11 @@
         <v>243</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6778,7 +6784,7 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>10</v>
@@ -6791,7 +6797,7 @@
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6808,7 +6814,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>10</v>
@@ -6821,7 +6827,7 @@
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6838,7 +6844,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>10</v>
@@ -6851,7 +6857,7 @@
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -6868,7 +6874,7 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
@@ -6881,7 +6887,7 @@
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
@@ -6898,7 +6904,7 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
@@ -6911,7 +6917,7 @@
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
@@ -6928,7 +6934,7 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>10</v>
@@ -6941,7 +6947,7 @@
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
@@ -6958,7 +6964,7 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
@@ -6971,7 +6977,7 @@
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -6988,7 +6994,7 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
@@ -7001,7 +7007,7 @@
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -7018,7 +7024,7 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>10</v>
@@ -7031,7 +7037,7 @@
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -7048,7 +7054,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>10</v>
@@ -7061,7 +7067,7 @@
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -7076,9 +7082,9 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
     </row>
-    <row r="128" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>10</v>
@@ -7087,17 +7093,15 @@
         <v>243</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
-      <c r="I128" s="5" t="s">
-        <v>282</v>
-      </c>
+      <c r="I128" s="5"/>
       <c r="J128" s="5" t="s">
         <v>14</v>
       </c>
@@ -7108,9 +7112,9 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>10</v>
@@ -7123,11 +7127,13 @@
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
+      <c r="I129" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="J129" s="5" t="s">
         <v>14</v>
       </c>
@@ -7140,7 +7146,7 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>10</v>
@@ -7153,7 +7159,7 @@
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
@@ -7170,7 +7176,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>10</v>
@@ -7183,7 +7189,7 @@
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -7200,7 +7206,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>10</v>
@@ -7213,7 +7219,7 @@
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -7228,9 +7234,9 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
     </row>
-    <row r="133" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>10</v>
@@ -7243,7 +7249,7 @@
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -7258,9 +7264,9 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>10</v>
@@ -7273,7 +7279,7 @@
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7290,18 +7296,20 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D135" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7318,7 +7326,7 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>10</v>
@@ -7329,7 +7337,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7346,7 +7354,7 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
@@ -7357,7 +7365,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7374,7 +7382,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -7385,7 +7393,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -7402,7 +7410,7 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -7413,7 +7421,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7430,7 +7438,7 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -7441,7 +7449,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7458,7 +7466,7 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -7469,7 +7477,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7486,7 +7494,7 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -7497,7 +7505,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7514,7 +7522,7 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -7525,7 +7533,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -7542,7 +7550,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -7553,7 +7561,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7570,7 +7578,7 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -7581,7 +7589,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7598,7 +7606,7 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -7609,7 +7617,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -7624,51 +7632,55 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
     </row>
-    <row r="147" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="7"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K147" s="5"/>
+      <c r="L147" s="5"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5"/>
+      <c r="P147" s="5"/>
+    </row>
+    <row r="148" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>321</v>
@@ -7681,7 +7693,7 @@
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
@@ -7692,7 +7704,7 @@
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>321</v>
@@ -7705,7 +7717,7 @@
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -7716,7 +7728,7 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>321</v>
@@ -7725,11 +7737,11 @@
         <v>11</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -7740,7 +7752,7 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>321</v>
@@ -7753,7 +7765,7 @@
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -7764,7 +7776,7 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>321</v>
@@ -7777,7 +7789,7 @@
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -7788,7 +7800,7 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>321</v>
@@ -7801,7 +7813,7 @@
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -7812,7 +7824,7 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>321</v>
@@ -7825,7 +7837,7 @@
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -7836,7 +7848,7 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>321</v>
@@ -7849,7 +7861,7 @@
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -7860,7 +7872,7 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>321</v>
@@ -7873,7 +7885,7 @@
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -7884,7 +7896,7 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>321</v>
@@ -7897,7 +7909,7 @@
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>42</v>
+        <v>337</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -7908,7 +7920,7 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>321</v>
@@ -7921,7 +7933,7 @@
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>340</v>
+        <v>42</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -7932,7 +7944,7 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>321</v>
@@ -7945,7 +7957,7 @@
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7956,7 +7968,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
@@ -7969,7 +7981,7 @@
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -7980,7 +7992,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>321</v>
@@ -7993,7 +8005,7 @@
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8004,7 +8016,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>321</v>
@@ -8017,7 +8029,7 @@
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8028,7 +8040,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>321</v>
@@ -8041,7 +8053,7 @@
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>44</v>
+        <v>348</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8050,9 +8062,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>321</v>
@@ -8065,28 +8077,40 @@
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>351</v>
+        <v>44</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
-      <c r="I165" s="6" t="s">
-        <v>352</v>
-      </c>
+      <c r="I165" s="6"/>
       <c r="J165" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
+    <row r="166" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
+      <c r="F166" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
+      <c r="I166" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="J166" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
@@ -8136,43 +8160,43 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A171" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
       <c r="E171" s="6"/>
-      <c r="F171" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
-      <c r="I171" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="J171" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
+      <c r="I171" s="6"/>
+      <c r="J171" s="6"/>
+    </row>
+    <row r="172" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
+      <c r="F172" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
+      <c r="I172" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
@@ -8223,32 +8247,20 @@
       <c r="J176" s="6"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D177" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="6" t="s">
-        <v>356</v>
-      </c>
+      <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
-      <c r="J177" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J177" s="6"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>321</v>
@@ -8261,7 +8273,7 @@
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
@@ -8272,7 +8284,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>321</v>
@@ -8285,7 +8297,7 @@
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -8296,7 +8308,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>321</v>
@@ -8309,7 +8321,7 @@
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -8318,9 +8330,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>321</v>
@@ -8331,29 +8343,41 @@
       <c r="D181" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
-      <c r="I181" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="I181" s="6"/>
       <c r="J181" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+    <row r="182" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
+      <c r="I182" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
@@ -8404,32 +8428,20 @@
       <c r="J186" s="6"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A187" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C187" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="6" t="s">
-        <v>368</v>
-      </c>
+      <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
-      <c r="J187" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J187" s="6"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>321</v>
@@ -8442,7 +8454,7 @@
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
@@ -8453,7 +8465,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>321</v>
@@ -8466,20 +8478,18 @@
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
-      <c r="I189" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I189" s="6"/>
       <c r="J189" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>321</v>
@@ -8492,18 +8502,20 @@
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
+      <c r="I190" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J190" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>321</v>
@@ -8516,7 +8528,7 @@
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
@@ -8525,9 +8537,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>321</v>
@@ -8540,7 +8552,7 @@
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8551,7 +8563,7 @@
     </row>
     <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>321</v>
@@ -8564,7 +8576,7 @@
       </c>
       <c r="E193" s="6"/>
       <c r="F193" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -8575,7 +8587,7 @@
     </row>
     <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>321</v>
@@ -8588,7 +8600,7 @@
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -8597,9 +8609,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>321</v>
@@ -8612,7 +8624,7 @@
       </c>
       <c r="E195" s="6"/>
       <c r="F195" s="6" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -8623,7 +8635,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>321</v>
@@ -8636,7 +8648,7 @@
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -8647,7 +8659,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>321</v>
@@ -8660,7 +8672,7 @@
       </c>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -8671,7 +8683,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>321</v>
@@ -8684,7 +8696,7 @@
       </c>
       <c r="E198" s="6"/>
       <c r="F198" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -8695,7 +8707,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>321</v>
@@ -8708,7 +8720,7 @@
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>387</v>
+        <v>97</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8719,7 +8731,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>321</v>
@@ -8732,7 +8744,7 @@
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>93</v>
+        <v>387</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8743,7 +8755,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>321</v>
@@ -8756,7 +8768,7 @@
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>390</v>
+        <v>93</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -8767,7 +8779,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>321</v>
@@ -8780,7 +8792,7 @@
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8791,7 +8803,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>321</v>
@@ -8804,7 +8816,7 @@
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8815,7 +8827,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>321</v>
@@ -8828,7 +8840,7 @@
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>395</v>
+        <v>76</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8839,7 +8851,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>321</v>
@@ -8852,7 +8864,7 @@
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8863,31 +8875,31 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D206" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
-      <c r="I206" s="6" t="s">
-        <v>401</v>
-      </c>
+      <c r="I206" s="6"/>
       <c r="J206" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>321</v>
@@ -8898,18 +8910,20 @@
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
+      <c r="I207" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="J207" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>321</v>
@@ -8920,7 +8934,7 @@
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
@@ -8931,18 +8945,18 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8951,9 +8965,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>321</v>
@@ -8964,7 +8978,7 @@
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -8973,9 +8987,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>321</v>
@@ -8986,7 +9000,7 @@
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -8995,9 +9009,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>321</v>
@@ -9006,29 +9020,39 @@
         <v>407</v>
       </c>
       <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
-      <c r="I212" s="6" t="s">
-        <v>415</v>
-      </c>
+      <c r="I212" s="6"/>
       <c r="J212" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="6"/>
+    <row r="213" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A213" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
+      <c r="F213" s="6" t="s">
+        <v>414</v>
+      </c>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
-      <c r="J213" s="6"/>
+      <c r="I213" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J213" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
@@ -9115,30 +9139,20 @@
       <c r="J220" s="6"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A221" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="6"/>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="6" t="s">
-        <v>417</v>
-      </c>
+      <c r="F221" s="6"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
-      <c r="J221" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J221" s="6"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>321</v>
@@ -9149,7 +9163,7 @@
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
@@ -9160,7 +9174,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>321</v>
@@ -9171,7 +9185,7 @@
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9182,7 +9196,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>321</v>
@@ -9193,7 +9207,7 @@
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
@@ -9204,7 +9218,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>321</v>
@@ -9215,7 +9229,7 @@
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
@@ -9226,7 +9240,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>321</v>
@@ -9237,20 +9251,18 @@
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
-      <c r="I226" s="6" t="s">
-        <v>924</v>
-      </c>
+      <c r="I226" s="6"/>
       <c r="J226" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>321</v>
@@ -9261,18 +9273,20 @@
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
+      <c r="I227" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J227" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>321</v>
@@ -9283,7 +9297,7 @@
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
@@ -9294,7 +9308,7 @@
     </row>
     <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>321</v>
@@ -9305,7 +9319,7 @@
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
@@ -9314,9 +9328,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>321</v>
@@ -9327,7 +9341,7 @@
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
@@ -9338,18 +9352,18 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
@@ -9360,7 +9374,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>321</v>
@@ -9371,7 +9385,7 @@
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -9382,7 +9396,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>321</v>
@@ -9393,20 +9407,18 @@
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
-      <c r="I233" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I233" s="6"/>
       <c r="J233" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>321</v>
@@ -9417,7 +9429,7 @@
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
@@ -9430,7 +9442,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>321</v>
@@ -9441,18 +9453,20 @@
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
-      <c r="I235" s="6"/>
+      <c r="I235" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J235" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>321</v>
@@ -9463,7 +9477,7 @@
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
@@ -9472,9 +9486,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>321</v>
@@ -9485,7 +9499,7 @@
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9496,7 +9510,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>321</v>
@@ -9507,7 +9521,7 @@
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
@@ -9518,7 +9532,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>321</v>
@@ -9529,7 +9543,7 @@
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9540,7 +9554,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>321</v>
@@ -9551,20 +9565,18 @@
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
-      <c r="I240" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I240" s="6"/>
       <c r="J240" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>321</v>
@@ -9575,7 +9587,7 @@
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
@@ -9586,9 +9598,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>321</v>
@@ -9599,28 +9611,40 @@
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J242" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
+    <row r="243" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A243" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
-      <c r="F243" s="6"/>
+      <c r="F243" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
-      <c r="I243" s="6"/>
-      <c r="J243" s="6"/>
+      <c r="I243" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="J243" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
@@ -9682,31 +9706,21 @@
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
     </row>
-    <row r="249" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A249" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>462</v>
-      </c>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A249" s="6"/>
+      <c r="B249" s="6"/>
+      <c r="C249" s="6"/>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="6" t="s">
-        <v>463</v>
-      </c>
+      <c r="F249" s="6"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
-      <c r="J249" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J249" s="6"/>
+    </row>
+    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>321</v>
@@ -9717,7 +9731,7 @@
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
@@ -9726,9 +9740,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
@@ -9737,29 +9751,39 @@
         <v>462</v>
       </c>
       <c r="D251" s="6"/>
+      <c r="E251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
-      <c r="I251" s="6" t="s">
-        <v>468</v>
-      </c>
+      <c r="I251" s="6"/>
       <c r="J251" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="6"/>
+    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A252" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D252" s="6"/>
-      <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
+      <c r="F252" s="6" t="s">
+        <v>467</v>
+      </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
-      <c r="I252" s="6"/>
-      <c r="J252" s="6"/>
+      <c r="I252" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
@@ -9786,30 +9810,20 @@
       <c r="J254" s="6"/>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A255" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A255" s="6"/>
+      <c r="B255" s="6"/>
+      <c r="C255" s="6"/>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
-      <c r="F255" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="F255" s="6"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
-      <c r="J255" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J255" s="6"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>321</v>
@@ -9820,7 +9834,7 @@
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
@@ -9831,7 +9845,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>321</v>
@@ -9842,7 +9856,7 @@
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9851,9 +9865,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>321</v>
@@ -9864,7 +9878,7 @@
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9875,7 +9889,7 @@
     </row>
     <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>321</v>
@@ -9886,7 +9900,7 @@
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9895,9 +9909,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>321</v>
@@ -9908,7 +9922,7 @@
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9917,9 +9931,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
@@ -9930,7 +9944,7 @@
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9941,7 +9955,7 @@
     </row>
     <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
@@ -9952,7 +9966,7 @@
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9963,7 +9977,7 @@
     </row>
     <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
@@ -9974,7 +9988,7 @@
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -9983,9 +9997,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>321</v>
@@ -9996,7 +10010,7 @@
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -10007,7 +10021,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>321</v>
@@ -10018,7 +10032,7 @@
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
@@ -10029,7 +10043,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>321</v>
@@ -10040,7 +10054,7 @@
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10049,9 +10063,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
@@ -10062,7 +10076,7 @@
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10071,9 +10085,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
@@ -10084,7 +10098,7 @@
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10095,18 +10109,18 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10117,7 +10131,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
@@ -10128,7 +10142,7 @@
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10139,7 +10153,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
@@ -10150,7 +10164,7 @@
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10161,18 +10175,18 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10183,7 +10197,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
@@ -10194,7 +10208,7 @@
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10205,7 +10219,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
@@ -10216,7 +10230,7 @@
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10227,7 +10241,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
@@ -10238,7 +10252,7 @@
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6" t="s">
-        <v>108</v>
+        <v>511</v>
       </c>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
@@ -10249,7 +10263,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
@@ -10260,7 +10274,7 @@
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10271,7 +10285,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
@@ -10282,7 +10296,7 @@
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10293,7 +10307,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
@@ -10304,7 +10318,7 @@
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10315,7 +10329,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
@@ -10326,7 +10340,7 @@
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10337,7 +10351,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
@@ -10348,7 +10362,7 @@
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10357,66 +10371,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D281" s="6"/>
+      <c r="E281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
-      <c r="I281" s="6" t="s">
-        <v>526</v>
-      </c>
+      <c r="I281" s="6"/>
       <c r="J281" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A282" s="6"/>
-      <c r="B282" s="6"/>
-      <c r="C282" s="6"/>
+    <row r="282" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D282" s="6"/>
-      <c r="E282" s="6"/>
-      <c r="F282" s="6"/>
+      <c r="F282" s="6" t="s">
+        <v>525</v>
+      </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="6"/>
-      <c r="J282" s="6"/>
-    </row>
-    <row r="283" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A283" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="I282" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J282" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283" s="6"/>
+      <c r="B283" s="6"/>
+      <c r="C283" s="6"/>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="6" t="s">
-        <v>528</v>
-      </c>
+      <c r="F283" s="6"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
-      <c r="J283" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J283" s="6"/>
+    </row>
+    <row r="284" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>321</v>
@@ -10427,7 +10441,7 @@
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
       <c r="F284" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
@@ -10438,7 +10452,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
@@ -10449,7 +10463,7 @@
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10460,18 +10474,18 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10482,7 +10496,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
@@ -10493,7 +10507,7 @@
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10504,7 +10518,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
@@ -10515,7 +10529,7 @@
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10526,7 +10540,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
@@ -10537,7 +10551,7 @@
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10548,7 +10562,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
@@ -10559,7 +10573,7 @@
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10568,9 +10582,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
@@ -10581,7 +10595,7 @@
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10590,9 +10604,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
@@ -10603,7 +10617,7 @@
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10614,7 +10628,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
@@ -10625,7 +10639,7 @@
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
@@ -10636,7 +10650,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>321</v>
@@ -10647,7 +10661,7 @@
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
@@ -10656,9 +10670,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
@@ -10667,29 +10681,39 @@
         <v>534</v>
       </c>
       <c r="D295" s="6"/>
+      <c r="E295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
-      <c r="I295" s="6" t="s">
-        <v>554</v>
-      </c>
+      <c r="I295" s="6"/>
       <c r="J295" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A296" s="6"/>
-      <c r="B296" s="6"/>
-      <c r="C296" s="6"/>
+    <row r="296" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A296" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D296" s="6"/>
-      <c r="E296" s="6"/>
-      <c r="F296" s="6"/>
+      <c r="F296" s="6" t="s">
+        <v>553</v>
+      </c>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="6"/>
-      <c r="J296" s="6"/>
+      <c r="I296" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="J296" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
@@ -10739,41 +10763,41 @@
       <c r="I300" s="6"/>
       <c r="J300" s="6"/>
     </row>
-    <row r="301" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A301" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="B301" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C301" s="6" t="s">
-        <v>534</v>
-      </c>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A301" s="6"/>
+      <c r="B301" s="6"/>
+      <c r="C301" s="6"/>
       <c r="D301" s="6"/>
       <c r="E301" s="6"/>
-      <c r="F301" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="F301" s="6"/>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
-      <c r="I301" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="J301" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" s="6"/>
-      <c r="B302" s="6"/>
-      <c r="C302" s="6"/>
+      <c r="I301" s="6"/>
+      <c r="J301" s="6"/>
+    </row>
+    <row r="302" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A302" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
-      <c r="F302" s="6"/>
+      <c r="F302" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
-      <c r="I302" s="6"/>
-      <c r="J302" s="6"/>
+      <c r="I302" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J302" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
@@ -11088,30 +11112,20 @@
       <c r="J328" s="6"/>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A329" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C329" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A329" s="6"/>
+      <c r="B329" s="6"/>
+      <c r="C329" s="6"/>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
-      <c r="F329" s="6" t="s">
-        <v>559</v>
-      </c>
+      <c r="F329" s="6"/>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
       <c r="I329" s="6"/>
-      <c r="J329" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J329" s="6"/>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B330" s="6" t="s">
         <v>321</v>
@@ -11122,7 +11136,7 @@
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
       <c r="F330" s="6" t="s">
-        <v>255</v>
+        <v>559</v>
       </c>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
@@ -11131,9 +11145,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>321</v>
@@ -11144,7 +11158,7 @@
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>562</v>
+        <v>255</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11155,7 +11169,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>321</v>
@@ -11166,7 +11180,7 @@
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11177,7 +11191,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>321</v>
@@ -11188,7 +11202,7 @@
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11199,18 +11213,18 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11221,7 +11235,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>321</v>
@@ -11232,7 +11246,7 @@
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11243,18 +11257,18 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11265,7 +11279,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>321</v>
@@ -11276,7 +11290,7 @@
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11287,7 +11301,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>321</v>
@@ -11298,7 +11312,7 @@
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11309,18 +11323,18 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>504</v>
+        <v>578</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11331,7 +11345,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>321</v>
@@ -11342,7 +11356,7 @@
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11353,7 +11367,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
@@ -11364,7 +11378,7 @@
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
       <c r="F341" s="6" t="s">
-        <v>307</v>
+        <v>582</v>
       </c>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
@@ -11375,18 +11389,18 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>586</v>
+        <v>307</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11397,7 +11411,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
@@ -11408,7 +11422,7 @@
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11419,7 +11433,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
@@ -11430,7 +11444,7 @@
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11441,7 +11455,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
@@ -11452,7 +11466,7 @@
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11461,9 +11475,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
@@ -11474,7 +11488,7 @@
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11483,20 +11497,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11507,7 +11521,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
@@ -11518,7 +11532,7 @@
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11529,7 +11543,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
@@ -11540,7 +11554,7 @@
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11551,7 +11565,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
@@ -11562,7 +11576,7 @@
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11573,7 +11587,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
@@ -11584,7 +11598,7 @@
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11595,7 +11609,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
@@ -11606,7 +11620,7 @@
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11615,9 +11629,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
@@ -11628,7 +11642,7 @@
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11637,9 +11651,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
@@ -11650,7 +11664,7 @@
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11659,45 +11673,43 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="9"/>
-      <c r="B355" s="9"/>
-      <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="F355" s="9"/>
-      <c r="G355" s="9"/>
-      <c r="H355" s="9"/>
-      <c r="I355" s="9"/>
-      <c r="J355" s="9"/>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A356" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B356" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C356" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D356" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E356" s="6"/>
-      <c r="F356" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G356" s="6"/>
-      <c r="H356" s="6"/>
-      <c r="I356" s="6"/>
-      <c r="J356" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A355" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D355" s="6"/>
+      <c r="E355" s="6"/>
+      <c r="F355" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G355" s="6"/>
+      <c r="H355" s="6"/>
+      <c r="I355" s="6"/>
+      <c r="J355" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A356" s="9"/>
+      <c r="B356" s="9"/>
+      <c r="C356" s="9"/>
+      <c r="D356" s="9"/>
+      <c r="E356" s="9"/>
+      <c r="F356" s="9"/>
+      <c r="G356" s="9"/>
+      <c r="H356" s="9"/>
+      <c r="I356" s="9"/>
+      <c r="J356" s="9"/>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B357" s="6" t="s">
         <v>613</v>
@@ -11710,7 +11722,7 @@
       </c>
       <c r="E357" s="6"/>
       <c r="F357" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
@@ -11721,7 +11733,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B358" s="6" t="s">
         <v>613</v>
@@ -11730,11 +11742,11 @@
         <v>11</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>616</v>
+        <v>18</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11743,9 +11755,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B359" s="6" t="s">
         <v>613</v>
@@ -11757,29 +11769,41 @@
         <v>37</v>
       </c>
       <c r="E359" s="6"/>
-      <c r="F359" s="10" t="s">
-        <v>618</v>
+      <c r="F359" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
-      <c r="I359" s="10" t="s">
-        <v>619</v>
-      </c>
+      <c r="I359" s="6"/>
       <c r="J359" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A360" s="6"/>
-      <c r="B360" s="6"/>
-      <c r="C360" s="6"/>
-      <c r="D360" s="6"/>
+    <row r="360" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A360" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="E360" s="6"/>
-      <c r="F360" s="6"/>
+      <c r="F360" s="10" t="s">
+        <v>618</v>
+      </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
-      <c r="I360" s="6"/>
-      <c r="J360" s="6"/>
+      <c r="I360" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="J360" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
@@ -11830,32 +11854,20 @@
       <c r="J364" s="6"/>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A365" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="B365" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C365" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D365" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A365" s="6"/>
+      <c r="B365" s="6"/>
+      <c r="C365" s="6"/>
+      <c r="D365" s="6"/>
       <c r="E365" s="6"/>
-      <c r="F365" s="6" t="s">
-        <v>621</v>
-      </c>
+      <c r="F365" s="6"/>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
       <c r="I365" s="6"/>
-      <c r="J365" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J365" s="6"/>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B366" s="6" t="s">
         <v>613</v>
@@ -11868,7 +11880,7 @@
       </c>
       <c r="E366" s="6"/>
       <c r="F366" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -11879,7 +11891,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B367" s="6" t="s">
         <v>613</v>
@@ -11892,7 +11904,7 @@
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="6" t="s">
-        <v>329</v>
+        <v>623</v>
       </c>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
@@ -11903,7 +11915,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B368" s="6" t="s">
         <v>613</v>
@@ -11916,7 +11928,7 @@
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>626</v>
+        <v>329</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11927,7 +11939,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B369" s="6" t="s">
         <v>613</v>
@@ -11940,7 +11952,7 @@
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11951,7 +11963,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B370" s="6" t="s">
         <v>613</v>
@@ -11964,7 +11976,7 @@
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11975,7 +11987,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B371" s="6" t="s">
         <v>613</v>
@@ -11988,7 +12000,7 @@
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -11999,7 +12011,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B372" s="6" t="s">
         <v>613</v>
@@ -12012,7 +12024,7 @@
       </c>
       <c r="E372" s="6"/>
       <c r="F372" s="6" t="s">
-        <v>42</v>
+        <v>632</v>
       </c>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
@@ -12021,9 +12033,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B373" s="6" t="s">
         <v>613</v>
@@ -12036,7 +12048,7 @@
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>635</v>
+        <v>42</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12045,9 +12057,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B374" s="6" t="s">
         <v>613</v>
@@ -12060,7 +12072,7 @@
       </c>
       <c r="E374" s="6"/>
       <c r="F374" s="6" t="s">
-        <v>342</v>
+        <v>635</v>
       </c>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
@@ -12071,7 +12083,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B375" s="6" t="s">
         <v>613</v>
@@ -12084,7 +12096,7 @@
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>638</v>
+        <v>342</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12095,7 +12107,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B376" s="6" t="s">
         <v>613</v>
@@ -12108,7 +12120,7 @@
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12119,7 +12131,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B377" s="6" t="s">
         <v>613</v>
@@ -12132,7 +12144,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12141,33 +12153,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="10" t="s">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A378" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D378" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E378" s="6"/>
+      <c r="F378" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="G378" s="6"/>
+      <c r="H378" s="6"/>
+      <c r="I378" s="6"/>
+      <c r="J378" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="B379" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C379" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D379" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E379" s="6"/>
-      <c r="F379" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="G379" s="6"/>
-      <c r="H379" s="6"/>
-      <c r="I379" s="6"/>
-      <c r="J379" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A380" s="6" t="s">
-        <v>645</v>
       </c>
       <c r="B380" s="6" t="s">
         <v>613</v>
@@ -12180,28 +12192,40 @@
       </c>
       <c r="E380" s="6"/>
       <c r="F380" s="10" t="s">
-        <v>351</v>
+        <v>644</v>
       </c>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
-      <c r="I380" s="10" t="s">
-        <v>646</v>
-      </c>
+      <c r="I380" s="6"/>
       <c r="J380" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A381" s="6"/>
-      <c r="B381" s="6"/>
-      <c r="C381" s="6"/>
-      <c r="D381" s="6"/>
+    <row r="381" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A381" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D381" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E381" s="6"/>
-      <c r="F381" s="6"/>
+      <c r="F381" s="10" t="s">
+        <v>351</v>
+      </c>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
-      <c r="I381" s="6"/>
-      <c r="J381" s="6"/>
+      <c r="I381" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J381" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
@@ -12227,43 +12251,43 @@
       <c r="I383" s="6"/>
       <c r="J383" s="6"/>
     </row>
-    <row r="384" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A384" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B384" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C384" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D384" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A384" s="6"/>
+      <c r="B384" s="6"/>
+      <c r="C384" s="6"/>
+      <c r="D384" s="6"/>
       <c r="E384" s="6"/>
-      <c r="F384" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="F384" s="6"/>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
-      <c r="I384" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="J384" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A385" s="6"/>
-      <c r="B385" s="6"/>
-      <c r="C385" s="6"/>
-      <c r="D385" s="6"/>
+      <c r="I384" s="6"/>
+      <c r="J384" s="6"/>
+    </row>
+    <row r="385" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A385" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E385" s="6"/>
-      <c r="F385" s="6"/>
+      <c r="F385" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
-      <c r="I385" s="6"/>
-      <c r="J385" s="6"/>
+      <c r="I385" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="J385" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
@@ -12337,43 +12361,43 @@
       <c r="I391" s="6"/>
       <c r="J391" s="6"/>
     </row>
-    <row r="392" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A392" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B392" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C392" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D392" s="6" t="s">
-        <v>650</v>
-      </c>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A392" s="6"/>
+      <c r="B392" s="6"/>
+      <c r="C392" s="6"/>
+      <c r="D392" s="6"/>
       <c r="E392" s="6"/>
-      <c r="F392" s="6" t="s">
-        <v>651</v>
-      </c>
+      <c r="F392" s="6"/>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
-      <c r="I392" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="J392" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A393" s="6"/>
-      <c r="B393" s="6"/>
-      <c r="C393" s="6"/>
-      <c r="D393" s="6"/>
+      <c r="I392" s="6"/>
+      <c r="J392" s="6"/>
+    </row>
+    <row r="393" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A393" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E393" s="6"/>
-      <c r="F393" s="6"/>
+      <c r="F393" s="6" t="s">
+        <v>651</v>
+      </c>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
-      <c r="I393" s="6"/>
-      <c r="J393" s="6"/>
+      <c r="I393" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="J393" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
@@ -12424,32 +12448,20 @@
       <c r="J397" s="6"/>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A398" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B398" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C398" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D398" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A398" s="6"/>
+      <c r="B398" s="6"/>
+      <c r="C398" s="6"/>
+      <c r="D398" s="6"/>
       <c r="E398" s="6"/>
-      <c r="F398" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="F398" s="6"/>
       <c r="G398" s="6"/>
       <c r="H398" s="6"/>
       <c r="I398" s="6"/>
-      <c r="J398" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J398" s="6"/>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B399" s="6" t="s">
         <v>613</v>
@@ -12462,7 +12474,7 @@
       </c>
       <c r="E399" s="6"/>
       <c r="F399" s="6" t="s">
-        <v>655</v>
+        <v>62</v>
       </c>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
@@ -12471,9 +12483,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>613</v>
@@ -12486,7 +12498,7 @@
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12495,9 +12507,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B401" s="6" t="s">
         <v>613</v>
@@ -12510,7 +12522,7 @@
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12521,7 +12533,7 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B402" s="6" t="s">
         <v>613</v>
@@ -12534,20 +12546,18 @@
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
-      <c r="I402" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I402" s="6"/>
       <c r="J402" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B403" s="6" t="s">
         <v>613</v>
@@ -12560,18 +12570,20 @@
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
-      <c r="I403" s="6"/>
+      <c r="I403" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J403" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B404" s="6" t="s">
         <v>613</v>
@@ -12584,7 +12596,7 @@
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
@@ -12593,9 +12605,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="405" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B405" s="6" t="s">
         <v>613</v>
@@ -12608,7 +12620,7 @@
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12617,9 +12629,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B406" s="6" t="s">
         <v>613</v>
@@ -12632,7 +12644,7 @@
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12643,7 +12655,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B407" s="6" t="s">
         <v>613</v>
@@ -12652,11 +12664,11 @@
         <v>11</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12667,7 +12679,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B408" s="6" t="s">
         <v>613</v>
@@ -12680,7 +12692,7 @@
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
-        <v>97</v>
+        <v>672</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
@@ -12691,7 +12703,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B409" s="6" t="s">
         <v>613</v>
@@ -12704,7 +12716,7 @@
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
@@ -12715,7 +12727,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B410" s="6" t="s">
         <v>613</v>
@@ -12727,8 +12739,8 @@
         <v>671</v>
       </c>
       <c r="E410" s="6"/>
-      <c r="F410" s="10" t="s">
-        <v>676</v>
+      <c r="F410" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12739,7 +12751,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B411" s="6" t="s">
         <v>613</v>
@@ -12751,8 +12763,8 @@
         <v>671</v>
       </c>
       <c r="E411" s="6"/>
-      <c r="F411" s="6" t="s">
-        <v>89</v>
+      <c r="F411" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12763,7 +12775,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B412" s="6" t="s">
         <v>613</v>
@@ -12776,7 +12788,7 @@
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12787,7 +12799,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>613</v>
@@ -12799,8 +12811,8 @@
         <v>671</v>
       </c>
       <c r="E413" s="6"/>
-      <c r="F413" s="10" t="s">
-        <v>680</v>
+      <c r="F413" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12811,7 +12823,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>613</v>
@@ -12823,8 +12835,8 @@
         <v>671</v>
       </c>
       <c r="E414" s="6"/>
-      <c r="F414" s="6" t="s">
-        <v>93</v>
+      <c r="F414" s="10" t="s">
+        <v>680</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
@@ -12834,16 +12846,28 @@
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A415" s="6"/>
-      <c r="B415" s="6"/>
-      <c r="C415" s="6"/>
-      <c r="D415" s="6"/>
+      <c r="A415" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C415" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D415" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E415" s="6"/>
-      <c r="F415" s="6"/>
+      <c r="F415" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
       <c r="I415" s="6"/>
-      <c r="J415" s="6"/>
+      <c r="J415" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
@@ -12882,30 +12906,20 @@
       <c r="J418" s="6"/>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A419" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B419" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C419" s="10" t="s">
-        <v>399</v>
-      </c>
+      <c r="A419" s="6"/>
+      <c r="B419" s="6"/>
+      <c r="C419" s="6"/>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
-      <c r="F419" s="6" t="s">
-        <v>194</v>
-      </c>
+      <c r="F419" s="6"/>
       <c r="G419" s="6"/>
       <c r="H419" s="6"/>
       <c r="I419" s="6"/>
-      <c r="J419" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J419" s="6"/>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B420" s="6" t="s">
         <v>613</v>
@@ -12916,7 +12930,7 @@
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>684</v>
+        <v>194</v>
       </c>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
@@ -12927,7 +12941,7 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B421" s="6" t="s">
         <v>613</v>
@@ -12938,7 +12952,7 @@
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12949,7 +12963,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B422" s="6" t="s">
         <v>613</v>
@@ -12960,7 +12974,7 @@
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
       <c r="F422" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12971,7 +12985,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B423" s="6" t="s">
         <v>613</v>
@@ -12982,7 +12996,7 @@
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -12993,18 +13007,18 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B424" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13015,18 +13029,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B425" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C425" s="6" t="s">
-        <v>585</v>
+      <c r="C425" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13037,7 +13051,7 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B426" s="6" t="s">
         <v>613</v>
@@ -13048,7 +13062,7 @@
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13057,9 +13071,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="427" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B427" s="6" t="s">
         <v>613</v>
@@ -13070,7 +13084,7 @@
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13079,44 +13093,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B428" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C428" s="10" t="s">
-        <v>700</v>
+      <c r="C428" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
-      <c r="I428" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I428" s="6"/>
       <c r="J428" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B429" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C429" s="6" t="s">
-        <v>437</v>
+      <c r="C429" s="10" t="s">
+        <v>700</v>
       </c>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
@@ -13129,7 +13141,7 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B430" s="6" t="s">
         <v>613</v>
@@ -13140,18 +13152,20 @@
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
       <c r="F430" s="6" t="s">
-        <v>412</v>
+        <v>703</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
-      <c r="I430" s="6"/>
+      <c r="I430" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J430" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B431" s="6" t="s">
         <v>613</v>
@@ -13162,28 +13176,38 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
-      <c r="I431" s="10" t="s">
-        <v>926</v>
-      </c>
+      <c r="I431" s="6"/>
       <c r="J431" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A432" s="6"/>
-      <c r="B432" s="6"/>
-      <c r="C432" s="6"/>
+    <row r="432" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A432" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
-      <c r="F432" s="6"/>
+      <c r="F432" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
-      <c r="I432" s="6"/>
-      <c r="J432" s="6"/>
+      <c r="I432" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="J432" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
@@ -13234,30 +13258,20 @@
       <c r="J436" s="6"/>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A437" s="6" t="s">
-        <v>706</v>
-      </c>
-      <c r="B437" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C437" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A437" s="6"/>
+      <c r="B437" s="6"/>
+      <c r="C437" s="6"/>
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
-      <c r="F437" s="6" t="s">
-        <v>707</v>
-      </c>
+      <c r="F437" s="6"/>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
       <c r="I437" s="6"/>
-      <c r="J437" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J437" s="6"/>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B438" s="6" t="s">
         <v>613</v>
@@ -13268,7 +13282,7 @@
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
@@ -13279,7 +13293,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B439" s="6" t="s">
         <v>613</v>
@@ -13290,7 +13304,7 @@
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13301,7 +13315,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B440" s="6" t="s">
         <v>613</v>
@@ -13312,7 +13326,7 @@
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13323,7 +13337,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B441" s="6" t="s">
         <v>613</v>
@@ -13334,7 +13348,7 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13345,18 +13359,18 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B442" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13367,7 +13381,7 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B443" s="6" t="s">
         <v>613</v>
@@ -13378,7 +13392,7 @@
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13387,9 +13401,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="444" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B444" s="6" t="s">
         <v>613</v>
@@ -13400,7 +13414,7 @@
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
@@ -13409,9 +13423,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B445" s="6" t="s">
         <v>613</v>
@@ -13422,7 +13436,7 @@
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
       <c r="F445" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
@@ -13431,9 +13445,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B446" s="6" t="s">
         <v>613</v>
@@ -13444,7 +13458,7 @@
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
       <c r="F446" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
@@ -13453,9 +13467,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B447" s="6" t="s">
         <v>613</v>
@@ -13466,7 +13480,7 @@
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
       <c r="F447" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
@@ -13477,7 +13491,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B448" s="6" t="s">
         <v>613</v>
@@ -13488,7 +13502,7 @@
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
       <c r="F448" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
@@ -13497,9 +13511,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B449" s="6" t="s">
         <v>613</v>
@@ -13510,7 +13524,7 @@
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13519,9 +13533,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B450" s="6" t="s">
         <v>613</v>
@@ -13532,7 +13546,7 @@
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13543,7 +13557,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B451" s="6" t="s">
         <v>613</v>
@@ -13554,7 +13568,7 @@
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13563,9 +13577,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B452" s="6" t="s">
         <v>613</v>
@@ -13575,29 +13589,39 @@
       </c>
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
-      <c r="F452" s="10" t="s">
-        <v>737</v>
+      <c r="F452" s="6" t="s">
+        <v>735</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
-      <c r="I452" s="10" t="s">
-        <v>738</v>
-      </c>
+      <c r="I452" s="6"/>
       <c r="J452" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A453" s="6"/>
-      <c r="B453" s="6"/>
-      <c r="C453" s="6"/>
+    <row r="453" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A453" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C453" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="6"/>
+      <c r="F453" s="10" t="s">
+        <v>737</v>
+      </c>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
-      <c r="I453" s="6"/>
-      <c r="J453" s="6"/>
+      <c r="I453" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J453" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
@@ -13612,30 +13636,20 @@
       <c r="J454" s="6"/>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A455" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="B455" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C455" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A455" s="6"/>
+      <c r="B455" s="6"/>
+      <c r="C455" s="6"/>
       <c r="D455" s="6"/>
       <c r="E455" s="6"/>
-      <c r="F455" s="6" t="s">
-        <v>740</v>
-      </c>
+      <c r="F455" s="6"/>
       <c r="G455" s="6"/>
       <c r="H455" s="6"/>
       <c r="I455" s="6"/>
-      <c r="J455" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J455" s="6"/>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B456" s="6" t="s">
         <v>613</v>
@@ -13646,7 +13660,7 @@
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
       <c r="F456" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
@@ -13657,7 +13671,7 @@
     </row>
     <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B457" s="6" t="s">
         <v>613</v>
@@ -13668,7 +13682,7 @@
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13677,20 +13691,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B458" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C458" s="10" t="s">
-        <v>746</v>
+      <c r="C458" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13701,7 +13715,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B459" s="6" t="s">
         <v>613</v>
@@ -13712,42 +13726,42 @@
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
-      <c r="I459" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I459" s="6"/>
       <c r="J459" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B460" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>506</v>
+        <v>746</v>
       </c>
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
-      <c r="I460" s="6"/>
+      <c r="I460" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J460" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B461" s="6" t="s">
         <v>613</v>
@@ -13758,7 +13772,7 @@
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>509</v>
+        <v>751</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -13769,7 +13783,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B462" s="6" t="s">
         <v>613</v>
@@ -13780,7 +13794,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>104</v>
+        <v>509</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -13791,7 +13805,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B463" s="6" t="s">
         <v>613</v>
@@ -13802,7 +13816,7 @@
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
       <c r="F463" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
@@ -13813,7 +13827,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B464" s="6" t="s">
         <v>613</v>
@@ -13823,8 +13837,8 @@
       </c>
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
-      <c r="F464" s="10" t="s">
-        <v>756</v>
+      <c r="F464" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
@@ -13835,7 +13849,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B465" s="6" t="s">
         <v>613</v>
@@ -13845,8 +13859,8 @@
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="6" t="s">
-        <v>110</v>
+      <c r="F465" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
@@ -13857,7 +13871,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B466" s="6" t="s">
         <v>613</v>
@@ -13868,7 +13882,7 @@
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
       <c r="F466" s="6" t="s">
-        <v>759</v>
+        <v>110</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13879,7 +13893,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B467" s="6" t="s">
         <v>613</v>
@@ -13890,7 +13904,7 @@
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13901,7 +13915,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B468" s="6" t="s">
         <v>613</v>
@@ -13912,7 +13926,7 @@
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13921,9 +13935,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="469" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B469" s="6" t="s">
         <v>613</v>
@@ -13934,7 +13948,7 @@
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13943,9 +13957,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B470" s="6" t="s">
         <v>613</v>
@@ -13956,7 +13970,7 @@
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13967,18 +13981,18 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B471" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C471" s="6" t="s">
+      <c r="C471" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
@@ -13989,7 +14003,7 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B472" s="6" t="s">
         <v>613</v>
@@ -14000,7 +14014,7 @@
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -14011,7 +14025,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B473" s="6" t="s">
         <v>613</v>
@@ -14022,7 +14036,7 @@
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14033,7 +14047,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B474" s="6" t="s">
         <v>613</v>
@@ -14044,7 +14058,7 @@
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14055,7 +14069,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B475" s="6" t="s">
         <v>613</v>
@@ -14066,7 +14080,7 @@
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14077,7 +14091,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B476" s="6" t="s">
         <v>613</v>
@@ -14088,7 +14102,7 @@
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
       <c r="F476" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14099,7 +14113,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B477" s="6" t="s">
         <v>613</v>
@@ -14110,7 +14124,7 @@
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14121,7 +14135,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B478" s="6" t="s">
         <v>613</v>
@@ -14132,7 +14146,7 @@
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14143,7 +14157,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B479" s="6" t="s">
         <v>613</v>
@@ -14154,7 +14168,7 @@
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14165,7 +14179,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B480" s="6" t="s">
         <v>613</v>
@@ -14176,7 +14190,7 @@
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14187,7 +14201,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B481" s="6" t="s">
         <v>613</v>
@@ -14198,7 +14212,7 @@
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14209,7 +14223,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B482" s="6" t="s">
         <v>613</v>
@@ -14220,7 +14234,7 @@
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14231,7 +14245,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B483" s="6" t="s">
         <v>613</v>
@@ -14242,7 +14256,7 @@
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14253,7 +14267,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B484" s="6" t="s">
         <v>613</v>
@@ -14264,7 +14278,7 @@
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>541</v>
+        <v>793</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14275,7 +14289,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B485" s="6" t="s">
         <v>613</v>
@@ -14286,7 +14300,7 @@
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>796</v>
+        <v>541</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14297,7 +14311,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B486" s="6" t="s">
         <v>613</v>
@@ -14308,7 +14322,7 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14317,41 +14331,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="487" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B487" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C487" s="10" t="s">
+      <c r="C487" s="6" t="s">
         <v>506</v>
       </c>
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
-      <c r="F487" s="10" t="s">
-        <v>800</v>
+      <c r="F487" s="6" t="s">
+        <v>798</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
-      <c r="I487" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I487" s="6"/>
       <c r="J487" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A488" s="6"/>
-      <c r="B488" s="6"/>
-      <c r="C488" s="6"/>
+    <row r="488" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A488" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B488" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C488" s="10" t="s">
+        <v>506</v>
+      </c>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="6"/>
+      <c r="F488" s="10" t="s">
+        <v>800</v>
+      </c>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
-      <c r="I488" s="6"/>
-      <c r="J488" s="6"/>
+      <c r="I488" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J488" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
@@ -14594,30 +14618,20 @@
       <c r="J508" s="6"/>
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A509" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="B509" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C509" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A509" s="6"/>
+      <c r="B509" s="6"/>
+      <c r="C509" s="6"/>
       <c r="D509" s="6"/>
       <c r="E509" s="6"/>
-      <c r="F509" s="6" t="s">
-        <v>803</v>
-      </c>
+      <c r="F509" s="6"/>
       <c r="G509" s="6"/>
       <c r="H509" s="6"/>
       <c r="I509" s="6"/>
-      <c r="J509" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="510" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J509" s="6"/>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B510" s="6" t="s">
         <v>613</v>
@@ -14628,7 +14642,7 @@
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
       <c r="F510" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
@@ -14637,9 +14651,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B511" s="6" t="s">
         <v>613</v>
@@ -14650,7 +14664,7 @@
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
       <c r="F511" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
@@ -14661,7 +14675,7 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B512" s="6" t="s">
         <v>613</v>
@@ -14672,7 +14686,7 @@
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
       <c r="F512" s="6" t="s">
-        <v>425</v>
+        <v>807</v>
       </c>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
@@ -14681,41 +14695,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="513" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B513" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C513" s="10" t="s">
+      <c r="C513" s="6" t="s">
         <v>524</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
-      <c r="F513" s="10" t="s">
-        <v>810</v>
+      <c r="F513" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
-      <c r="I513" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I513" s="6"/>
       <c r="J513" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A514" s="6"/>
-      <c r="B514" s="6"/>
-      <c r="C514" s="6"/>
+    <row r="514" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A514" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B514" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C514" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="6"/>
+      <c r="F514" s="10" t="s">
+        <v>810</v>
+      </c>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
-      <c r="I514" s="6"/>
-      <c r="J514" s="6"/>
+      <c r="I514" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J514" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="6"/>
@@ -14957,41 +14981,41 @@
       <c r="I534" s="6"/>
       <c r="J534" s="6"/>
     </row>
-    <row r="535" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A535" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="B535" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C535" s="10" t="s">
-        <v>524</v>
-      </c>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A535" s="6"/>
+      <c r="B535" s="6"/>
+      <c r="C535" s="6"/>
       <c r="D535" s="6"/>
       <c r="E535" s="6"/>
-      <c r="F535" s="10" t="s">
-        <v>812</v>
-      </c>
+      <c r="F535" s="6"/>
       <c r="G535" s="6"/>
       <c r="H535" s="6"/>
-      <c r="I535" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J535" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A536" s="6"/>
-      <c r="B536" s="6"/>
-      <c r="C536" s="6"/>
+      <c r="I535" s="6"/>
+      <c r="J535" s="6"/>
+    </row>
+    <row r="536" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A536" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B536" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C536" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="6"/>
+      <c r="F536" s="10" t="s">
+        <v>812</v>
+      </c>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
-      <c r="I536" s="6"/>
-      <c r="J536" s="6"/>
+      <c r="I536" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="J536" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="6"/>
@@ -15078,30 +15102,20 @@
       <c r="J543" s="6"/>
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A544" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="B544" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C544" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A544" s="6"/>
+      <c r="B544" s="6"/>
+      <c r="C544" s="6"/>
       <c r="D544" s="6"/>
       <c r="E544" s="6"/>
-      <c r="F544" s="6" t="s">
-        <v>814</v>
-      </c>
+      <c r="F544" s="6"/>
       <c r="G544" s="6"/>
       <c r="H544" s="6"/>
       <c r="I544" s="6"/>
-      <c r="J544" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="545" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J544" s="6"/>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B545" s="6" t="s">
         <v>613</v>
@@ -15112,7 +15126,7 @@
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
       <c r="F545" s="6" t="s">
-        <v>206</v>
+        <v>814</v>
       </c>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
@@ -15123,7 +15137,7 @@
     </row>
     <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B546" s="6" t="s">
         <v>613</v>
@@ -15134,7 +15148,7 @@
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>817</v>
+        <v>206</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15143,9 +15157,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B547" s="6" t="s">
         <v>613</v>
@@ -15156,7 +15170,7 @@
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
       <c r="F547" s="6" t="s">
-        <v>210</v>
+        <v>817</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
@@ -15167,7 +15181,7 @@
     </row>
     <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B548" s="6" t="s">
         <v>613</v>
@@ -15178,7 +15192,7 @@
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="6" t="s">
-        <v>820</v>
+        <v>210</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
@@ -15189,7 +15203,7 @@
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B549" s="6" t="s">
         <v>613</v>
@@ -15200,7 +15214,7 @@
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
       <c r="F549" s="6" t="s">
-        <v>717</v>
+        <v>820</v>
       </c>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
@@ -15209,9 +15223,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="550" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B550" s="6" t="s">
         <v>613</v>
@@ -15221,88 +15235,110 @@
       </c>
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
-      <c r="F550" s="10" t="s">
-        <v>823</v>
+      <c r="F550" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
-      <c r="I550" s="10" t="s">
-        <v>824</v>
-      </c>
+      <c r="I550" s="6"/>
       <c r="J550" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A551" s="6"/>
-      <c r="B551" s="6"/>
-      <c r="C551" s="6"/>
+    <row r="551" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A551" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="B551" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C551" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="6"/>
+      <c r="F551" s="10" t="s">
+        <v>823</v>
+      </c>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
-      <c r="I551" s="6"/>
-      <c r="J551" s="6"/>
+      <c r="I551" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="J551" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A552" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="B552" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C552" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A552" s="6"/>
+      <c r="B552" s="6"/>
+      <c r="C552" s="6"/>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
-      <c r="F552" s="6" t="s">
-        <v>826</v>
-      </c>
+      <c r="F552" s="6"/>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
       <c r="I552" s="6"/>
-      <c r="J552" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="553" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="J552" s="6"/>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B553" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>828</v>
+        <v>524</v>
       </c>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
       <c r="F553" s="6" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
-      <c r="I553" s="10" t="s">
+      <c r="I553" s="6"/>
+      <c r="J553" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A554" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B554" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C554" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D554" s="6"/>
+      <c r="E554" s="6"/>
+      <c r="F554" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="G554" s="6"/>
+      <c r="H554" s="6"/>
+      <c r="I554" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="J553" s="6" t="s">
+      <c r="J554" s="6" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H377 H379:H946" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H380:H947 H2:H378" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J377 J379:J946" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J380:J947 J2:J378" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F9CFCB-28C5-470F-A6E6-C029E2AA151E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB7E575-6B9F-466C-9CE0-18C93DC75566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2983,10 +2983,10 @@
 (Keyword: Breathing Apparatus)</t>
   </si>
   <si>
-    <t>BR-022.1</t>
-  </si>
-  <si>
     <t>Chock Tray Layout Photo</t>
+  </si>
+  <si>
+    <t>BR-0122</t>
   </si>
 </sst>
 </file>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB7E575-6B9F-466C-9CE0-18C93DC75566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9968AE-08F1-438F-B55C-36B769952BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2986,7 +2986,7 @@
     <t>Chock Tray Layout Photo</t>
   </si>
   <si>
-    <t>BR-0122</t>
+    <t>BR-0100</t>
   </si>
 </sst>
 </file>
@@ -3078,7 +3078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3111,6 +3111,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3319,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P554"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5336,36 +5339,6 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
-        <v>928</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5" t="s">
-        <v>927</v>
-      </c>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
-    </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>150</v>
@@ -7660,291 +7633,237 @@
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
     </row>
-    <row r="148" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="7"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-      <c r="I148" s="7"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="7"/>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5"/>
+      <c r="P148" s="5"/>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A149" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A149" s="13"/>
+      <c r="B149" s="13"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="13"/>
+      <c r="K149" s="13"/>
+      <c r="L149" s="13"/>
+      <c r="M149" s="13"/>
+      <c r="N149" s="13"/>
+      <c r="O149" s="13"/>
+      <c r="P149" s="13"/>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A150" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A150" s="13"/>
+      <c r="B150" s="13"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="13"/>
+      <c r="K150" s="13"/>
+      <c r="L150" s="13"/>
+      <c r="M150" s="13"/>
+      <c r="N150" s="13"/>
+      <c r="O150" s="13"/>
+      <c r="P150" s="13"/>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A151" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A151" s="13"/>
+      <c r="B151" s="13"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="13"/>
+      <c r="K151" s="13"/>
+      <c r="L151" s="13"/>
+      <c r="M151" s="13"/>
+      <c r="N151" s="13"/>
+      <c r="O151" s="13"/>
+      <c r="P151" s="13"/>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A152" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A152" s="13"/>
+      <c r="B152" s="13"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="13"/>
+      <c r="K152" s="13"/>
+      <c r="L152" s="13"/>
+      <c r="M152" s="13"/>
+      <c r="N152" s="13"/>
+      <c r="O152" s="13"/>
+      <c r="P152" s="13"/>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A153" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A153" s="13"/>
+      <c r="B153" s="13"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="13"/>
+      <c r="K153" s="13"/>
+      <c r="L153" s="13"/>
+      <c r="M153" s="13"/>
+      <c r="N153" s="13"/>
+      <c r="O153" s="13"/>
+      <c r="P153" s="13"/>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A154" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A154" s="13"/>
+      <c r="B154" s="13"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="13"/>
+      <c r="K154" s="13"/>
+      <c r="L154" s="13"/>
+      <c r="M154" s="13"/>
+      <c r="N154" s="13"/>
+      <c r="O154" s="13"/>
+      <c r="P154" s="13"/>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A155" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A155" s="13"/>
+      <c r="B155" s="13"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="13"/>
+      <c r="J155" s="13"/>
+      <c r="K155" s="13"/>
+      <c r="L155" s="13"/>
+      <c r="M155" s="13"/>
+      <c r="N155" s="13"/>
+      <c r="O155" s="13"/>
+      <c r="P155" s="13"/>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A156" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A156" s="13"/>
+      <c r="B156" s="13"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="I156" s="13"/>
+      <c r="J156" s="13"/>
+      <c r="K156" s="13"/>
+      <c r="L156" s="13"/>
+      <c r="M156" s="13"/>
+      <c r="N156" s="13"/>
+      <c r="O156" s="13"/>
+      <c r="P156" s="13"/>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A157" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A157" s="13"/>
+      <c r="B157" s="13"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="I157" s="13"/>
+      <c r="J157" s="13"/>
+      <c r="K157" s="13"/>
+      <c r="L157" s="13"/>
+      <c r="M157" s="13"/>
+      <c r="N157" s="13"/>
+      <c r="O157" s="13"/>
+      <c r="P157" s="13"/>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A158" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A159" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A158" s="13"/>
+      <c r="B158" s="13"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="13"/>
+      <c r="J158" s="13"/>
+      <c r="K158" s="13"/>
+      <c r="L158" s="13"/>
+      <c r="M158" s="13"/>
+      <c r="N158" s="13"/>
+      <c r="O158" s="13"/>
+      <c r="P158" s="13"/>
+    </row>
+    <row r="159" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="7"/>
+      <c r="K159" s="7"/>
+      <c r="L159" s="7"/>
+      <c r="M159" s="7"/>
+      <c r="N159" s="7"/>
+      <c r="O159" s="7"/>
+      <c r="P159" s="7"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>321</v>
@@ -7953,11 +7872,11 @@
         <v>11</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>340</v>
+        <v>13</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7968,7 +7887,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
@@ -7977,11 +7896,11 @@
         <v>11</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>342</v>
+        <v>16</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -7992,7 +7911,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>321</v>
@@ -8001,11 +7920,11 @@
         <v>11</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>344</v>
+        <v>18</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8016,7 +7935,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>321</v>
@@ -8029,7 +7948,7 @@
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8040,7 +7959,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>321</v>
@@ -8053,7 +7972,7 @@
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8064,7 +7983,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>321</v>
@@ -8077,7 +7996,7 @@
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>44</v>
+        <v>329</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
@@ -8086,9 +8005,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>321</v>
@@ -8101,80 +8020,138 @@
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="6" t="s">
-        <v>352</v>
-      </c>
+      <c r="I166" s="6"/>
       <c r="J166" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
+      <c r="A167" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
+      <c r="F167" s="6" t="s">
+        <v>333</v>
+      </c>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
+      <c r="J167" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
+      <c r="A168" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
+      <c r="F168" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
+      <c r="J168" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
+      <c r="A169" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
+      <c r="F169" s="6" t="s">
+        <v>337</v>
+      </c>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
+      <c r="J169" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
+      <c r="A170" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
+      <c r="F170" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
+      <c r="J170" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
+      <c r="A171" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
+      <c r="F171" s="6" t="s">
+        <v>340</v>
+      </c>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-    </row>
-    <row r="172" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="J171" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>321</v>
@@ -8187,209 +8164,210 @@
       </c>
       <c r="E172" s="6"/>
       <c r="F172" s="6" t="s">
-        <v>54</v>
+        <v>342</v>
       </c>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="6" t="s">
-        <v>354</v>
-      </c>
+      <c r="I172" s="6"/>
       <c r="J172" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
+      <c r="A173" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
+      <c r="J173" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
+      <c r="A174" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
+      <c r="F174" s="6" t="s">
+        <v>346</v>
+      </c>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
+      <c r="J174" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
+      <c r="A175" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
+      <c r="F175" s="6" t="s">
+        <v>348</v>
+      </c>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
       <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
+      <c r="J175" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
+      <c r="A176" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
+      <c r="F176" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
       <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
+      <c r="J176" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
+      <c r="F177" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
+      <c r="I177" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="J177" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C178" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="6" t="s">
-        <v>356</v>
-      </c>
+      <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
-      <c r="J178" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A179" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C179" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D179" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J178" s="6"/>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A180" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C180" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D180" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A180" s="6"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="6" t="s">
-        <v>360</v>
-      </c>
+      <c r="F180" s="6"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
       <c r="I180" s="6"/>
-      <c r="J180" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J180" s="6"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A181" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C181" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D181" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A181" s="6"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="6" t="s">
-        <v>362</v>
-      </c>
+      <c r="F181" s="6"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
       <c r="I181" s="6"/>
-      <c r="J181" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D182" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F182" s="6" t="s">
-        <v>364</v>
-      </c>
+      <c r="J181" s="6"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" s="6"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="6"/>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="J182" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
+      <c r="I182" s="6"/>
+      <c r="J182" s="6"/>
+    </row>
+    <row r="183" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
+      <c r="F183" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
+      <c r="I183" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
@@ -8440,32 +8418,20 @@
       <c r="J187" s="6"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A188" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C188" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="6" t="s">
-        <v>368</v>
-      </c>
+      <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
-      <c r="J188" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J188" s="6"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>321</v>
@@ -8474,11 +8440,11 @@
         <v>11</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
@@ -8489,7 +8455,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>321</v>
@@ -8498,24 +8464,22 @@
         <v>11</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I190" s="6"/>
       <c r="J190" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>321</v>
@@ -8524,11 +8488,11 @@
         <v>11</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
@@ -8539,7 +8503,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>321</v>
@@ -8548,11 +8512,11 @@
         <v>11</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>367</v>
+        <v>37</v>
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8561,9 +8525,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>321</v>
@@ -8572,142 +8536,83 @@
         <v>11</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E193" s="6"/>
+        <v>37</v>
+      </c>
       <c r="F193" s="6" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
+      <c r="I193" s="6" t="s">
+        <v>365</v>
+      </c>
       <c r="J193" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>367</v>
-      </c>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" s="6"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="6" t="s">
-        <v>379</v>
-      </c>
+      <c r="F194" s="6"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
       <c r="I194" s="6"/>
-      <c r="J194" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D195" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="J194" s="6"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="6" t="s">
-        <v>381</v>
-      </c>
+      <c r="F195" s="6"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
       <c r="I195" s="6"/>
-      <c r="J195" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J195" s="6"/>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A196" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C196" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D196" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="6" t="s">
-        <v>91</v>
-      </c>
+      <c r="F196" s="6"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
-      <c r="J196" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J196" s="6"/>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A197" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="F197" s="6"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
       <c r="I197" s="6"/>
-      <c r="J197" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J197" s="6"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A198" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C198" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="6" t="s">
-        <v>99</v>
-      </c>
+      <c r="F198" s="6"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
       <c r="I198" s="6"/>
-      <c r="J198" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J198" s="6"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>321</v>
@@ -8720,7 +8625,7 @@
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>97</v>
+        <v>368</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8731,7 +8636,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>321</v>
@@ -8744,7 +8649,7 @@
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>387</v>
+        <v>348</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8755,7 +8660,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>321</v>
@@ -8768,18 +8673,20 @@
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>93</v>
+        <v>371</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
+      <c r="I201" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J201" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>321</v>
@@ -8792,7 +8699,7 @@
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8803,7 +8710,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>321</v>
@@ -8816,7 +8723,7 @@
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8825,9 +8732,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>321</v>
@@ -8840,7 +8747,7 @@
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8849,9 +8756,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>321</v>
@@ -8864,7 +8771,7 @@
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8873,9 +8780,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>321</v>
@@ -8888,7 +8795,7 @@
       </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
@@ -8899,42 +8806,44 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D207" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>400</v>
+        <v>91</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="6" t="s">
-        <v>401</v>
-      </c>
+      <c r="I207" s="6"/>
       <c r="J207" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D208" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>403</v>
+        <v>89</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
@@ -8945,18 +8854,20 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D209" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>405</v>
+        <v>99</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8967,18 +8878,20 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D210" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>408</v>
+        <v>97</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -8987,20 +8900,22 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D211" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -9011,18 +8926,20 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D212" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
@@ -9031,128 +8948,219 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D213" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E213" s="6"/>
       <c r="F213" s="6" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="6" t="s">
-        <v>415</v>
-      </c>
+      <c r="I213" s="6"/>
       <c r="J213" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
+      <c r="A214" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
+      <c r="F214" s="6" t="s">
+        <v>392</v>
+      </c>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
       <c r="I214" s="6"/>
-      <c r="J214" s="6"/>
+      <c r="J214" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
+      <c r="A215" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
+      <c r="F215" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
       <c r="I215" s="6"/>
-      <c r="J215" s="6"/>
+      <c r="J215" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
+      <c r="A216" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
+      <c r="F216" s="6" t="s">
+        <v>395</v>
+      </c>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
       <c r="I216" s="6"/>
-      <c r="J216" s="6"/>
+      <c r="J216" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
+      <c r="A217" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
+      <c r="F217" s="6" t="s">
+        <v>397</v>
+      </c>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
       <c r="I217" s="6"/>
-      <c r="J217" s="6"/>
+      <c r="J217" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="6"/>
+      <c r="A218" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
+      <c r="F218" s="6" t="s">
+        <v>400</v>
+      </c>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
-      <c r="J218" s="6"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="6"/>
+      <c r="I218" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J218" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A219" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
+      <c r="F219" s="6" t="s">
+        <v>403</v>
+      </c>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
       <c r="I219" s="6"/>
-      <c r="J219" s="6"/>
+      <c r="J219" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="6"/>
+      <c r="A220" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
+      <c r="F220" s="6" t="s">
+        <v>405</v>
+      </c>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
       <c r="I220" s="6"/>
-      <c r="J220" s="6"/>
+      <c r="J220" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="6"/>
+      <c r="A221" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
+      <c r="F221" s="6" t="s">
+        <v>408</v>
+      </c>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
-      <c r="J221" s="6"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J221" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>321</v>
@@ -9163,7 +9171,7 @@
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
@@ -9174,7 +9182,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>321</v>
@@ -9185,7 +9193,7 @@
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9194,9 +9202,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>321</v>
@@ -9205,209 +9213,128 @@
         <v>407</v>
       </c>
       <c r="D224" s="6"/>
-      <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
-      <c r="I224" s="6"/>
+      <c r="I224" s="6" t="s">
+        <v>415</v>
+      </c>
       <c r="J224" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A225" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A225" s="6"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="6"/>
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
-      <c r="F225" s="6" t="s">
-        <v>423</v>
-      </c>
+      <c r="F225" s="6"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
       <c r="I225" s="6"/>
-      <c r="J225" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J225" s="6"/>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A226" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A226" s="6"/>
+      <c r="B226" s="6"/>
+      <c r="C226" s="6"/>
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
-      <c r="F226" s="6" t="s">
-        <v>425</v>
-      </c>
+      <c r="F226" s="6"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
       <c r="I226" s="6"/>
-      <c r="J226" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J226" s="6"/>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A227" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C227" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A227" s="6"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="6"/>
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
-      <c r="F227" s="6" t="s">
-        <v>427</v>
-      </c>
+      <c r="F227" s="6"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="J227" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A228" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C228" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="I227" s="6"/>
+      <c r="J227" s="6"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" s="6"/>
+      <c r="B228" s="6"/>
+      <c r="C228" s="6"/>
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
-      <c r="F228" s="6" t="s">
-        <v>429</v>
-      </c>
+      <c r="F228" s="6"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
       <c r="I228" s="6"/>
-      <c r="J228" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A229" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C229" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="J228" s="6"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" s="6"/>
+      <c r="B229" s="6"/>
+      <c r="C229" s="6"/>
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
-      <c r="F229" s="6" t="s">
-        <v>431</v>
-      </c>
+      <c r="F229" s="6"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
       <c r="I229" s="6"/>
-      <c r="J229" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A230" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C230" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="J229" s="6"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A230" s="6"/>
+      <c r="B230" s="6"/>
+      <c r="C230" s="6"/>
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
-      <c r="F230" s="6" t="s">
-        <v>433</v>
-      </c>
+      <c r="F230" s="6"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
       <c r="I230" s="6"/>
-      <c r="J230" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J230" s="6"/>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A231" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C231" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A231" s="6"/>
+      <c r="B231" s="6"/>
+      <c r="C231" s="6"/>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
-      <c r="F231" s="6" t="s">
-        <v>435</v>
-      </c>
+      <c r="F231" s="6"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
       <c r="I231" s="6"/>
-      <c r="J231" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J231" s="6"/>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A232" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A232" s="6"/>
+      <c r="B232" s="6"/>
+      <c r="C232" s="6"/>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
-      <c r="F232" s="6" t="s">
-        <v>438</v>
-      </c>
+      <c r="F232" s="6"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
       <c r="I232" s="6"/>
-      <c r="J232" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J232" s="6"/>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
@@ -9418,66 +9345,62 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
-      <c r="I234" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I234" s="6"/>
       <c r="J234" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
-      <c r="I235" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I235" s="6"/>
       <c r="J235" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
@@ -9486,20 +9409,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9510,40 +9433,42 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
-      <c r="I238" s="6"/>
+      <c r="I238" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J238" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9552,20 +9477,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
@@ -9574,57 +9499,53 @@
         <v>14</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
-      <c r="I241" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I241" s="6"/>
       <c r="J241" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
-      <c r="I242" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I242" s="6"/>
       <c r="J242" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>321</v>
@@ -9635,103 +9556,165 @@
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
-      <c r="I243" s="6" t="s">
-        <v>925</v>
-      </c>
+      <c r="I243" s="6"/>
       <c r="J243" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="6"/>
+      <c r="A244" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
+      <c r="F244" s="6" t="s">
+        <v>440</v>
+      </c>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
       <c r="I244" s="6"/>
-      <c r="J244" s="6"/>
+      <c r="J244" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="6"/>
+      <c r="A245" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
-      <c r="F245" s="6"/>
+      <c r="F245" s="6" t="s">
+        <v>442</v>
+      </c>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
-      <c r="I245" s="6"/>
-      <c r="J245" s="6"/>
+      <c r="I245" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="J245" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="6"/>
+      <c r="A246" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
-      <c r="F246" s="6"/>
+      <c r="F246" s="6" t="s">
+        <v>444</v>
+      </c>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
-      <c r="I246" s="6"/>
-      <c r="J246" s="6"/>
+      <c r="I246" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="J246" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="6"/>
+      <c r="A247" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
-      <c r="F247" s="6"/>
+      <c r="F247" s="6" t="s">
+        <v>446</v>
+      </c>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
       <c r="I247" s="6"/>
-      <c r="J247" s="6"/>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="6"/>
+      <c r="J247" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A248" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
-      <c r="F248" s="6"/>
+      <c r="F248" s="6" t="s">
+        <v>448</v>
+      </c>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
       <c r="I248" s="6"/>
-      <c r="J248" s="6"/>
+      <c r="J248" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="6"/>
+      <c r="A249" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="6"/>
+      <c r="F249" s="6" t="s">
+        <v>450</v>
+      </c>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
-      <c r="J249" s="6"/>
-    </row>
-    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J249" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
@@ -9742,18 +9725,18 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
@@ -9762,52 +9745,77 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D252" s="6"/>
+      <c r="E252" s="6"/>
       <c r="F252" s="6" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
       <c r="I252" s="6" t="s">
-        <v>468</v>
+        <v>923</v>
       </c>
       <c r="J252" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
+      <c r="A253" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
-      <c r="F253" s="6"/>
+      <c r="F253" s="6" t="s">
+        <v>458</v>
+      </c>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
-      <c r="I253" s="6"/>
-      <c r="J253" s="6"/>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="6"/>
+      <c r="I253" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="J253" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A254" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
+      <c r="F254" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
-      <c r="I254" s="6"/>
-      <c r="J254" s="6"/>
+      <c r="I254" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="J254" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
@@ -9822,129 +9830,79 @@
       <c r="J255" s="6"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A256" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C256" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="6"/>
+      <c r="C256" s="6"/>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="F256" s="6"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
-      <c r="J256" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J256" s="6"/>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A257" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A257" s="6"/>
+      <c r="B257" s="6"/>
+      <c r="C257" s="6"/>
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
-      <c r="F257" s="6" t="s">
-        <v>473</v>
-      </c>
+      <c r="F257" s="6"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
-      <c r="J257" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J257" s="6"/>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A258" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A258" s="6"/>
+      <c r="B258" s="6"/>
+      <c r="C258" s="6"/>
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
-      <c r="F258" s="6" t="s">
-        <v>475</v>
-      </c>
+      <c r="F258" s="6"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
       <c r="I258" s="6"/>
-      <c r="J258" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A259" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C259" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="J258" s="6"/>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A259" s="6"/>
+      <c r="B259" s="6"/>
+      <c r="C259" s="6"/>
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
-      <c r="F259" s="6" t="s">
-        <v>477</v>
-      </c>
+      <c r="F259" s="6"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
       <c r="I259" s="6"/>
-      <c r="J259" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A260" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C260" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="J259" s="6"/>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A260" s="6"/>
+      <c r="B260" s="6"/>
+      <c r="C260" s="6"/>
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
-      <c r="F260" s="6" t="s">
-        <v>479</v>
-      </c>
+      <c r="F260" s="6"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
       <c r="I260" s="6"/>
-      <c r="J260" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J260" s="6"/>
+    </row>
+    <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9953,20 +9911,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9975,97 +9933,68 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D263" s="6"/>
-      <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
-      <c r="I263" s="6"/>
+      <c r="I263" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="J263" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A264" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C264" s="6" t="s">
-        <v>470</v>
-      </c>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A264" s="6"/>
+      <c r="B264" s="6"/>
+      <c r="C264" s="6"/>
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
-      <c r="F264" s="6" t="s">
-        <v>487</v>
-      </c>
+      <c r="F264" s="6"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
       <c r="I264" s="6"/>
-      <c r="J264" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J264" s="6"/>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A265" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C265" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A265" s="6"/>
+      <c r="B265" s="6"/>
+      <c r="C265" s="6"/>
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
-      <c r="F265" s="6" t="s">
-        <v>489</v>
-      </c>
+      <c r="F265" s="6"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
-      <c r="J265" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J265" s="6"/>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A266" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C266" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A266" s="6"/>
+      <c r="B266" s="6"/>
+      <c r="C266" s="6"/>
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
-      <c r="F266" s="6" t="s">
-        <v>491</v>
-      </c>
+      <c r="F266" s="6"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
       <c r="I266" s="6"/>
-      <c r="J266" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J266" s="6"/>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
@@ -10076,7 +10005,7 @@
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10085,9 +10014,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
@@ -10098,7 +10027,7 @@
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10109,7 +10038,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
@@ -10120,7 +10049,7 @@
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10129,20 +10058,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10151,20 +10080,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10175,18 +10104,18 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10195,20 +10124,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10217,20 +10146,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10239,20 +10168,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
@@ -10263,18 +10192,18 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>108</v>
+        <v>489</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10285,18 +10214,18 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10307,18 +10236,18 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10327,20 +10256,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10351,18 +10280,18 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10373,18 +10302,18 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
@@ -10393,55 +10322,64 @@
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="D282" s="6"/>
+      <c r="E282" s="6"/>
       <c r="F282" s="6" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="6" t="s">
-        <v>526</v>
-      </c>
+      <c r="I282" s="6"/>
       <c r="J282" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A283" s="6"/>
-      <c r="B283" s="6"/>
-      <c r="C283" s="6"/>
+      <c r="A283" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>499</v>
+      </c>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="6"/>
+      <c r="F283" s="6" t="s">
+        <v>504</v>
+      </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
-      <c r="J283" s="6"/>
-    </row>
-    <row r="284" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J283" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
       <c r="F284" s="6" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
@@ -10452,18 +10390,18 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10474,18 +10412,18 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10496,18 +10434,18 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>535</v>
+        <v>108</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10518,18 +10456,18 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10540,18 +10478,18 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10562,18 +10500,18 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10584,18 +10522,18 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10604,20 +10542,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>534</v>
+        <v>506</v>
       </c>
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10626,64 +10564,55 @@
         <v>14</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D293" s="6"/>
-      <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
-      <c r="I293" s="6"/>
+      <c r="I293" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="J293" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A294" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C294" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A294" s="6"/>
+      <c r="B294" s="6"/>
+      <c r="C294" s="6"/>
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
-      <c r="F294" s="6" t="s">
-        <v>549</v>
-      </c>
+      <c r="F294" s="6"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
       <c r="I294" s="6"/>
-      <c r="J294" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J294" s="6"/>
+    </row>
+    <row r="295" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
@@ -10692,92 +10621,141 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D296" s="6"/>
+      <c r="E296" s="6"/>
       <c r="F296" s="6" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="6" t="s">
-        <v>554</v>
-      </c>
+      <c r="I296" s="6"/>
       <c r="J296" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A297" s="6"/>
-      <c r="B297" s="6"/>
-      <c r="C297" s="6"/>
+      <c r="A297" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D297" s="6"/>
       <c r="E297" s="6"/>
-      <c r="F297" s="6"/>
+      <c r="F297" s="6" t="s">
+        <v>532</v>
+      </c>
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
       <c r="I297" s="6"/>
-      <c r="J297" s="6"/>
+      <c r="J297" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A298" s="6"/>
-      <c r="B298" s="6"/>
-      <c r="C298" s="6"/>
+      <c r="A298" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D298" s="6"/>
       <c r="E298" s="6"/>
-      <c r="F298" s="6"/>
+      <c r="F298" s="6" t="s">
+        <v>535</v>
+      </c>
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
       <c r="I298" s="6"/>
-      <c r="J298" s="6"/>
+      <c r="J298" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A299" s="6"/>
-      <c r="B299" s="6"/>
-      <c r="C299" s="6"/>
+      <c r="A299" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D299" s="6"/>
       <c r="E299" s="6"/>
-      <c r="F299" s="6"/>
+      <c r="F299" s="6" t="s">
+        <v>537</v>
+      </c>
       <c r="G299" s="6"/>
       <c r="H299" s="6"/>
       <c r="I299" s="6"/>
-      <c r="J299" s="6"/>
+      <c r="J299" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A300" s="6"/>
-      <c r="B300" s="6"/>
-      <c r="C300" s="6"/>
+      <c r="A300" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D300" s="6"/>
       <c r="E300" s="6"/>
-      <c r="F300" s="6"/>
+      <c r="F300" s="6" t="s">
+        <v>539</v>
+      </c>
       <c r="G300" s="6"/>
       <c r="H300" s="6"/>
       <c r="I300" s="6"/>
-      <c r="J300" s="6"/>
+      <c r="J300" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A301" s="6"/>
-      <c r="B301" s="6"/>
-      <c r="C301" s="6"/>
+      <c r="A301" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D301" s="6"/>
       <c r="E301" s="6"/>
-      <c r="F301" s="6"/>
+      <c r="F301" s="6" t="s">
+        <v>541</v>
+      </c>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
       <c r="I301" s="6"/>
-      <c r="J301" s="6"/>
-    </row>
-    <row r="302" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="J301" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="6" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="B302" s="6" t="s">
         <v>321</v>
@@ -10788,76 +10766,125 @@
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
       <c r="F302" s="6" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
-      <c r="I302" s="6" t="s">
-        <v>557</v>
-      </c>
+      <c r="I302" s="6"/>
       <c r="J302" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A303" s="6"/>
-      <c r="B303" s="6"/>
-      <c r="C303" s="6"/>
+    <row r="303" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A303" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D303" s="6"/>
       <c r="E303" s="6"/>
-      <c r="F303" s="6"/>
+      <c r="F303" s="6" t="s">
+        <v>545</v>
+      </c>
       <c r="G303" s="6"/>
       <c r="H303" s="6"/>
       <c r="I303" s="6"/>
-      <c r="J303" s="6"/>
+      <c r="J303" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A304" s="6"/>
-      <c r="B304" s="6"/>
-      <c r="C304" s="6"/>
+      <c r="A304" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D304" s="6"/>
       <c r="E304" s="6"/>
-      <c r="F304" s="6"/>
+      <c r="F304" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="G304" s="6"/>
       <c r="H304" s="6"/>
       <c r="I304" s="6"/>
-      <c r="J304" s="6"/>
+      <c r="J304" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A305" s="6"/>
-      <c r="B305" s="6"/>
-      <c r="C305" s="6"/>
+      <c r="A305" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D305" s="6"/>
       <c r="E305" s="6"/>
-      <c r="F305" s="6"/>
+      <c r="F305" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="G305" s="6"/>
       <c r="H305" s="6"/>
       <c r="I305" s="6"/>
-      <c r="J305" s="6"/>
+      <c r="J305" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A306" s="6"/>
-      <c r="B306" s="6"/>
-      <c r="C306" s="6"/>
+      <c r="A306" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D306" s="6"/>
       <c r="E306" s="6"/>
-      <c r="F306" s="6"/>
+      <c r="F306" s="6" t="s">
+        <v>551</v>
+      </c>
       <c r="G306" s="6"/>
       <c r="H306" s="6"/>
       <c r="I306" s="6"/>
-      <c r="J306" s="6"/>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A307" s="6"/>
-      <c r="B307" s="6"/>
-      <c r="C307" s="6"/>
+      <c r="J306" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A307" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D307" s="6"/>
-      <c r="E307" s="6"/>
-      <c r="F307" s="6"/>
+      <c r="F307" s="6" t="s">
+        <v>553</v>
+      </c>
       <c r="G307" s="6"/>
       <c r="H307" s="6"/>
-      <c r="I307" s="6"/>
-      <c r="J307" s="6"/>
+      <c r="I307" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="J307" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
@@ -10919,17 +10946,29 @@
       <c r="I312" s="6"/>
       <c r="J312" s="6"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A313" s="6"/>
-      <c r="B313" s="6"/>
-      <c r="C313" s="6"/>
+    <row r="313" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A313" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D313" s="6"/>
       <c r="E313" s="6"/>
-      <c r="F313" s="6"/>
+      <c r="F313" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="G313" s="6"/>
       <c r="H313" s="6"/>
-      <c r="I313" s="6"/>
-      <c r="J313" s="6"/>
+      <c r="I313" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J313" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
@@ -11124,261 +11163,151 @@
       <c r="J329" s="6"/>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A330" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C330" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A330" s="6"/>
+      <c r="B330" s="6"/>
+      <c r="C330" s="6"/>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
-      <c r="F330" s="6" t="s">
-        <v>559</v>
-      </c>
+      <c r="F330" s="6"/>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
       <c r="I330" s="6"/>
-      <c r="J330" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A331" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="B331" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C331" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="J330" s="6"/>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A331" s="6"/>
+      <c r="B331" s="6"/>
+      <c r="C331" s="6"/>
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
-      <c r="F331" s="6" t="s">
-        <v>255</v>
-      </c>
+      <c r="F331" s="6"/>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
       <c r="I331" s="6"/>
-      <c r="J331" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J331" s="6"/>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A332" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="B332" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C332" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A332" s="6"/>
+      <c r="B332" s="6"/>
+      <c r="C332" s="6"/>
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
-      <c r="F332" s="6" t="s">
-        <v>562</v>
-      </c>
+      <c r="F332" s="6"/>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
       <c r="I332" s="6"/>
-      <c r="J332" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J332" s="6"/>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A333" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="B333" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C333" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A333" s="6"/>
+      <c r="B333" s="6"/>
+      <c r="C333" s="6"/>
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
-      <c r="F333" s="6" t="s">
-        <v>564</v>
-      </c>
+      <c r="F333" s="6"/>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
       <c r="I333" s="6"/>
-      <c r="J333" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J333" s="6"/>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A334" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="B334" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C334" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A334" s="6"/>
+      <c r="B334" s="6"/>
+      <c r="C334" s="6"/>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
-      <c r="F334" s="6" t="s">
-        <v>566</v>
-      </c>
+      <c r="F334" s="6"/>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
       <c r="I334" s="6"/>
-      <c r="J334" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J334" s="6"/>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A335" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="B335" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C335" s="6" t="s">
-        <v>568</v>
-      </c>
+      <c r="A335" s="6"/>
+      <c r="B335" s="6"/>
+      <c r="C335" s="6"/>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
-      <c r="F335" s="6" t="s">
-        <v>569</v>
-      </c>
+      <c r="F335" s="6"/>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
       <c r="I335" s="6"/>
-      <c r="J335" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J335" s="6"/>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A336" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="B336" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C336" s="6" t="s">
-        <v>568</v>
-      </c>
+      <c r="A336" s="6"/>
+      <c r="B336" s="6"/>
+      <c r="C336" s="6"/>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
-      <c r="F336" s="6" t="s">
-        <v>571</v>
-      </c>
+      <c r="F336" s="6"/>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
       <c r="I336" s="6"/>
-      <c r="J336" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J336" s="6"/>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A337" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="B337" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C337" s="6" t="s">
-        <v>573</v>
-      </c>
+      <c r="A337" s="6"/>
+      <c r="B337" s="6"/>
+      <c r="C337" s="6"/>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
-      <c r="F337" s="6" t="s">
-        <v>574</v>
-      </c>
+      <c r="F337" s="6"/>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
       <c r="I337" s="6"/>
-      <c r="J337" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J337" s="6"/>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A338" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C338" s="6" t="s">
-        <v>573</v>
-      </c>
+      <c r="A338" s="6"/>
+      <c r="B338" s="6"/>
+      <c r="C338" s="6"/>
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
-      <c r="F338" s="6" t="s">
-        <v>576</v>
-      </c>
+      <c r="F338" s="6"/>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
       <c r="I338" s="6"/>
-      <c r="J338" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J338" s="6"/>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A339" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C339" s="6" t="s">
-        <v>573</v>
-      </c>
+      <c r="A339" s="6"/>
+      <c r="B339" s="6"/>
+      <c r="C339" s="6"/>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
-      <c r="F339" s="6" t="s">
-        <v>578</v>
-      </c>
+      <c r="F339" s="6"/>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
       <c r="I339" s="6"/>
-      <c r="J339" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J339" s="6"/>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A340" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="B340" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C340" s="6" t="s">
-        <v>580</v>
-      </c>
+      <c r="A340" s="6"/>
+      <c r="B340" s="6"/>
+      <c r="C340" s="6"/>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
-      <c r="F340" s="6" t="s">
-        <v>504</v>
-      </c>
+      <c r="F340" s="6"/>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
       <c r="I340" s="6"/>
-      <c r="J340" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J340" s="6"/>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>580</v>
+        <v>534</v>
       </c>
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
       <c r="F341" s="6" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
@@ -11387,20 +11316,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>580</v>
+        <v>534</v>
       </c>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>307</v>
+        <v>255</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11411,18 +11340,18 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11433,18 +11362,18 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11455,18 +11384,18 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11477,18 +11406,18 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11497,20 +11426,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11521,18 +11450,18 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11543,18 +11472,18 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11565,18 +11494,18 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11587,18 +11516,18 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>603</v>
+        <v>504</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11609,18 +11538,18 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11631,18 +11560,18 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>607</v>
+        <v>307</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11651,20 +11580,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>608</v>
+        <v>584</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11675,18 +11604,18 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="6" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B355" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D355" s="6"/>
       <c r="E355" s="6"/>
       <c r="F355" s="6" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="G355" s="6"/>
       <c r="H355" s="6"/>
@@ -11695,34 +11624,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="356" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="9"/>
-      <c r="B356" s="9"/>
-      <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="F356" s="9"/>
-      <c r="G356" s="9"/>
-      <c r="H356" s="9"/>
-      <c r="I356" s="9"/>
-      <c r="J356" s="9"/>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A356" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D356" s="6"/>
+      <c r="E356" s="6"/>
+      <c r="F356" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="G356" s="6"/>
+      <c r="H356" s="6"/>
+      <c r="I356" s="6"/>
+      <c r="J356" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D357" s="6" t="s">
-        <v>12</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="D357" s="6"/>
       <c r="E357" s="6"/>
       <c r="F357" s="6" t="s">
-        <v>13</v>
+        <v>592</v>
       </c>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
@@ -11731,22 +11668,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D358" s="6" t="s">
-        <v>12</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="D358" s="6"/>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>18</v>
+        <v>594</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11757,20 +11692,18 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D359" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="D359" s="6"/>
       <c r="E359" s="6"/>
       <c r="F359" s="6" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
@@ -11779,108 +11712,152 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D360" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="D360" s="6"/>
       <c r="E360" s="6"/>
-      <c r="F360" s="10" t="s">
-        <v>618</v>
+      <c r="F360" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
-      <c r="I360" s="10" t="s">
-        <v>619</v>
-      </c>
+      <c r="I360" s="6"/>
       <c r="J360" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A361" s="6"/>
-      <c r="B361" s="6"/>
-      <c r="C361" s="6"/>
+      <c r="A361" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>596</v>
+      </c>
       <c r="D361" s="6"/>
       <c r="E361" s="6"/>
-      <c r="F361" s="6"/>
+      <c r="F361" s="6" t="s">
+        <v>601</v>
+      </c>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
       <c r="I361" s="6"/>
-      <c r="J361" s="6"/>
+      <c r="J361" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A362" s="6"/>
-      <c r="B362" s="6"/>
-      <c r="C362" s="6"/>
+      <c r="A362" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>596</v>
+      </c>
       <c r="D362" s="6"/>
       <c r="E362" s="6"/>
-      <c r="F362" s="6"/>
+      <c r="F362" s="6" t="s">
+        <v>603</v>
+      </c>
       <c r="G362" s="6"/>
       <c r="H362" s="6"/>
       <c r="I362" s="6"/>
-      <c r="J362" s="6"/>
+      <c r="J362" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A363" s="6"/>
-      <c r="B363" s="6"/>
-      <c r="C363" s="6"/>
+      <c r="A363" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>596</v>
+      </c>
       <c r="D363" s="6"/>
       <c r="E363" s="6"/>
-      <c r="F363" s="6"/>
+      <c r="F363" s="6" t="s">
+        <v>605</v>
+      </c>
       <c r="G363" s="6"/>
       <c r="H363" s="6"/>
       <c r="I363" s="6"/>
-      <c r="J363" s="6"/>
+      <c r="J363" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A364" s="6"/>
-      <c r="B364" s="6"/>
-      <c r="C364" s="6"/>
+      <c r="A364" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>596</v>
+      </c>
       <c r="D364" s="6"/>
       <c r="E364" s="6"/>
-      <c r="F364" s="6"/>
+      <c r="F364" s="6" t="s">
+        <v>607</v>
+      </c>
       <c r="G364" s="6"/>
       <c r="H364" s="6"/>
       <c r="I364" s="6"/>
-      <c r="J364" s="6"/>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A365" s="6"/>
-      <c r="B365" s="6"/>
-      <c r="C365" s="6"/>
+      <c r="J364" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A365" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>596</v>
+      </c>
       <c r="D365" s="6"/>
       <c r="E365" s="6"/>
-      <c r="F365" s="6"/>
+      <c r="F365" s="6" t="s">
+        <v>609</v>
+      </c>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
       <c r="I365" s="6"/>
-      <c r="J365" s="6"/>
+      <c r="J365" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>613</v>
+        <v>321</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D366" s="10" t="s">
-        <v>20</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="D366" s="6"/>
       <c r="E366" s="6"/>
       <c r="F366" s="6" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -11889,33 +11866,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A367" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="B367" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C367" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D367" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E367" s="6"/>
-      <c r="F367" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="G367" s="6"/>
-      <c r="H367" s="6"/>
-      <c r="I367" s="6"/>
-      <c r="J367" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="367" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="9"/>
+      <c r="B367" s="9"/>
+      <c r="C367" s="9"/>
+      <c r="D367" s="9"/>
+      <c r="E367" s="9"/>
+      <c r="F367" s="9"/>
+      <c r="G367" s="9"/>
+      <c r="H367" s="9"/>
+      <c r="I367" s="9"/>
+      <c r="J367" s="9"/>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B368" s="6" t="s">
         <v>613</v>
@@ -11923,12 +11888,12 @@
       <c r="C368" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D368" s="10" t="s">
-        <v>20</v>
+      <c r="D368" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>329</v>
+        <v>13</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11939,7 +11904,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B369" s="6" t="s">
         <v>613</v>
@@ -11947,12 +11912,12 @@
       <c r="C369" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D369" s="10" t="s">
-        <v>20</v>
+      <c r="D369" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>626</v>
+        <v>18</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11963,7 +11928,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="B370" s="6" t="s">
         <v>613</v>
@@ -11971,12 +11936,12 @@
       <c r="C370" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D370" s="10" t="s">
-        <v>20</v>
+      <c r="D370" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11985,9 +11950,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="B371" s="6" t="s">
         <v>613</v>
@@ -11995,143 +11960,85 @@
       <c r="C371" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D371" s="10" t="s">
-        <v>20</v>
+      <c r="D371" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="E371" s="6"/>
-      <c r="F371" s="6" t="s">
-        <v>630</v>
+      <c r="F371" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
-      <c r="I371" s="6"/>
+      <c r="I371" s="10" t="s">
+        <v>619</v>
+      </c>
       <c r="J371" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A372" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="B372" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C372" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D372" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A372" s="6"/>
+      <c r="B372" s="6"/>
+      <c r="C372" s="6"/>
+      <c r="D372" s="6"/>
       <c r="E372" s="6"/>
-      <c r="F372" s="6" t="s">
-        <v>632</v>
-      </c>
+      <c r="F372" s="6"/>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
       <c r="I372" s="6"/>
-      <c r="J372" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J372" s="6"/>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A373" s="6" t="s">
-        <v>633</v>
-      </c>
-      <c r="B373" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C373" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D373" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A373" s="6"/>
+      <c r="B373" s="6"/>
+      <c r="C373" s="6"/>
+      <c r="D373" s="6"/>
       <c r="E373" s="6"/>
-      <c r="F373" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="F373" s="6"/>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
       <c r="I373" s="6"/>
-      <c r="J373" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A374" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="B374" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C374" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D374" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="J373" s="6"/>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A374" s="6"/>
+      <c r="B374" s="6"/>
+      <c r="C374" s="6"/>
+      <c r="D374" s="6"/>
       <c r="E374" s="6"/>
-      <c r="F374" s="6" t="s">
-        <v>635</v>
-      </c>
+      <c r="F374" s="6"/>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
       <c r="I374" s="6"/>
-      <c r="J374" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J374" s="6"/>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A375" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="B375" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C375" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D375" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A375" s="6"/>
+      <c r="B375" s="6"/>
+      <c r="C375" s="6"/>
+      <c r="D375" s="6"/>
       <c r="E375" s="6"/>
-      <c r="F375" s="6" t="s">
-        <v>342</v>
-      </c>
+      <c r="F375" s="6"/>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
       <c r="I375" s="6"/>
-      <c r="J375" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J375" s="6"/>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A376" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="B376" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C376" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D376" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A376" s="6"/>
+      <c r="B376" s="6"/>
+      <c r="C376" s="6"/>
+      <c r="D376" s="6"/>
       <c r="E376" s="6"/>
-      <c r="F376" s="6" t="s">
-        <v>638</v>
-      </c>
+      <c r="F376" s="6"/>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
       <c r="I376" s="6"/>
-      <c r="J376" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J376" s="6"/>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="B377" s="6" t="s">
         <v>613</v>
@@ -12144,7 +12051,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12155,7 +12062,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="B378" s="6" t="s">
         <v>613</v>
@@ -12168,7 +12075,7 @@
       </c>
       <c r="E378" s="6"/>
       <c r="F378" s="6" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="G378" s="6"/>
       <c r="H378" s="6"/>
@@ -12177,9 +12084,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="10" t="s">
-        <v>643</v>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A379" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D379" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E379" s="6"/>
+      <c r="F379" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G379" s="6"/>
+      <c r="H379" s="6"/>
+      <c r="I379" s="6"/>
+      <c r="J379" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A380" s="6" t="s">
+        <v>625</v>
       </c>
       <c r="B380" s="6" t="s">
         <v>613</v>
@@ -12191,8 +12122,8 @@
         <v>20</v>
       </c>
       <c r="E380" s="6"/>
-      <c r="F380" s="10" t="s">
-        <v>644</v>
+      <c r="F380" s="6" t="s">
+        <v>626</v>
       </c>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
@@ -12201,9 +12132,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="6" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="B381" s="6" t="s">
         <v>613</v>
@@ -12215,57 +12146,91 @@
         <v>20</v>
       </c>
       <c r="E381" s="6"/>
-      <c r="F381" s="10" t="s">
-        <v>351</v>
+      <c r="F381" s="6" t="s">
+        <v>628</v>
       </c>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
-      <c r="I381" s="10" t="s">
-        <v>646</v>
-      </c>
+      <c r="I381" s="6"/>
       <c r="J381" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A382" s="6"/>
-      <c r="B382" s="6"/>
-      <c r="C382" s="6"/>
-      <c r="D382" s="6"/>
+      <c r="A382" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D382" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E382" s="6"/>
-      <c r="F382" s="6"/>
+      <c r="F382" s="6" t="s">
+        <v>630</v>
+      </c>
       <c r="G382" s="6"/>
       <c r="H382" s="6"/>
       <c r="I382" s="6"/>
-      <c r="J382" s="6"/>
+      <c r="J382" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A383" s="6"/>
-      <c r="B383" s="6"/>
-      <c r="C383" s="6"/>
-      <c r="D383" s="6"/>
+      <c r="A383" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D383" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E383" s="6"/>
-      <c r="F383" s="6"/>
+      <c r="F383" s="6" t="s">
+        <v>632</v>
+      </c>
       <c r="G383" s="6"/>
       <c r="H383" s="6"/>
       <c r="I383" s="6"/>
-      <c r="J383" s="6"/>
+      <c r="J383" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A384" s="6"/>
-      <c r="B384" s="6"/>
-      <c r="C384" s="6"/>
-      <c r="D384" s="6"/>
+      <c r="A384" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D384" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E384" s="6"/>
-      <c r="F384" s="6"/>
+      <c r="F384" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
       <c r="I384" s="6"/>
-      <c r="J384" s="6"/>
-    </row>
-    <row r="385" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="J384" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A385" s="6" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="B385" s="6" t="s">
         <v>613</v>
@@ -12273,131 +12238,177 @@
       <c r="C385" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D385" s="6" t="s">
+      <c r="D385" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E385" s="6"/>
-      <c r="F385" s="10" t="s">
-        <v>54</v>
+      <c r="F385" s="6" t="s">
+        <v>635</v>
       </c>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
-      <c r="I385" s="10" t="s">
-        <v>648</v>
-      </c>
+      <c r="I385" s="6"/>
       <c r="J385" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A386" s="6"/>
-      <c r="B386" s="6"/>
-      <c r="C386" s="6"/>
-      <c r="D386" s="6"/>
+      <c r="A386" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D386" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E386" s="6"/>
-      <c r="F386" s="6"/>
+      <c r="F386" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="G386" s="6"/>
       <c r="H386" s="6"/>
       <c r="I386" s="6"/>
-      <c r="J386" s="6"/>
+      <c r="J386" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A387" s="6"/>
-      <c r="B387" s="6"/>
-      <c r="C387" s="6"/>
-      <c r="D387" s="6"/>
+      <c r="A387" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D387" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E387" s="6"/>
-      <c r="F387" s="6"/>
+      <c r="F387" s="6" t="s">
+        <v>638</v>
+      </c>
       <c r="G387" s="6"/>
       <c r="H387" s="6"/>
       <c r="I387" s="6"/>
-      <c r="J387" s="6"/>
+      <c r="J387" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A388" s="6"/>
-      <c r="B388" s="6"/>
-      <c r="C388" s="6"/>
-      <c r="D388" s="6"/>
+      <c r="A388" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D388" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E388" s="6"/>
-      <c r="F388" s="6"/>
+      <c r="F388" s="6" t="s">
+        <v>640</v>
+      </c>
       <c r="G388" s="6"/>
       <c r="H388" s="6"/>
       <c r="I388" s="6"/>
-      <c r="J388" s="6"/>
+      <c r="J388" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A389" s="6"/>
-      <c r="B389" s="6"/>
-      <c r="C389" s="6"/>
-      <c r="D389" s="6"/>
+      <c r="A389" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D389" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E389" s="6"/>
-      <c r="F389" s="6"/>
+      <c r="F389" s="6" t="s">
+        <v>642</v>
+      </c>
       <c r="G389" s="6"/>
       <c r="H389" s="6"/>
       <c r="I389" s="6"/>
-      <c r="J389" s="6"/>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A390" s="6"/>
-      <c r="B390" s="6"/>
-      <c r="C390" s="6"/>
-      <c r="D390" s="6"/>
-      <c r="E390" s="6"/>
-      <c r="F390" s="6"/>
-      <c r="G390" s="6"/>
-      <c r="H390" s="6"/>
-      <c r="I390" s="6"/>
-      <c r="J390" s="6"/>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A391" s="6"/>
-      <c r="B391" s="6"/>
-      <c r="C391" s="6"/>
-      <c r="D391" s="6"/>
+      <c r="J389" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D391" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E391" s="6"/>
-      <c r="F391" s="6"/>
+      <c r="F391" s="10" t="s">
+        <v>644</v>
+      </c>
       <c r="G391" s="6"/>
       <c r="H391" s="6"/>
       <c r="I391" s="6"/>
-      <c r="J391" s="6"/>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A392" s="6"/>
-      <c r="B392" s="6"/>
-      <c r="C392" s="6"/>
-      <c r="D392" s="6"/>
+      <c r="J391" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A392" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D392" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E392" s="6"/>
-      <c r="F392" s="6"/>
+      <c r="F392" s="10" t="s">
+        <v>351</v>
+      </c>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
-      <c r="I392" s="6"/>
-      <c r="J392" s="6"/>
-    </row>
-    <row r="393" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A393" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B393" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C393" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D393" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="I392" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J392" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A393" s="6"/>
+      <c r="B393" s="6"/>
+      <c r="C393" s="6"/>
+      <c r="D393" s="6"/>
       <c r="E393" s="6"/>
-      <c r="F393" s="6" t="s">
-        <v>651</v>
-      </c>
+      <c r="F393" s="6"/>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
-      <c r="I393" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="J393" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I393" s="6"/>
+      <c r="J393" s="6"/>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
@@ -12423,17 +12434,31 @@
       <c r="I395" s="6"/>
       <c r="J395" s="6"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A396" s="6"/>
-      <c r="B396" s="6"/>
-      <c r="C396" s="6"/>
-      <c r="D396" s="6"/>
+    <row r="396" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A396" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E396" s="6"/>
-      <c r="F396" s="6"/>
+      <c r="F396" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G396" s="6"/>
       <c r="H396" s="6"/>
-      <c r="I396" s="6"/>
-      <c r="J396" s="6"/>
+      <c r="I396" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="J396" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="6"/>
@@ -12460,130 +12485,68 @@
       <c r="J398" s="6"/>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A399" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B399" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C399" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D399" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A399" s="6"/>
+      <c r="B399" s="6"/>
+      <c r="C399" s="6"/>
+      <c r="D399" s="6"/>
       <c r="E399" s="6"/>
-      <c r="F399" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="F399" s="6"/>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
       <c r="I399" s="6"/>
-      <c r="J399" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J399" s="6"/>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A400" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="B400" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C400" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D400" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A400" s="6"/>
+      <c r="B400" s="6"/>
+      <c r="C400" s="6"/>
+      <c r="D400" s="6"/>
       <c r="E400" s="6"/>
-      <c r="F400" s="6" t="s">
-        <v>655</v>
-      </c>
+      <c r="F400" s="6"/>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
       <c r="I400" s="6"/>
-      <c r="J400" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A401" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="B401" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C401" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D401" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="J400" s="6"/>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A401" s="6"/>
+      <c r="B401" s="6"/>
+      <c r="C401" s="6"/>
+      <c r="D401" s="6"/>
       <c r="E401" s="6"/>
-      <c r="F401" s="6" t="s">
-        <v>657</v>
-      </c>
+      <c r="F401" s="6"/>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
       <c r="I401" s="6"/>
-      <c r="J401" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J401" s="6"/>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A402" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="B402" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C402" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D402" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A402" s="6"/>
+      <c r="B402" s="6"/>
+      <c r="C402" s="6"/>
+      <c r="D402" s="6"/>
       <c r="E402" s="6"/>
-      <c r="F402" s="6" t="s">
-        <v>659</v>
-      </c>
+      <c r="F402" s="6"/>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
       <c r="I402" s="6"/>
-      <c r="J402" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J402" s="6"/>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A403" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="B403" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C403" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D403" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A403" s="6"/>
+      <c r="B403" s="6"/>
+      <c r="C403" s="6"/>
+      <c r="D403" s="6"/>
       <c r="E403" s="6"/>
-      <c r="F403" s="6" t="s">
-        <v>661</v>
-      </c>
+      <c r="F403" s="6"/>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
-      <c r="I403" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="J403" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I403" s="6"/>
+      <c r="J403" s="6"/>
+    </row>
+    <row r="404" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="B404" s="6" t="s">
         <v>613</v>
@@ -12596,138 +12559,80 @@
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
-      <c r="I404" s="6"/>
+      <c r="I404" s="10" t="s">
+        <v>652</v>
+      </c>
       <c r="J404" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A405" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="B405" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C405" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D405" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A405" s="6"/>
+      <c r="B405" s="6"/>
+      <c r="C405" s="6"/>
+      <c r="D405" s="6"/>
       <c r="E405" s="6"/>
-      <c r="F405" s="6" t="s">
-        <v>665</v>
-      </c>
+      <c r="F405" s="6"/>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
       <c r="I405" s="6"/>
-      <c r="J405" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A406" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="B406" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C406" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D406" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="J405" s="6"/>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A406" s="6"/>
+      <c r="B406" s="6"/>
+      <c r="C406" s="6"/>
+      <c r="D406" s="6"/>
       <c r="E406" s="6"/>
-      <c r="F406" s="6" t="s">
-        <v>667</v>
-      </c>
+      <c r="F406" s="6"/>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
       <c r="I406" s="6"/>
-      <c r="J406" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J406" s="6"/>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A407" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="B407" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C407" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D407" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A407" s="6"/>
+      <c r="B407" s="6"/>
+      <c r="C407" s="6"/>
+      <c r="D407" s="6"/>
       <c r="E407" s="6"/>
-      <c r="F407" s="6" t="s">
-        <v>669</v>
-      </c>
+      <c r="F407" s="6"/>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
       <c r="I407" s="6"/>
-      <c r="J407" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J407" s="6"/>
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A408" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="B408" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C408" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D408" s="6" t="s">
-        <v>671</v>
-      </c>
+      <c r="A408" s="6"/>
+      <c r="B408" s="6"/>
+      <c r="C408" s="6"/>
+      <c r="D408" s="6"/>
       <c r="E408" s="6"/>
-      <c r="F408" s="6" t="s">
-        <v>672</v>
-      </c>
+      <c r="F408" s="6"/>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
       <c r="I408" s="6"/>
-      <c r="J408" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J408" s="6"/>
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A409" s="6" t="s">
-        <v>673</v>
-      </c>
-      <c r="B409" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C409" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D409" s="6" t="s">
-        <v>671</v>
-      </c>
+      <c r="A409" s="6"/>
+      <c r="B409" s="6"/>
+      <c r="C409" s="6"/>
+      <c r="D409" s="6"/>
       <c r="E409" s="6"/>
-      <c r="F409" s="6" t="s">
-        <v>97</v>
-      </c>
+      <c r="F409" s="6"/>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
       <c r="I409" s="6"/>
-      <c r="J409" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J409" s="6"/>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="B410" s="6" t="s">
         <v>613</v>
@@ -12736,11 +12641,11 @@
         <v>11</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E410" s="6"/>
       <c r="F410" s="6" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12751,7 +12656,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="B411" s="6" t="s">
         <v>613</v>
@@ -12760,11 +12665,11 @@
         <v>11</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E411" s="6"/>
-      <c r="F411" s="10" t="s">
-        <v>676</v>
+      <c r="F411" s="6" t="s">
+        <v>655</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12773,9 +12678,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="B412" s="6" t="s">
         <v>613</v>
@@ -12784,11 +12689,11 @@
         <v>11</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="6" t="s">
-        <v>89</v>
+        <v>657</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12799,7 +12704,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>613</v>
@@ -12808,11 +12713,11 @@
         <v>11</v>
       </c>
       <c r="D413" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E413" s="6"/>
       <c r="F413" s="6" t="s">
-        <v>91</v>
+        <v>659</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12823,7 +12728,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>679</v>
+        <v>660</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>613</v>
@@ -12832,22 +12737,24 @@
         <v>11</v>
       </c>
       <c r="D414" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E414" s="6"/>
-      <c r="F414" s="10" t="s">
-        <v>680</v>
+      <c r="F414" s="6" t="s">
+        <v>661</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
-      <c r="I414" s="6"/>
+      <c r="I414" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J414" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="B415" s="6" t="s">
         <v>613</v>
@@ -12856,11 +12763,11 @@
         <v>11</v>
       </c>
       <c r="D415" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E415" s="6"/>
       <c r="F415" s="6" t="s">
-        <v>93</v>
+        <v>663</v>
       </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
@@ -12870,67 +12777,117 @@
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A416" s="6"/>
-      <c r="B416" s="6"/>
-      <c r="C416" s="6"/>
-      <c r="D416" s="6"/>
+      <c r="A416" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D416" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E416" s="6"/>
-      <c r="F416" s="6"/>
+      <c r="F416" s="6" t="s">
+        <v>665</v>
+      </c>
       <c r="G416" s="6"/>
       <c r="H416" s="6"/>
       <c r="I416" s="6"/>
-      <c r="J416" s="6"/>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A417" s="6"/>
-      <c r="B417" s="6"/>
-      <c r="C417" s="6"/>
-      <c r="D417" s="6"/>
+      <c r="J416" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A417" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="B417" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C417" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D417" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E417" s="6"/>
-      <c r="F417" s="6"/>
+      <c r="F417" s="6" t="s">
+        <v>667</v>
+      </c>
       <c r="G417" s="6"/>
       <c r="H417" s="6"/>
       <c r="I417" s="6"/>
-      <c r="J417" s="6"/>
+      <c r="J417" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A418" s="6"/>
-      <c r="B418" s="6"/>
-      <c r="C418" s="6"/>
-      <c r="D418" s="6"/>
+      <c r="A418" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C418" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D418" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E418" s="6"/>
-      <c r="F418" s="6"/>
+      <c r="F418" s="6" t="s">
+        <v>669</v>
+      </c>
       <c r="G418" s="6"/>
       <c r="H418" s="6"/>
       <c r="I418" s="6"/>
-      <c r="J418" s="6"/>
+      <c r="J418" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A419" s="6"/>
-      <c r="B419" s="6"/>
-      <c r="C419" s="6"/>
-      <c r="D419" s="6"/>
+      <c r="A419" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="B419" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C419" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D419" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E419" s="6"/>
-      <c r="F419" s="6"/>
+      <c r="F419" s="6" t="s">
+        <v>672</v>
+      </c>
       <c r="G419" s="6"/>
       <c r="H419" s="6"/>
       <c r="I419" s="6"/>
-      <c r="J419" s="6"/>
+      <c r="J419" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="B420" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C420" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D420" s="6"/>
+      <c r="C420" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D420" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
@@ -12941,18 +12898,20 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B421" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C421" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D421" s="6"/>
+      <c r="C421" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>684</v>
+        <v>99</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12963,18 +12922,20 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="B422" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C422" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D422" s="6"/>
+      <c r="C422" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D422" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E422" s="6"/>
-      <c r="F422" s="6" t="s">
-        <v>686</v>
+      <c r="F422" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12985,18 +12946,20 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="B423" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C423" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D423" s="6"/>
+      <c r="C423" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D423" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>688</v>
+        <v>89</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -13007,18 +12970,20 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="B424" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C424" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D424" s="6"/>
+      <c r="C424" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D424" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>690</v>
+        <v>91</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13029,18 +12994,20 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B425" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C425" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D425" s="6"/>
+      <c r="C425" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D425" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E425" s="6"/>
-      <c r="F425" s="6" t="s">
-        <v>692</v>
+      <c r="F425" s="10" t="s">
+        <v>680</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13051,18 +13018,20 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="B426" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>585</v>
-      </c>
-      <c r="D426" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D426" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>694</v>
+        <v>93</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13072,111 +13041,67 @@
       </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A427" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="B427" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C427" s="6" t="s">
-        <v>585</v>
-      </c>
+      <c r="A427" s="6"/>
+      <c r="B427" s="6"/>
+      <c r="C427" s="6"/>
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
-      <c r="F427" s="6" t="s">
-        <v>696</v>
-      </c>
+      <c r="F427" s="6"/>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
       <c r="I427" s="6"/>
-      <c r="J427" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A428" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="B428" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C428" s="6" t="s">
-        <v>585</v>
-      </c>
+      <c r="J427" s="6"/>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A428" s="6"/>
+      <c r="B428" s="6"/>
+      <c r="C428" s="6"/>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
-      <c r="F428" s="6" t="s">
-        <v>698</v>
-      </c>
+      <c r="F428" s="6"/>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
       <c r="I428" s="6"/>
-      <c r="J428" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J428" s="6"/>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A429" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="B429" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C429" s="10" t="s">
-        <v>700</v>
-      </c>
+      <c r="A429" s="6"/>
+      <c r="B429" s="6"/>
+      <c r="C429" s="6"/>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
-      <c r="F429" s="6" t="s">
-        <v>701</v>
-      </c>
+      <c r="F429" s="6"/>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
-      <c r="I429" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="J429" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I429" s="6"/>
+      <c r="J429" s="6"/>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A430" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="B430" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C430" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A430" s="6"/>
+      <c r="B430" s="6"/>
+      <c r="C430" s="6"/>
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
-      <c r="F430" s="6" t="s">
-        <v>703</v>
-      </c>
+      <c r="F430" s="6"/>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
-      <c r="I430" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="J430" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I430" s="6"/>
+      <c r="J430" s="6"/>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>704</v>
+        <v>682</v>
       </c>
       <c r="B431" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C431" s="6" t="s">
-        <v>437</v>
+      <c r="C431" s="10" t="s">
+        <v>399</v>
       </c>
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>412</v>
+        <v>194</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
@@ -13185,104 +13110,152 @@
         <v>14</v>
       </c>
     </row>
-    <row r="432" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="B432" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C432" s="6" t="s">
-        <v>437</v>
+      <c r="C432" s="10" t="s">
+        <v>399</v>
       </c>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>460</v>
+        <v>684</v>
       </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
-      <c r="I432" s="10" t="s">
-        <v>926</v>
-      </c>
+      <c r="I432" s="6"/>
       <c r="J432" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A433" s="6"/>
-      <c r="B433" s="6"/>
-      <c r="C433" s="6"/>
+      <c r="A433" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C433" s="10" t="s">
+        <v>399</v>
+      </c>
       <c r="D433" s="6"/>
       <c r="E433" s="6"/>
-      <c r="F433" s="6"/>
+      <c r="F433" s="6" t="s">
+        <v>686</v>
+      </c>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
       <c r="I433" s="6"/>
-      <c r="J433" s="6"/>
+      <c r="J433" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A434" s="6"/>
-      <c r="B434" s="6"/>
-      <c r="C434" s="6"/>
+      <c r="A434" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C434" s="10" t="s">
+        <v>399</v>
+      </c>
       <c r="D434" s="6"/>
       <c r="E434" s="6"/>
-      <c r="F434" s="6"/>
+      <c r="F434" s="6" t="s">
+        <v>688</v>
+      </c>
       <c r="G434" s="6"/>
       <c r="H434" s="6"/>
       <c r="I434" s="6"/>
-      <c r="J434" s="6"/>
+      <c r="J434" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A435" s="6"/>
-      <c r="B435" s="6"/>
-      <c r="C435" s="6"/>
+      <c r="A435" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="B435" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C435" s="10" t="s">
+        <v>399</v>
+      </c>
       <c r="D435" s="6"/>
       <c r="E435" s="6"/>
-      <c r="F435" s="6"/>
+      <c r="F435" s="6" t="s">
+        <v>690</v>
+      </c>
       <c r="G435" s="6"/>
       <c r="H435" s="6"/>
       <c r="I435" s="6"/>
-      <c r="J435" s="6"/>
+      <c r="J435" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A436" s="6"/>
-      <c r="B436" s="6"/>
-      <c r="C436" s="6"/>
+      <c r="A436" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C436" s="10" t="s">
+        <v>407</v>
+      </c>
       <c r="D436" s="6"/>
       <c r="E436" s="6"/>
-      <c r="F436" s="6"/>
+      <c r="F436" s="6" t="s">
+        <v>692</v>
+      </c>
       <c r="G436" s="6"/>
       <c r="H436" s="6"/>
       <c r="I436" s="6"/>
-      <c r="J436" s="6"/>
+      <c r="J436" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A437" s="6"/>
-      <c r="B437" s="6"/>
-      <c r="C437" s="6"/>
+      <c r="A437" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C437" s="6" t="s">
+        <v>585</v>
+      </c>
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
-      <c r="F437" s="6"/>
+      <c r="F437" s="6" t="s">
+        <v>694</v>
+      </c>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
       <c r="I437" s="6"/>
-      <c r="J437" s="6"/>
+      <c r="J437" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B438" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
@@ -13291,20 +13264,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="B439" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>437</v>
+        <v>585</v>
       </c>
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13315,29 +13288,31 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B440" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C440" s="6" t="s">
-        <v>437</v>
+      <c r="C440" s="10" t="s">
+        <v>700</v>
       </c>
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
-      <c r="I440" s="6"/>
+      <c r="I440" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J440" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="B441" s="6" t="s">
         <v>613</v>
@@ -13348,18 +13323,20 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
-      <c r="I441" s="6"/>
+      <c r="I441" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J441" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="B442" s="6" t="s">
         <v>613</v>
@@ -13370,7 +13347,7 @@
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>715</v>
+        <v>412</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13379,152 +13356,104 @@
         <v>14</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="B443" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>717</v>
+        <v>460</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
-      <c r="I443" s="6"/>
+      <c r="I443" s="10" t="s">
+        <v>926</v>
+      </c>
       <c r="J443" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A444" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="B444" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C444" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A444" s="6"/>
+      <c r="B444" s="6"/>
+      <c r="C444" s="6"/>
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
-      <c r="F444" s="6" t="s">
-        <v>719</v>
-      </c>
+      <c r="F444" s="6"/>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
       <c r="I444" s="6"/>
-      <c r="J444" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A445" s="6" t="s">
-        <v>720</v>
-      </c>
-      <c r="B445" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C445" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="J444" s="6"/>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A445" s="6"/>
+      <c r="B445" s="6"/>
+      <c r="C445" s="6"/>
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
-      <c r="F445" s="6" t="s">
-        <v>721</v>
-      </c>
+      <c r="F445" s="6"/>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
       <c r="I445" s="6"/>
-      <c r="J445" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J445" s="6"/>
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A446" s="6" t="s">
-        <v>722</v>
-      </c>
-      <c r="B446" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C446" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A446" s="6"/>
+      <c r="B446" s="6"/>
+      <c r="C446" s="6"/>
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
-      <c r="F446" s="6" t="s">
-        <v>723</v>
-      </c>
+      <c r="F446" s="6"/>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
       <c r="I446" s="6"/>
-      <c r="J446" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="447" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A447" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="B447" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C447" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="J446" s="6"/>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A447" s="6"/>
+      <c r="B447" s="6"/>
+      <c r="C447" s="6"/>
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
-      <c r="F447" s="6" t="s">
-        <v>725</v>
-      </c>
+      <c r="F447" s="6"/>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
       <c r="I447" s="6"/>
-      <c r="J447" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J447" s="6"/>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A448" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="B448" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C448" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A448" s="6"/>
+      <c r="B448" s="6"/>
+      <c r="C448" s="6"/>
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
-      <c r="F448" s="6" t="s">
-        <v>727</v>
-      </c>
+      <c r="F448" s="6"/>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
       <c r="I448" s="6"/>
-      <c r="J448" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J448" s="6"/>
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>728</v>
+        <v>706</v>
       </c>
       <c r="B449" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13533,20 +13462,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="450" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>730</v>
+        <v>708</v>
       </c>
       <c r="B450" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13557,18 +13486,18 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>732</v>
+        <v>710</v>
       </c>
       <c r="B451" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>733</v>
+        <v>711</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13579,18 +13508,18 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>734</v>
+        <v>712</v>
       </c>
       <c r="B452" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
       <c r="F452" s="6" t="s">
-        <v>735</v>
+        <v>713</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
@@ -13599,57 +13528,75 @@
         <v>14</v>
       </c>
     </row>
-    <row r="453" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="B453" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="10" t="s">
-        <v>737</v>
+      <c r="F453" s="6" t="s">
+        <v>715</v>
       </c>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
-      <c r="I453" s="10" t="s">
-        <v>738</v>
-      </c>
+      <c r="I453" s="6"/>
       <c r="J453" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A454" s="6"/>
-      <c r="B454" s="6"/>
-      <c r="C454" s="6"/>
+      <c r="A454" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D454" s="6"/>
       <c r="E454" s="6"/>
-      <c r="F454" s="6"/>
+      <c r="F454" s="6" t="s">
+        <v>717</v>
+      </c>
       <c r="G454" s="6"/>
       <c r="H454" s="6"/>
       <c r="I454" s="6"/>
-      <c r="J454" s="6"/>
+      <c r="J454" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A455" s="6"/>
-      <c r="B455" s="6"/>
-      <c r="C455" s="6"/>
+      <c r="A455" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C455" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D455" s="6"/>
       <c r="E455" s="6"/>
-      <c r="F455" s="6"/>
+      <c r="F455" s="6" t="s">
+        <v>719</v>
+      </c>
       <c r="G455" s="6"/>
       <c r="H455" s="6"/>
       <c r="I455" s="6"/>
-      <c r="J455" s="6"/>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J455" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A456" s="6" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="B456" s="6" t="s">
         <v>613</v>
@@ -13660,7 +13607,7 @@
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
       <c r="F456" s="6" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
@@ -13669,9 +13616,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="B457" s="6" t="s">
         <v>613</v>
@@ -13682,7 +13629,7 @@
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13693,7 +13640,7 @@
     </row>
     <row r="458" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="B458" s="6" t="s">
         <v>613</v>
@@ -13704,7 +13651,7 @@
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13715,18 +13662,18 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="B459" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C459" s="10" t="s">
-        <v>746</v>
+      <c r="C459" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
@@ -13737,42 +13684,40 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="B460" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C460" s="10" t="s">
-        <v>746</v>
+      <c r="C460" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
-      <c r="I460" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I460" s="6"/>
       <c r="J460" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B461" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C461" s="10" t="s">
-        <v>506</v>
+      <c r="C461" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -13783,18 +13728,18 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="B462" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C462" s="10" t="s">
-        <v>506</v>
+      <c r="C462" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>509</v>
+        <v>733</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -13805,18 +13750,18 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="B463" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C463" s="10" t="s">
-        <v>506</v>
+      <c r="C463" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
       <c r="F463" s="6" t="s">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
@@ -13825,86 +13770,68 @@
         <v>14</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="B464" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C464" s="10" t="s">
-        <v>506</v>
+      <c r="C464" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
-      <c r="F464" s="6" t="s">
-        <v>108</v>
+      <c r="F464" s="10" t="s">
+        <v>737</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
-      <c r="I464" s="6"/>
+      <c r="I464" s="10" t="s">
+        <v>738</v>
+      </c>
       <c r="J464" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A465" s="6" t="s">
-        <v>755</v>
-      </c>
-      <c r="B465" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C465" s="10" t="s">
-        <v>506</v>
-      </c>
+      <c r="A465" s="6"/>
+      <c r="B465" s="6"/>
+      <c r="C465" s="6"/>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="10" t="s">
-        <v>756</v>
-      </c>
+      <c r="F465" s="6"/>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
       <c r="I465" s="6"/>
-      <c r="J465" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J465" s="6"/>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A466" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="B466" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C466" s="10" t="s">
-        <v>506</v>
-      </c>
+      <c r="A466" s="6"/>
+      <c r="B466" s="6"/>
+      <c r="C466" s="6"/>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
-      <c r="F466" s="6" t="s">
-        <v>110</v>
-      </c>
+      <c r="F466" s="6"/>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
       <c r="I466" s="6"/>
-      <c r="J466" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J466" s="6"/>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="B467" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C467" s="10" t="s">
-        <v>506</v>
+      <c r="C467" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13913,20 +13840,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="B468" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C468" s="10" t="s">
-        <v>506</v>
+      <c r="C468" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13935,20 +13862,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B469" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C469" s="10" t="s">
-        <v>506</v>
+      <c r="C469" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13957,20 +13884,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="B470" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C470" s="10" t="s">
-        <v>506</v>
+        <v>746</v>
       </c>
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13981,40 +13908,42 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="B471" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C471" s="10" t="s">
-        <v>506</v>
+        <v>746</v>
       </c>
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
-      <c r="I471" s="6"/>
+      <c r="I471" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J471" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="B472" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C472" s="6" t="s">
+      <c r="C472" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -14025,18 +13954,18 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="B473" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C473" s="6" t="s">
+      <c r="C473" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>771</v>
+        <v>509</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14047,18 +13976,18 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="B474" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C474" s="6" t="s">
+      <c r="C474" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>773</v>
+        <v>104</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14069,18 +13998,18 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="B475" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C475" s="6" t="s">
+      <c r="C475" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>775</v>
+        <v>108</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14091,18 +14020,18 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="B476" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C476" s="6" t="s">
+      <c r="C476" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
-      <c r="F476" s="6" t="s">
-        <v>777</v>
+      <c r="F476" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14113,18 +14042,18 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="B477" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C477" s="6" t="s">
+      <c r="C477" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>779</v>
+        <v>110</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14135,18 +14064,18 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>780</v>
+        <v>758</v>
       </c>
       <c r="B478" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C478" s="6" t="s">
+      <c r="C478" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14157,18 +14086,18 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
       <c r="B479" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C479" s="6" t="s">
+      <c r="C479" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>783</v>
+        <v>761</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14179,18 +14108,18 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>784</v>
+        <v>762</v>
       </c>
       <c r="B480" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C480" s="6" t="s">
+      <c r="C480" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>785</v>
+        <v>763</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14199,20 +14128,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>786</v>
+        <v>764</v>
       </c>
       <c r="B481" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C481" s="6" t="s">
+      <c r="C481" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14223,18 +14152,18 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>788</v>
+        <v>766</v>
       </c>
       <c r="B482" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C482" s="6" t="s">
+      <c r="C482" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14245,7 +14174,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>790</v>
+        <v>768</v>
       </c>
       <c r="B483" s="6" t="s">
         <v>613</v>
@@ -14256,7 +14185,7 @@
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14267,7 +14196,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="B484" s="6" t="s">
         <v>613</v>
@@ -14278,7 +14207,7 @@
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>793</v>
+        <v>771</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14289,7 +14218,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>794</v>
+        <v>772</v>
       </c>
       <c r="B485" s="6" t="s">
         <v>613</v>
@@ -14300,7 +14229,7 @@
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>541</v>
+        <v>773</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14311,7 +14240,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="B486" s="6" t="s">
         <v>613</v>
@@ -14322,7 +14251,7 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14333,7 +14262,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="B487" s="6" t="s">
         <v>613</v>
@@ -14344,7 +14273,7 @@
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
       <c r="F487" s="6" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
@@ -14353,161 +14282,271 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="B488" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C488" s="10" t="s">
+      <c r="C488" s="6" t="s">
         <v>506</v>
       </c>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="10" t="s">
-        <v>800</v>
+      <c r="F488" s="6" t="s">
+        <v>779</v>
       </c>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
-      <c r="I488" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I488" s="6"/>
       <c r="J488" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A489" s="6"/>
-      <c r="B489" s="6"/>
-      <c r="C489" s="6"/>
+      <c r="A489" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="B489" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C489" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
-      <c r="F489" s="6"/>
+      <c r="F489" s="6" t="s">
+        <v>781</v>
+      </c>
       <c r="G489" s="6"/>
       <c r="H489" s="6"/>
       <c r="I489" s="6"/>
-      <c r="J489" s="6"/>
+      <c r="J489" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A490" s="6"/>
-      <c r="B490" s="6"/>
-      <c r="C490" s="6"/>
+      <c r="A490" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="B490" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C490" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D490" s="6"/>
       <c r="E490" s="6"/>
-      <c r="F490" s="6"/>
+      <c r="F490" s="6" t="s">
+        <v>783</v>
+      </c>
       <c r="G490" s="6"/>
       <c r="H490" s="6"/>
       <c r="I490" s="6"/>
-      <c r="J490" s="6"/>
+      <c r="J490" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A491" s="6"/>
-      <c r="B491" s="6"/>
-      <c r="C491" s="6"/>
+      <c r="A491" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="B491" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C491" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D491" s="6"/>
       <c r="E491" s="6"/>
-      <c r="F491" s="6"/>
+      <c r="F491" s="6" t="s">
+        <v>785</v>
+      </c>
       <c r="G491" s="6"/>
       <c r="H491" s="6"/>
       <c r="I491" s="6"/>
-      <c r="J491" s="6"/>
+      <c r="J491" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="492" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A492" s="6"/>
-      <c r="B492" s="6"/>
-      <c r="C492" s="6"/>
+      <c r="A492" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="B492" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C492" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D492" s="6"/>
       <c r="E492" s="6"/>
-      <c r="F492" s="6"/>
+      <c r="F492" s="6" t="s">
+        <v>787</v>
+      </c>
       <c r="G492" s="6"/>
       <c r="H492" s="6"/>
       <c r="I492" s="6"/>
-      <c r="J492" s="6"/>
+      <c r="J492" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="493" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A493" s="6"/>
-      <c r="B493" s="6"/>
-      <c r="C493" s="6"/>
+      <c r="A493" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="B493" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C493" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D493" s="6"/>
       <c r="E493" s="6"/>
-      <c r="F493" s="6"/>
+      <c r="F493" s="6" t="s">
+        <v>789</v>
+      </c>
       <c r="G493" s="6"/>
       <c r="H493" s="6"/>
       <c r="I493" s="6"/>
-      <c r="J493" s="6"/>
+      <c r="J493" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="494" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A494" s="6"/>
-      <c r="B494" s="6"/>
-      <c r="C494" s="6"/>
+      <c r="A494" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="B494" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C494" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D494" s="6"/>
       <c r="E494" s="6"/>
-      <c r="F494" s="6"/>
+      <c r="F494" s="6" t="s">
+        <v>791</v>
+      </c>
       <c r="G494" s="6"/>
       <c r="H494" s="6"/>
       <c r="I494" s="6"/>
-      <c r="J494" s="6"/>
+      <c r="J494" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="495" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A495" s="6"/>
-      <c r="B495" s="6"/>
-      <c r="C495" s="6"/>
+      <c r="A495" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B495" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C495" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D495" s="6"/>
       <c r="E495" s="6"/>
-      <c r="F495" s="6"/>
+      <c r="F495" s="6" t="s">
+        <v>793</v>
+      </c>
       <c r="G495" s="6"/>
       <c r="H495" s="6"/>
       <c r="I495" s="6"/>
-      <c r="J495" s="6"/>
+      <c r="J495" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="496" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A496" s="6"/>
-      <c r="B496" s="6"/>
-      <c r="C496" s="6"/>
+      <c r="A496" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B496" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C496" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D496" s="6"/>
       <c r="E496" s="6"/>
-      <c r="F496" s="6"/>
+      <c r="F496" s="6" t="s">
+        <v>541</v>
+      </c>
       <c r="G496" s="6"/>
       <c r="H496" s="6"/>
       <c r="I496" s="6"/>
-      <c r="J496" s="6"/>
+      <c r="J496" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A497" s="6"/>
-      <c r="B497" s="6"/>
-      <c r="C497" s="6"/>
+      <c r="A497" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="B497" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C497" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D497" s="6"/>
       <c r="E497" s="6"/>
-      <c r="F497" s="6"/>
+      <c r="F497" s="6" t="s">
+        <v>796</v>
+      </c>
       <c r="G497" s="6"/>
       <c r="H497" s="6"/>
       <c r="I497" s="6"/>
-      <c r="J497" s="6"/>
+      <c r="J497" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="498" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A498" s="6"/>
-      <c r="B498" s="6"/>
-      <c r="C498" s="6"/>
+      <c r="A498" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="B498" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C498" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="D498" s="6"/>
       <c r="E498" s="6"/>
-      <c r="F498" s="6"/>
+      <c r="F498" s="6" t="s">
+        <v>798</v>
+      </c>
       <c r="G498" s="6"/>
       <c r="H498" s="6"/>
       <c r="I498" s="6"/>
-      <c r="J498" s="6"/>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A499" s="6"/>
-      <c r="B499" s="6"/>
-      <c r="C499" s="6"/>
+      <c r="J498" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A499" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B499" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C499" s="10" t="s">
+        <v>506</v>
+      </c>
       <c r="D499" s="6"/>
       <c r="E499" s="6"/>
-      <c r="F499" s="6"/>
+      <c r="F499" s="10" t="s">
+        <v>800</v>
+      </c>
       <c r="G499" s="6"/>
       <c r="H499" s="6"/>
-      <c r="I499" s="6"/>
-      <c r="J499" s="6"/>
+      <c r="I499" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J499" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" s="6"/>
@@ -14630,116 +14669,64 @@
       <c r="J509" s="6"/>
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A510" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="B510" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C510" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A510" s="6"/>
+      <c r="B510" s="6"/>
+      <c r="C510" s="6"/>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
-      <c r="F510" s="6" t="s">
-        <v>803</v>
-      </c>
+      <c r="F510" s="6"/>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
       <c r="I510" s="6"/>
-      <c r="J510" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A511" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="B511" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C511" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="J510" s="6"/>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A511" s="6"/>
+      <c r="B511" s="6"/>
+      <c r="C511" s="6"/>
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
-      <c r="F511" s="6" t="s">
-        <v>805</v>
-      </c>
+      <c r="F511" s="6"/>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
       <c r="I511" s="6"/>
-      <c r="J511" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J511" s="6"/>
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A512" s="6" t="s">
-        <v>806</v>
-      </c>
-      <c r="B512" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C512" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A512" s="6"/>
+      <c r="B512" s="6"/>
+      <c r="C512" s="6"/>
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
-      <c r="F512" s="6" t="s">
-        <v>807</v>
-      </c>
+      <c r="F512" s="6"/>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
       <c r="I512" s="6"/>
-      <c r="J512" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J512" s="6"/>
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A513" s="6" t="s">
-        <v>808</v>
-      </c>
-      <c r="B513" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C513" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A513" s="6"/>
+      <c r="B513" s="6"/>
+      <c r="C513" s="6"/>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
-      <c r="F513" s="6" t="s">
-        <v>425</v>
-      </c>
+      <c r="F513" s="6"/>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
       <c r="I513" s="6"/>
-      <c r="J513" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="514" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A514" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="B514" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C514" s="10" t="s">
-        <v>524</v>
-      </c>
+      <c r="J513" s="6"/>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A514" s="6"/>
+      <c r="B514" s="6"/>
+      <c r="C514" s="6"/>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="10" t="s">
-        <v>810</v>
-      </c>
+      <c r="F514" s="6"/>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
-      <c r="I514" s="10" t="s">
-        <v>801</v>
-      </c>
-      <c r="J514" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I514" s="6"/>
+      <c r="J514" s="6"/>
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="6"/>
@@ -14814,64 +14801,116 @@
       <c r="J520" s="6"/>
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A521" s="6"/>
-      <c r="B521" s="6"/>
-      <c r="C521" s="6"/>
+      <c r="A521" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="B521" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C521" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D521" s="6"/>
       <c r="E521" s="6"/>
-      <c r="F521" s="6"/>
+      <c r="F521" s="6" t="s">
+        <v>803</v>
+      </c>
       <c r="G521" s="6"/>
       <c r="H521" s="6"/>
       <c r="I521" s="6"/>
-      <c r="J521" s="6"/>
-    </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A522" s="6"/>
-      <c r="B522" s="6"/>
-      <c r="C522" s="6"/>
+      <c r="J521" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A522" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B522" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C522" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D522" s="6"/>
       <c r="E522" s="6"/>
-      <c r="F522" s="6"/>
+      <c r="F522" s="6" t="s">
+        <v>805</v>
+      </c>
       <c r="G522" s="6"/>
       <c r="H522" s="6"/>
       <c r="I522" s="6"/>
-      <c r="J522" s="6"/>
+      <c r="J522" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A523" s="6"/>
-      <c r="B523" s="6"/>
-      <c r="C523" s="6"/>
+      <c r="A523" s="6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B523" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C523" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D523" s="6"/>
       <c r="E523" s="6"/>
-      <c r="F523" s="6"/>
+      <c r="F523" s="6" t="s">
+        <v>807</v>
+      </c>
       <c r="G523" s="6"/>
       <c r="H523" s="6"/>
       <c r="I523" s="6"/>
-      <c r="J523" s="6"/>
+      <c r="J523" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A524" s="6"/>
-      <c r="B524" s="6"/>
-      <c r="C524" s="6"/>
+      <c r="A524" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="B524" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C524" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D524" s="6"/>
       <c r="E524" s="6"/>
-      <c r="F524" s="6"/>
+      <c r="F524" s="6" t="s">
+        <v>425</v>
+      </c>
       <c r="G524" s="6"/>
       <c r="H524" s="6"/>
       <c r="I524" s="6"/>
-      <c r="J524" s="6"/>
-    </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A525" s="6"/>
-      <c r="B525" s="6"/>
-      <c r="C525" s="6"/>
+      <c r="J524" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A525" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B525" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C525" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D525" s="6"/>
       <c r="E525" s="6"/>
-      <c r="F525" s="6"/>
+      <c r="F525" s="10" t="s">
+        <v>810</v>
+      </c>
       <c r="G525" s="6"/>
       <c r="H525" s="6"/>
-      <c r="I525" s="6"/>
-      <c r="J525" s="6"/>
+      <c r="I525" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J525" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="6"/>
@@ -14993,29 +15032,17 @@
       <c r="I535" s="6"/>
       <c r="J535" s="6"/>
     </row>
-    <row r="536" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A536" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="B536" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C536" s="10" t="s">
-        <v>524</v>
-      </c>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A536" s="6"/>
+      <c r="B536" s="6"/>
+      <c r="C536" s="6"/>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="10" t="s">
-        <v>812</v>
-      </c>
+      <c r="F536" s="6"/>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
-      <c r="I536" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J536" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I536" s="6"/>
+      <c r="J536" s="6"/>
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="6"/>
@@ -15114,160 +15141,100 @@
       <c r="J544" s="6"/>
     </row>
     <row r="545" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A545" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="B545" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C545" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A545" s="6"/>
+      <c r="B545" s="6"/>
+      <c r="C545" s="6"/>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
-      <c r="F545" s="6" t="s">
-        <v>814</v>
-      </c>
+      <c r="F545" s="6"/>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
       <c r="I545" s="6"/>
-      <c r="J545" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A546" s="6" t="s">
-        <v>815</v>
-      </c>
-      <c r="B546" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C546" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="J545" s="6"/>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A546" s="6"/>
+      <c r="B546" s="6"/>
+      <c r="C546" s="6"/>
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
-      <c r="F546" s="6" t="s">
-        <v>206</v>
-      </c>
+      <c r="F546" s="6"/>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
       <c r="I546" s="6"/>
-      <c r="J546" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="547" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J546" s="6"/>
+    </row>
+    <row r="547" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B547" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C547" s="6" t="s">
+      <c r="C547" s="10" t="s">
         <v>524</v>
       </c>
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
-      <c r="F547" s="6" t="s">
-        <v>817</v>
+      <c r="F547" s="10" t="s">
+        <v>812</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
-      <c r="I547" s="6"/>
+      <c r="I547" s="10" t="s">
+        <v>415</v>
+      </c>
       <c r="J547" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="548" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A548" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="B548" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C548" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A548" s="6"/>
+      <c r="B548" s="6"/>
+      <c r="C548" s="6"/>
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
-      <c r="F548" s="6" t="s">
-        <v>210</v>
-      </c>
+      <c r="F548" s="6"/>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
       <c r="I548" s="6"/>
-      <c r="J548" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J548" s="6"/>
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A549" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="B549" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C549" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A549" s="6"/>
+      <c r="B549" s="6"/>
+      <c r="C549" s="6"/>
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
-      <c r="F549" s="6" t="s">
-        <v>820</v>
-      </c>
+      <c r="F549" s="6"/>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
       <c r="I549" s="6"/>
-      <c r="J549" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J549" s="6"/>
     </row>
     <row r="550" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A550" s="6" t="s">
-        <v>821</v>
-      </c>
-      <c r="B550" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C550" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A550" s="6"/>
+      <c r="B550" s="6"/>
+      <c r="C550" s="6"/>
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
-      <c r="F550" s="6" t="s">
-        <v>717</v>
-      </c>
+      <c r="F550" s="6"/>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
       <c r="I550" s="6"/>
-      <c r="J550" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="551" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A551" s="6" t="s">
-        <v>822</v>
-      </c>
-      <c r="B551" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C551" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="J550" s="6"/>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A551" s="6"/>
+      <c r="B551" s="6"/>
+      <c r="C551" s="6"/>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="10" t="s">
-        <v>823</v>
-      </c>
+      <c r="F551" s="6"/>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
-      <c r="I551" s="10" t="s">
-        <v>824</v>
-      </c>
-      <c r="J551" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I551" s="6"/>
+      <c r="J551" s="6"/>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" s="6"/>
@@ -15282,63 +15249,267 @@
       <c r="J552" s="6"/>
     </row>
     <row r="553" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A553" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="B553" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C553" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A553" s="6"/>
+      <c r="B553" s="6"/>
+      <c r="C553" s="6"/>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
-      <c r="F553" s="6" t="s">
-        <v>826</v>
-      </c>
+      <c r="F553" s="6"/>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
       <c r="I553" s="6"/>
-      <c r="J553" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="554" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A554" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="B554" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C554" s="6" t="s">
-        <v>828</v>
-      </c>
+      <c r="J553" s="6"/>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A554" s="6"/>
+      <c r="B554" s="6"/>
+      <c r="C554" s="6"/>
       <c r="D554" s="6"/>
       <c r="E554" s="6"/>
-      <c r="F554" s="6" t="s">
-        <v>829</v>
-      </c>
+      <c r="F554" s="6"/>
       <c r="G554" s="6"/>
       <c r="H554" s="6"/>
-      <c r="I554" s="10" t="s">
+      <c r="I554" s="6"/>
+      <c r="J554" s="6"/>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A555" s="6"/>
+      <c r="B555" s="6"/>
+      <c r="C555" s="6"/>
+      <c r="D555" s="6"/>
+      <c r="E555" s="6"/>
+      <c r="F555" s="6"/>
+      <c r="G555" s="6"/>
+      <c r="H555" s="6"/>
+      <c r="I555" s="6"/>
+      <c r="J555" s="6"/>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A556" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="B556" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C556" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D556" s="6"/>
+      <c r="E556" s="6"/>
+      <c r="F556" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="G556" s="6"/>
+      <c r="H556" s="6"/>
+      <c r="I556" s="6"/>
+      <c r="J556" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A557" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="B557" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C557" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D557" s="6"/>
+      <c r="E557" s="6"/>
+      <c r="F557" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G557" s="6"/>
+      <c r="H557" s="6"/>
+      <c r="I557" s="6"/>
+      <c r="J557" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A558" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="B558" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C558" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D558" s="6"/>
+      <c r="E558" s="6"/>
+      <c r="F558" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="G558" s="6"/>
+      <c r="H558" s="6"/>
+      <c r="I558" s="6"/>
+      <c r="J558" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A559" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="B559" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C559" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D559" s="6"/>
+      <c r="E559" s="6"/>
+      <c r="F559" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="G559" s="6"/>
+      <c r="H559" s="6"/>
+      <c r="I559" s="6"/>
+      <c r="J559" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A560" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="B560" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C560" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D560" s="6"/>
+      <c r="E560" s="6"/>
+      <c r="F560" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="G560" s="6"/>
+      <c r="H560" s="6"/>
+      <c r="I560" s="6"/>
+      <c r="J560" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A561" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="B561" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C561" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D561" s="6"/>
+      <c r="E561" s="6"/>
+      <c r="F561" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="G561" s="6"/>
+      <c r="H561" s="6"/>
+      <c r="I561" s="6"/>
+      <c r="J561" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A562" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="B562" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C562" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D562" s="6"/>
+      <c r="E562" s="6"/>
+      <c r="F562" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="G562" s="6"/>
+      <c r="H562" s="6"/>
+      <c r="I562" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="J562" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A563" s="6"/>
+      <c r="B563" s="6"/>
+      <c r="C563" s="6"/>
+      <c r="D563" s="6"/>
+      <c r="E563" s="6"/>
+      <c r="F563" s="6"/>
+      <c r="G563" s="6"/>
+      <c r="H563" s="6"/>
+      <c r="I563" s="6"/>
+      <c r="J563" s="6"/>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A564" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="B564" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C564" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D564" s="6"/>
+      <c r="E564" s="6"/>
+      <c r="F564" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="G564" s="6"/>
+      <c r="H564" s="6"/>
+      <c r="I564" s="6"/>
+      <c r="J564" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A565" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B565" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C565" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D565" s="6"/>
+      <c r="E565" s="6"/>
+      <c r="F565" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="G565" s="6"/>
+      <c r="H565" s="6"/>
+      <c r="I565" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="J554" s="6" t="s">
+      <c r="J565" s="6" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C2:C67 C180:C389 C69:C178" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H380:H947 H2:H378" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H391:H958 H2:H67 H180:H389 H69:H178" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J380:J947 J2:J378" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J391:J958 J2:J67 J180:J389 J69:J178" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C2:C67 C180:C389 C69:C178" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9968AE-08F1-438F-B55C-36B769952BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC35090-3845-4491-BA53-7EC0D133AD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2983,10 +2983,10 @@
 (Keyword: Breathing Apparatus)</t>
   </si>
   <si>
-    <t>Chock Tray Layout Photo</t>
-  </si>
-  <si>
     <t>BR-0100</t>
+  </si>
+  <si>
+    <t>CHOCK TRAY LAYOUT PHOTO</t>
   </si>
 </sst>
 </file>
@@ -5339,6 +5339,36 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
     </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+    </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>150</v>
@@ -7632,36 +7662,6 @@
       <c r="N147" s="5"/>
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="5" t="s">
-        <v>928</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5" t="s">
-        <v>927</v>
-      </c>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K148" s="5"/>
-      <c r="L148" s="5"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="5"/>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="13"/>
@@ -15500,16 +15500,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C2:C67 C180:C389 C69:C178" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C180:C389 C2:C147 C149:C178" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H391:H958 H2:H67 H180:H389 H69:H178" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H391:H958 H180:H389 H2:H147 H149:H178" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J391:J958 J2:J67 J180:J389 J69:J178" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J391:J958 J180:J389 J2:J147 J149:J178" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C2:C67 C180:C389 C69:C178" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C499:C520 C525:C555 C431:C436 C440 C444:C448 C566:C958 C391:C426 C470:C482 C180:C389 C2:C147 C149:C178" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA10522D-1361-467B-8005-0D6907310CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798EA734-DBAD-4125-A394-7790864A913D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="930">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2981,6 +2981,15 @@
 Clock
 Entry Control sheets
 (Keyword: Breathing Apparatus)</t>
+  </si>
+  <si>
+    <t>BR-0112</t>
+  </si>
+  <si>
+    <t>Block Tray Layout</t>
+  </si>
+  <si>
+    <t>(Keyword: Chock)</t>
   </si>
 </sst>
 </file>
@@ -3313,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P553"/>
+  <dimension ref="A1:P554"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5002,7 +5011,7 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>125</v>
+        <v>927</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
@@ -5010,16 +5019,16 @@
       <c r="C57" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>128</v>
+        <v>928</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="I57" s="5" t="s">
+        <v>929</v>
+      </c>
       <c r="J57" s="5" t="s">
         <v>14</v>
       </c>
@@ -5032,7 +5041,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
@@ -5045,7 +5054,7 @@
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -5062,7 +5071,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
@@ -5075,7 +5084,7 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5092,7 +5101,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
@@ -5105,7 +5114,7 @@
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5122,7 +5131,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
@@ -5135,7 +5144,7 @@
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5152,7 +5161,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
@@ -5165,7 +5174,7 @@
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5182,7 +5191,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
@@ -5195,7 +5204,7 @@
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5212,7 +5221,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
@@ -5221,11 +5230,11 @@
         <v>126</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -5242,7 +5251,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
@@ -5255,7 +5264,7 @@
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -5272,7 +5281,7 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
@@ -5285,7 +5294,7 @@
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5302,7 +5311,7 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
@@ -5315,7 +5324,7 @@
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5332,7 +5341,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
@@ -5341,11 +5350,11 @@
         <v>126</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5362,7 +5371,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
@@ -5375,7 +5384,7 @@
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5392,7 +5401,7 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -5401,11 +5410,11 @@
         <v>126</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5422,7 +5431,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
@@ -5435,7 +5444,7 @@
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5452,7 +5461,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
@@ -5465,7 +5474,7 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5482,7 +5491,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
@@ -5495,7 +5504,7 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5512,7 +5521,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
@@ -5525,7 +5534,7 @@
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5542,7 +5551,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
@@ -5555,7 +5564,7 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5572,7 +5581,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
@@ -5585,7 +5594,7 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5602,7 +5611,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
@@ -5611,11 +5620,11 @@
         <v>126</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5632,7 +5641,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
@@ -5645,7 +5654,7 @@
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5662,7 +5671,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
@@ -5675,7 +5684,7 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5692,7 +5701,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
@@ -5705,7 +5714,7 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5722,7 +5731,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
@@ -5735,7 +5744,7 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5752,18 +5761,20 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D82" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5780,18 +5791,18 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5808,7 +5819,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
@@ -5819,7 +5830,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5836,7 +5847,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
@@ -5847,7 +5858,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5864,7 +5875,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
@@ -5875,7 +5886,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5892,7 +5903,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>10</v>
@@ -5903,7 +5914,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5920,7 +5931,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
@@ -5931,7 +5942,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5948,7 +5959,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>10</v>
@@ -5959,7 +5970,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5976,7 +5987,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>10</v>
@@ -5987,7 +5998,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -6004,7 +6015,7 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>10</v>
@@ -6015,7 +6026,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -6032,7 +6043,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>10</v>
@@ -6043,7 +6054,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6058,9 +6069,9 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
     </row>
-    <row r="93" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
@@ -6071,7 +6082,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -6086,9 +6097,9 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>10</v>
@@ -6099,7 +6110,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -6116,7 +6127,7 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>10</v>
@@ -6127,7 +6138,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -6144,7 +6155,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>10</v>
@@ -6155,7 +6166,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -6172,7 +6183,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>10</v>
@@ -6183,7 +6194,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -6200,7 +6211,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>10</v>
@@ -6211,7 +6222,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -6228,7 +6239,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>10</v>
@@ -6239,7 +6250,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -6256,7 +6267,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
@@ -6267,7 +6278,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -6284,7 +6295,7 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>10</v>
@@ -6295,7 +6306,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -6312,7 +6323,7 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
@@ -6323,7 +6334,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -6340,7 +6351,7 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
@@ -6351,7 +6362,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -6368,7 +6379,7 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
@@ -6379,7 +6390,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -6396,7 +6407,7 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
@@ -6407,7 +6418,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -6424,7 +6435,7 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
@@ -6435,7 +6446,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -6452,7 +6463,7 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
@@ -6463,7 +6474,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6480,7 +6491,7 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -6491,7 +6502,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6506,9 +6517,9 @@
       <c r="O108" s="5"/>
       <c r="P108" s="5"/>
     </row>
-    <row r="109" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -6519,13 +6530,11 @@
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
-      <c r="I109" s="5" t="s">
-        <v>239</v>
-      </c>
+      <c r="I109" s="5"/>
       <c r="J109" s="5" t="s">
         <v>14</v>
       </c>
@@ -6536,9 +6545,9 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -6549,12 +6558,12 @@
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5" t="s">
-        <v>923</v>
+        <v>239</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>14</v>
@@ -6568,24 +6577,24 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>244</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
+      <c r="I111" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="J111" s="5" t="s">
         <v>14</v>
       </c>
@@ -6598,7 +6607,7 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
@@ -6611,7 +6620,7 @@
       </c>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
@@ -6628,7 +6637,7 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
@@ -6641,7 +6650,7 @@
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6658,7 +6667,7 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>10</v>
@@ -6671,7 +6680,7 @@
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6688,7 +6697,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>10</v>
@@ -6701,7 +6710,7 @@
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6716,9 +6725,9 @@
       <c r="O115" s="5"/>
       <c r="P115" s="5"/>
     </row>
-    <row r="116" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
@@ -6731,7 +6740,7 @@
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6746,9 +6755,9 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>10</v>
@@ -6757,11 +6766,11 @@
         <v>243</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6778,7 +6787,7 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>10</v>
@@ -6791,7 +6800,7 @@
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6808,7 +6817,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>10</v>
@@ -6821,7 +6830,7 @@
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6838,7 +6847,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>10</v>
@@ -6851,7 +6860,7 @@
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -6868,7 +6877,7 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
@@ -6881,7 +6890,7 @@
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
@@ -6898,7 +6907,7 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
@@ -6911,7 +6920,7 @@
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
@@ -6928,7 +6937,7 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>10</v>
@@ -6941,7 +6950,7 @@
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
@@ -6958,7 +6967,7 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
@@ -6971,7 +6980,7 @@
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -6988,7 +6997,7 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
@@ -7001,7 +7010,7 @@
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -7018,7 +7027,7 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>10</v>
@@ -7031,7 +7040,7 @@
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -7048,7 +7057,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>10</v>
@@ -7061,7 +7070,7 @@
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -7076,9 +7085,9 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
     </row>
-    <row r="128" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>10</v>
@@ -7087,17 +7096,15 @@
         <v>243</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
-      <c r="I128" s="5" t="s">
-        <v>282</v>
-      </c>
+      <c r="I128" s="5"/>
       <c r="J128" s="5" t="s">
         <v>14</v>
       </c>
@@ -7108,9 +7115,9 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>10</v>
@@ -7123,11 +7130,13 @@
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
+      <c r="I129" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="J129" s="5" t="s">
         <v>14</v>
       </c>
@@ -7140,7 +7149,7 @@
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>10</v>
@@ -7153,7 +7162,7 @@
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
@@ -7170,7 +7179,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>10</v>
@@ -7183,7 +7192,7 @@
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -7200,7 +7209,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>10</v>
@@ -7213,7 +7222,7 @@
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -7228,9 +7237,9 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
     </row>
-    <row r="133" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>10</v>
@@ -7243,7 +7252,7 @@
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -7258,9 +7267,9 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>10</v>
@@ -7273,7 +7282,7 @@
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7290,18 +7299,20 @@
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D135" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7318,7 +7329,7 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>10</v>
@@ -7329,7 +7340,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7346,7 +7357,7 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
@@ -7357,7 +7368,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7374,7 +7385,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -7385,7 +7396,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -7402,7 +7413,7 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -7413,7 +7424,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7430,7 +7441,7 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -7441,7 +7452,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7458,7 +7469,7 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -7469,7 +7480,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7486,7 +7497,7 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -7497,7 +7508,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7514,7 +7525,7 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -7525,7 +7536,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -7542,7 +7553,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -7553,7 +7564,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7570,7 +7581,7 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -7581,7 +7592,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7598,7 +7609,7 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -7609,7 +7620,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -7624,51 +7635,55 @@
       <c r="O146" s="5"/>
       <c r="P146" s="5"/>
     </row>
-    <row r="147" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="7"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K147" s="5"/>
+      <c r="L147" s="5"/>
+      <c r="M147" s="5"/>
+      <c r="N147" s="5"/>
+      <c r="O147" s="5"/>
+      <c r="P147" s="5"/>
+    </row>
+    <row r="148" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>321</v>
@@ -7681,7 +7696,7 @@
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
@@ -7692,7 +7707,7 @@
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>321</v>
@@ -7705,7 +7720,7 @@
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -7716,7 +7731,7 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>321</v>
@@ -7725,11 +7740,11 @@
         <v>11</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -7740,7 +7755,7 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>321</v>
@@ -7753,7 +7768,7 @@
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -7764,7 +7779,7 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>321</v>
@@ -7777,7 +7792,7 @@
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -7788,7 +7803,7 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>321</v>
@@ -7801,7 +7816,7 @@
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -7812,7 +7827,7 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>321</v>
@@ -7825,7 +7840,7 @@
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -7836,7 +7851,7 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>321</v>
@@ -7849,7 +7864,7 @@
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -7860,7 +7875,7 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>321</v>
@@ -7873,7 +7888,7 @@
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -7884,7 +7899,7 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>321</v>
@@ -7897,7 +7912,7 @@
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>42</v>
+        <v>337</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -7908,7 +7923,7 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>321</v>
@@ -7921,7 +7936,7 @@
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>340</v>
+        <v>42</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -7932,7 +7947,7 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>321</v>
@@ -7945,7 +7960,7 @@
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7956,7 +7971,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
@@ -7969,7 +7984,7 @@
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -7980,7 +7995,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>321</v>
@@ -7993,7 +8008,7 @@
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8004,7 +8019,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>321</v>
@@ -8017,7 +8032,7 @@
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8028,7 +8043,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>321</v>
@@ -8041,7 +8056,7 @@
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>44</v>
+        <v>348</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8050,9 +8065,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>321</v>
@@ -8065,28 +8080,40 @@
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>351</v>
+        <v>44</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
-      <c r="I165" s="6" t="s">
-        <v>352</v>
-      </c>
+      <c r="I165" s="6"/>
       <c r="J165" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
+    <row r="166" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
+      <c r="F166" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
+      <c r="I166" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="J166" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
@@ -8136,43 +8163,43 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A171" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="6"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
       <c r="E171" s="6"/>
-      <c r="F171" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
-      <c r="I171" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="J171" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
+      <c r="I171" s="6"/>
+      <c r="J171" s="6"/>
+    </row>
+    <row r="172" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
+      <c r="F172" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
+      <c r="I172" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
@@ -8223,32 +8250,20 @@
       <c r="J176" s="6"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D177" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A177" s="6"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="6" t="s">
-        <v>356</v>
-      </c>
+      <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
       <c r="I177" s="6"/>
-      <c r="J177" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J177" s="6"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>321</v>
@@ -8261,7 +8276,7 @@
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
@@ -8272,7 +8287,7 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>321</v>
@@ -8285,7 +8300,7 @@
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -8296,7 +8311,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>321</v>
@@ -8309,7 +8324,7 @@
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -8318,9 +8333,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>321</v>
@@ -8331,29 +8346,41 @@
       <c r="D181" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
-      <c r="I181" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="I181" s="6"/>
       <c r="J181" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+    <row r="182" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
+      <c r="I182" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
@@ -8404,32 +8431,20 @@
       <c r="J186" s="6"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A187" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C187" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A187" s="6"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="6" t="s">
-        <v>368</v>
-      </c>
+      <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
       <c r="I187" s="6"/>
-      <c r="J187" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J187" s="6"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>321</v>
@@ -8442,7 +8457,7 @@
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
@@ -8453,7 +8468,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>321</v>
@@ -8466,20 +8481,18 @@
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
-      <c r="I189" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I189" s="6"/>
       <c r="J189" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>321</v>
@@ -8492,18 +8505,20 @@
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
+      <c r="I190" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J190" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>321</v>
@@ -8516,7 +8531,7 @@
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
@@ -8525,9 +8540,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>321</v>
@@ -8540,7 +8555,7 @@
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8551,7 +8566,7 @@
     </row>
     <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>321</v>
@@ -8564,7 +8579,7 @@
       </c>
       <c r="E193" s="6"/>
       <c r="F193" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -8575,7 +8590,7 @@
     </row>
     <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>321</v>
@@ -8588,7 +8603,7 @@
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -8597,9 +8612,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>321</v>
@@ -8612,7 +8627,7 @@
       </c>
       <c r="E195" s="6"/>
       <c r="F195" s="6" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -8623,7 +8638,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>321</v>
@@ -8636,7 +8651,7 @@
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -8647,7 +8662,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>321</v>
@@ -8660,7 +8675,7 @@
       </c>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -8671,7 +8686,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>321</v>
@@ -8684,7 +8699,7 @@
       </c>
       <c r="E198" s="6"/>
       <c r="F198" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -8695,7 +8710,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>321</v>
@@ -8708,7 +8723,7 @@
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>387</v>
+        <v>97</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8719,7 +8734,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>321</v>
@@ -8732,7 +8747,7 @@
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>93</v>
+        <v>387</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8743,7 +8758,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>321</v>
@@ -8756,7 +8771,7 @@
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>390</v>
+        <v>93</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -8767,7 +8782,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>321</v>
@@ -8780,7 +8795,7 @@
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8791,7 +8806,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>321</v>
@@ -8804,7 +8819,7 @@
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8815,7 +8830,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>321</v>
@@ -8828,7 +8843,7 @@
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>395</v>
+        <v>76</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8839,7 +8854,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>321</v>
@@ -8852,7 +8867,7 @@
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8863,31 +8878,31 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D206" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
-      <c r="I206" s="6" t="s">
-        <v>401</v>
-      </c>
+      <c r="I206" s="6"/>
       <c r="J206" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>321</v>
@@ -8898,18 +8913,20 @@
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
+      <c r="I207" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="J207" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>321</v>
@@ -8920,7 +8937,7 @@
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
@@ -8931,18 +8948,18 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8951,9 +8968,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>321</v>
@@ -8964,7 +8981,7 @@
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -8973,9 +8990,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>321</v>
@@ -8986,7 +9003,7 @@
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -8995,9 +9012,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>321</v>
@@ -9006,29 +9023,39 @@
         <v>407</v>
       </c>
       <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
-      <c r="I212" s="6" t="s">
-        <v>415</v>
-      </c>
+      <c r="I212" s="6"/>
       <c r="J212" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="6"/>
+    <row r="213" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A213" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
+      <c r="F213" s="6" t="s">
+        <v>414</v>
+      </c>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
-      <c r="J213" s="6"/>
+      <c r="I213" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J213" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
@@ -9115,30 +9142,20 @@
       <c r="J220" s="6"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A221" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="6"/>
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
-      <c r="F221" s="6" t="s">
-        <v>417</v>
-      </c>
+      <c r="F221" s="6"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
       <c r="I221" s="6"/>
-      <c r="J221" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J221" s="6"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>321</v>
@@ -9149,7 +9166,7 @@
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
@@ -9160,7 +9177,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>321</v>
@@ -9171,7 +9188,7 @@
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9182,7 +9199,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>321</v>
@@ -9193,7 +9210,7 @@
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
@@ -9204,7 +9221,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>321</v>
@@ -9215,7 +9232,7 @@
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
@@ -9226,7 +9243,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>321</v>
@@ -9237,20 +9254,18 @@
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
-      <c r="I226" s="6" t="s">
-        <v>924</v>
-      </c>
+      <c r="I226" s="6"/>
       <c r="J226" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>321</v>
@@ -9261,18 +9276,20 @@
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
+      <c r="I227" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J227" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>321</v>
@@ -9283,7 +9300,7 @@
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
@@ -9294,7 +9311,7 @@
     </row>
     <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>321</v>
@@ -9305,7 +9322,7 @@
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
@@ -9314,9 +9331,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>321</v>
@@ -9327,7 +9344,7 @@
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
@@ -9338,18 +9355,18 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
@@ -9360,7 +9377,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>321</v>
@@ -9371,7 +9388,7 @@
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -9382,7 +9399,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>321</v>
@@ -9393,20 +9410,18 @@
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
-      <c r="I233" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I233" s="6"/>
       <c r="J233" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>321</v>
@@ -9417,7 +9432,7 @@
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
@@ -9430,7 +9445,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>321</v>
@@ -9441,18 +9456,20 @@
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
-      <c r="I235" s="6"/>
+      <c r="I235" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J235" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>321</v>
@@ -9463,7 +9480,7 @@
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
@@ -9472,9 +9489,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>321</v>
@@ -9485,7 +9502,7 @@
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9496,7 +9513,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>321</v>
@@ -9507,7 +9524,7 @@
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
@@ -9518,7 +9535,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>321</v>
@@ -9529,7 +9546,7 @@
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9540,7 +9557,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>321</v>
@@ -9551,20 +9568,18 @@
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
-      <c r="I240" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I240" s="6"/>
       <c r="J240" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>321</v>
@@ -9575,7 +9590,7 @@
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
@@ -9586,9 +9601,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>321</v>
@@ -9599,28 +9614,40 @@
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
       <c r="I242" s="6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J242" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
+    <row r="243" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A243" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
-      <c r="F243" s="6"/>
+      <c r="F243" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
-      <c r="I243" s="6"/>
-      <c r="J243" s="6"/>
+      <c r="I243" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="J243" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
@@ -9682,31 +9709,21 @@
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
     </row>
-    <row r="249" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A249" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>462</v>
-      </c>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A249" s="6"/>
+      <c r="B249" s="6"/>
+      <c r="C249" s="6"/>
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
-      <c r="F249" s="6" t="s">
-        <v>463</v>
-      </c>
+      <c r="F249" s="6"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
       <c r="I249" s="6"/>
-      <c r="J249" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J249" s="6"/>
+    </row>
+    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>321</v>
@@ -9717,7 +9734,7 @@
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
@@ -9726,9 +9743,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
@@ -9737,29 +9754,39 @@
         <v>462</v>
       </c>
       <c r="D251" s="6"/>
+      <c r="E251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
-      <c r="I251" s="6" t="s">
-        <v>468</v>
-      </c>
+      <c r="I251" s="6"/>
       <c r="J251" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="6"/>
+    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A252" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D252" s="6"/>
-      <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
+      <c r="F252" s="6" t="s">
+        <v>467</v>
+      </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
-      <c r="I252" s="6"/>
-      <c r="J252" s="6"/>
+      <c r="I252" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
@@ -9786,30 +9813,20 @@
       <c r="J254" s="6"/>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A255" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A255" s="6"/>
+      <c r="B255" s="6"/>
+      <c r="C255" s="6"/>
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
-      <c r="F255" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="F255" s="6"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
       <c r="I255" s="6"/>
-      <c r="J255" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J255" s="6"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>321</v>
@@ -9820,7 +9837,7 @@
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
@@ -9831,7 +9848,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>321</v>
@@ -9842,7 +9859,7 @@
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9851,9 +9868,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>321</v>
@@ -9864,7 +9881,7 @@
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9875,7 +9892,7 @@
     </row>
     <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>321</v>
@@ -9886,7 +9903,7 @@
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9895,9 +9912,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>321</v>
@@ -9908,7 +9925,7 @@
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9917,9 +9934,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
@@ -9930,7 +9947,7 @@
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9941,7 +9958,7 @@
     </row>
     <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
@@ -9952,7 +9969,7 @@
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9963,7 +9980,7 @@
     </row>
     <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
@@ -9974,7 +9991,7 @@
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -9983,9 +10000,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>321</v>
@@ -9996,7 +10013,7 @@
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -10007,7 +10024,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>321</v>
@@ -10018,7 +10035,7 @@
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
@@ -10029,7 +10046,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>321</v>
@@ -10040,7 +10057,7 @@
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10049,9 +10066,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
@@ -10062,7 +10079,7 @@
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10071,9 +10088,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
@@ -10084,7 +10101,7 @@
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10095,18 +10112,18 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10117,7 +10134,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
@@ -10128,7 +10145,7 @@
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10139,7 +10156,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
@@ -10150,7 +10167,7 @@
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10161,18 +10178,18 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10183,7 +10200,7 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
@@ -10194,7 +10211,7 @@
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10205,7 +10222,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
@@ -10216,7 +10233,7 @@
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10227,7 +10244,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
@@ -10238,7 +10255,7 @@
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6" t="s">
-        <v>108</v>
+        <v>511</v>
       </c>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
@@ -10249,7 +10266,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
@@ -10260,7 +10277,7 @@
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10271,7 +10288,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
@@ -10282,7 +10299,7 @@
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10293,7 +10310,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
@@ -10304,7 +10321,7 @@
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10315,7 +10332,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
@@ -10326,7 +10343,7 @@
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10337,7 +10354,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
@@ -10348,7 +10365,7 @@
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10357,66 +10374,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D281" s="6"/>
+      <c r="E281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
-      <c r="I281" s="6" t="s">
-        <v>526</v>
-      </c>
+      <c r="I281" s="6"/>
       <c r="J281" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A282" s="6"/>
-      <c r="B282" s="6"/>
-      <c r="C282" s="6"/>
+    <row r="282" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D282" s="6"/>
-      <c r="E282" s="6"/>
-      <c r="F282" s="6"/>
+      <c r="F282" s="6" t="s">
+        <v>525</v>
+      </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="6"/>
-      <c r="J282" s="6"/>
-    </row>
-    <row r="283" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A283" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="I282" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J282" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283" s="6"/>
+      <c r="B283" s="6"/>
+      <c r="C283" s="6"/>
       <c r="D283" s="6"/>
       <c r="E283" s="6"/>
-      <c r="F283" s="6" t="s">
-        <v>528</v>
-      </c>
+      <c r="F283" s="6"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
       <c r="I283" s="6"/>
-      <c r="J283" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J283" s="6"/>
+    </row>
+    <row r="284" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>321</v>
@@ -10427,7 +10444,7 @@
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
       <c r="F284" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
@@ -10438,7 +10455,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
@@ -10449,7 +10466,7 @@
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10460,18 +10477,18 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10482,7 +10499,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
@@ -10493,7 +10510,7 @@
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10504,7 +10521,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
@@ -10515,7 +10532,7 @@
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10526,7 +10543,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
@@ -10537,7 +10554,7 @@
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10548,7 +10565,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
@@ -10559,7 +10576,7 @@
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10568,9 +10585,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
@@ -10581,7 +10598,7 @@
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10590,9 +10607,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
@@ -10603,7 +10620,7 @@
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10614,7 +10631,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
@@ -10625,7 +10642,7 @@
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
@@ -10636,7 +10653,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>321</v>
@@ -10647,7 +10664,7 @@
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
@@ -10656,9 +10673,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
@@ -10667,29 +10684,39 @@
         <v>534</v>
       </c>
       <c r="D295" s="6"/>
+      <c r="E295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
-      <c r="I295" s="6" t="s">
-        <v>554</v>
-      </c>
+      <c r="I295" s="6"/>
       <c r="J295" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A296" s="6"/>
-      <c r="B296" s="6"/>
-      <c r="C296" s="6"/>
+    <row r="296" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A296" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D296" s="6"/>
-      <c r="E296" s="6"/>
-      <c r="F296" s="6"/>
+      <c r="F296" s="6" t="s">
+        <v>553</v>
+      </c>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="6"/>
-      <c r="J296" s="6"/>
+      <c r="I296" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="J296" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
@@ -10739,41 +10766,41 @@
       <c r="I300" s="6"/>
       <c r="J300" s="6"/>
     </row>
-    <row r="301" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A301" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="B301" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C301" s="6" t="s">
-        <v>534</v>
-      </c>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A301" s="6"/>
+      <c r="B301" s="6"/>
+      <c r="C301" s="6"/>
       <c r="D301" s="6"/>
       <c r="E301" s="6"/>
-      <c r="F301" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="F301" s="6"/>
       <c r="G301" s="6"/>
       <c r="H301" s="6"/>
-      <c r="I301" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="J301" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" s="6"/>
-      <c r="B302" s="6"/>
-      <c r="C302" s="6"/>
+      <c r="I301" s="6"/>
+      <c r="J301" s="6"/>
+    </row>
+    <row r="302" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A302" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
-      <c r="F302" s="6"/>
+      <c r="F302" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
-      <c r="I302" s="6"/>
-      <c r="J302" s="6"/>
+      <c r="I302" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J302" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
@@ -11088,30 +11115,20 @@
       <c r="J328" s="6"/>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A329" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C329" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A329" s="6"/>
+      <c r="B329" s="6"/>
+      <c r="C329" s="6"/>
       <c r="D329" s="6"/>
       <c r="E329" s="6"/>
-      <c r="F329" s="6" t="s">
-        <v>559</v>
-      </c>
+      <c r="F329" s="6"/>
       <c r="G329" s="6"/>
       <c r="H329" s="6"/>
       <c r="I329" s="6"/>
-      <c r="J329" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J329" s="6"/>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B330" s="6" t="s">
         <v>321</v>
@@ -11122,7 +11139,7 @@
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
       <c r="F330" s="6" t="s">
-        <v>255</v>
+        <v>559</v>
       </c>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
@@ -11131,9 +11148,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>321</v>
@@ -11144,7 +11161,7 @@
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>562</v>
+        <v>255</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11155,7 +11172,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>321</v>
@@ -11166,7 +11183,7 @@
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11177,7 +11194,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>321</v>
@@ -11188,7 +11205,7 @@
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11199,18 +11216,18 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11221,7 +11238,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>321</v>
@@ -11232,7 +11249,7 @@
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11243,18 +11260,18 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11265,7 +11282,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>321</v>
@@ -11276,7 +11293,7 @@
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11287,7 +11304,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>321</v>
@@ -11298,7 +11315,7 @@
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11309,18 +11326,18 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>504</v>
+        <v>578</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11331,7 +11348,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>321</v>
@@ -11342,7 +11359,7 @@
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11353,7 +11370,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
@@ -11364,7 +11381,7 @@
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
       <c r="F341" s="6" t="s">
-        <v>307</v>
+        <v>582</v>
       </c>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
@@ -11375,18 +11392,18 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>586</v>
+        <v>307</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11397,7 +11414,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
@@ -11408,7 +11425,7 @@
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11419,7 +11436,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
@@ -11430,7 +11447,7 @@
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11441,7 +11458,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
@@ -11452,7 +11469,7 @@
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11461,9 +11478,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
@@ -11474,7 +11491,7 @@
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11483,20 +11500,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11507,7 +11524,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
@@ -11518,7 +11535,7 @@
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11529,7 +11546,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
@@ -11540,7 +11557,7 @@
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11551,7 +11568,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
@@ -11562,7 +11579,7 @@
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11573,7 +11590,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
@@ -11584,7 +11601,7 @@
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11595,7 +11612,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
@@ -11606,7 +11623,7 @@
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11615,9 +11632,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
@@ -11628,7 +11645,7 @@
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11637,9 +11654,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
@@ -11650,7 +11667,7 @@
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11659,45 +11676,43 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="9"/>
-      <c r="B355" s="9"/>
-      <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="F355" s="9"/>
-      <c r="G355" s="9"/>
-      <c r="H355" s="9"/>
-      <c r="I355" s="9"/>
-      <c r="J355" s="9"/>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A356" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B356" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C356" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D356" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E356" s="6"/>
-      <c r="F356" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G356" s="6"/>
-      <c r="H356" s="6"/>
-      <c r="I356" s="6"/>
-      <c r="J356" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A355" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D355" s="6"/>
+      <c r="E355" s="6"/>
+      <c r="F355" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G355" s="6"/>
+      <c r="H355" s="6"/>
+      <c r="I355" s="6"/>
+      <c r="J355" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A356" s="9"/>
+      <c r="B356" s="9"/>
+      <c r="C356" s="9"/>
+      <c r="D356" s="9"/>
+      <c r="E356" s="9"/>
+      <c r="F356" s="9"/>
+      <c r="G356" s="9"/>
+      <c r="H356" s="9"/>
+      <c r="I356" s="9"/>
+      <c r="J356" s="9"/>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B357" s="6" t="s">
         <v>613</v>
@@ -11710,7 +11725,7 @@
       </c>
       <c r="E357" s="6"/>
       <c r="F357" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G357" s="6"/>
       <c r="H357" s="6"/>
@@ -11721,7 +11736,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B358" s="6" t="s">
         <v>613</v>
@@ -11730,11 +11745,11 @@
         <v>11</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>616</v>
+        <v>18</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11743,9 +11758,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B359" s="6" t="s">
         <v>613</v>
@@ -11757,29 +11772,41 @@
         <v>37</v>
       </c>
       <c r="E359" s="6"/>
-      <c r="F359" s="10" t="s">
-        <v>618</v>
+      <c r="F359" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
-      <c r="I359" s="10" t="s">
-        <v>619</v>
-      </c>
+      <c r="I359" s="6"/>
       <c r="J359" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A360" s="6"/>
-      <c r="B360" s="6"/>
-      <c r="C360" s="6"/>
-      <c r="D360" s="6"/>
+    <row r="360" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A360" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="E360" s="6"/>
-      <c r="F360" s="6"/>
+      <c r="F360" s="10" t="s">
+        <v>618</v>
+      </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
-      <c r="I360" s="6"/>
-      <c r="J360" s="6"/>
+      <c r="I360" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="J360" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
@@ -11830,32 +11857,20 @@
       <c r="J364" s="6"/>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A365" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="B365" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C365" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D365" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A365" s="6"/>
+      <c r="B365" s="6"/>
+      <c r="C365" s="6"/>
+      <c r="D365" s="6"/>
       <c r="E365" s="6"/>
-      <c r="F365" s="6" t="s">
-        <v>621</v>
-      </c>
+      <c r="F365" s="6"/>
       <c r="G365" s="6"/>
       <c r="H365" s="6"/>
       <c r="I365" s="6"/>
-      <c r="J365" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J365" s="6"/>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B366" s="6" t="s">
         <v>613</v>
@@ -11868,7 +11883,7 @@
       </c>
       <c r="E366" s="6"/>
       <c r="F366" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
@@ -11879,7 +11894,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B367" s="6" t="s">
         <v>613</v>
@@ -11892,7 +11907,7 @@
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="6" t="s">
-        <v>329</v>
+        <v>623</v>
       </c>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
@@ -11903,7 +11918,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B368" s="6" t="s">
         <v>613</v>
@@ -11916,7 +11931,7 @@
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>626</v>
+        <v>329</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11927,7 +11942,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B369" s="6" t="s">
         <v>613</v>
@@ -11940,7 +11955,7 @@
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11951,7 +11966,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B370" s="6" t="s">
         <v>613</v>
@@ -11964,7 +11979,7 @@
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11975,7 +11990,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B371" s="6" t="s">
         <v>613</v>
@@ -11988,7 +12003,7 @@
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -11999,7 +12014,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B372" s="6" t="s">
         <v>613</v>
@@ -12012,7 +12027,7 @@
       </c>
       <c r="E372" s="6"/>
       <c r="F372" s="6" t="s">
-        <v>42</v>
+        <v>632</v>
       </c>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
@@ -12021,9 +12036,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B373" s="6" t="s">
         <v>613</v>
@@ -12036,7 +12051,7 @@
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>635</v>
+        <v>42</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12045,9 +12060,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B374" s="6" t="s">
         <v>613</v>
@@ -12060,7 +12075,7 @@
       </c>
       <c r="E374" s="6"/>
       <c r="F374" s="6" t="s">
-        <v>342</v>
+        <v>635</v>
       </c>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
@@ -12071,7 +12086,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B375" s="6" t="s">
         <v>613</v>
@@ -12084,7 +12099,7 @@
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>638</v>
+        <v>342</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12095,7 +12110,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B376" s="6" t="s">
         <v>613</v>
@@ -12108,7 +12123,7 @@
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12119,7 +12134,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B377" s="6" t="s">
         <v>613</v>
@@ -12132,7 +12147,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12141,33 +12156,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="10" t="s">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A378" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D378" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E378" s="6"/>
+      <c r="F378" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="G378" s="6"/>
+      <c r="H378" s="6"/>
+      <c r="I378" s="6"/>
+      <c r="J378" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="B379" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C379" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D379" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E379" s="6"/>
-      <c r="F379" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="G379" s="6"/>
-      <c r="H379" s="6"/>
-      <c r="I379" s="6"/>
-      <c r="J379" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A380" s="6" t="s">
-        <v>645</v>
       </c>
       <c r="B380" s="6" t="s">
         <v>613</v>
@@ -12180,28 +12195,40 @@
       </c>
       <c r="E380" s="6"/>
       <c r="F380" s="10" t="s">
-        <v>351</v>
+        <v>644</v>
       </c>
       <c r="G380" s="6"/>
       <c r="H380" s="6"/>
-      <c r="I380" s="10" t="s">
-        <v>646</v>
-      </c>
+      <c r="I380" s="6"/>
       <c r="J380" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A381" s="6"/>
-      <c r="B381" s="6"/>
-      <c r="C381" s="6"/>
-      <c r="D381" s="6"/>
+    <row r="381" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A381" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D381" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E381" s="6"/>
-      <c r="F381" s="6"/>
+      <c r="F381" s="10" t="s">
+        <v>351</v>
+      </c>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
-      <c r="I381" s="6"/>
-      <c r="J381" s="6"/>
+      <c r="I381" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J381" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
@@ -12227,43 +12254,43 @@
       <c r="I383" s="6"/>
       <c r="J383" s="6"/>
     </row>
-    <row r="384" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A384" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B384" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C384" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D384" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A384" s="6"/>
+      <c r="B384" s="6"/>
+      <c r="C384" s="6"/>
+      <c r="D384" s="6"/>
       <c r="E384" s="6"/>
-      <c r="F384" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="F384" s="6"/>
       <c r="G384" s="6"/>
       <c r="H384" s="6"/>
-      <c r="I384" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="J384" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A385" s="6"/>
-      <c r="B385" s="6"/>
-      <c r="C385" s="6"/>
-      <c r="D385" s="6"/>
+      <c r="I384" s="6"/>
+      <c r="J384" s="6"/>
+    </row>
+    <row r="385" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A385" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E385" s="6"/>
-      <c r="F385" s="6"/>
+      <c r="F385" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
-      <c r="I385" s="6"/>
-      <c r="J385" s="6"/>
+      <c r="I385" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="J385" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
@@ -12337,43 +12364,43 @@
       <c r="I391" s="6"/>
       <c r="J391" s="6"/>
     </row>
-    <row r="392" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A392" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B392" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C392" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D392" s="6" t="s">
-        <v>650</v>
-      </c>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A392" s="6"/>
+      <c r="B392" s="6"/>
+      <c r="C392" s="6"/>
+      <c r="D392" s="6"/>
       <c r="E392" s="6"/>
-      <c r="F392" s="6" t="s">
-        <v>651</v>
-      </c>
+      <c r="F392" s="6"/>
       <c r="G392" s="6"/>
       <c r="H392" s="6"/>
-      <c r="I392" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="J392" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A393" s="6"/>
-      <c r="B393" s="6"/>
-      <c r="C393" s="6"/>
-      <c r="D393" s="6"/>
+      <c r="I392" s="6"/>
+      <c r="J392" s="6"/>
+    </row>
+    <row r="393" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A393" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E393" s="6"/>
-      <c r="F393" s="6"/>
+      <c r="F393" s="6" t="s">
+        <v>651</v>
+      </c>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
-      <c r="I393" s="6"/>
-      <c r="J393" s="6"/>
+      <c r="I393" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="J393" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="6"/>
@@ -12424,32 +12451,20 @@
       <c r="J397" s="6"/>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A398" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B398" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C398" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D398" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A398" s="6"/>
+      <c r="B398" s="6"/>
+      <c r="C398" s="6"/>
+      <c r="D398" s="6"/>
       <c r="E398" s="6"/>
-      <c r="F398" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="F398" s="6"/>
       <c r="G398" s="6"/>
       <c r="H398" s="6"/>
       <c r="I398" s="6"/>
-      <c r="J398" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J398" s="6"/>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B399" s="6" t="s">
         <v>613</v>
@@ -12462,7 +12477,7 @@
       </c>
       <c r="E399" s="6"/>
       <c r="F399" s="6" t="s">
-        <v>655</v>
+        <v>62</v>
       </c>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
@@ -12471,9 +12486,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>613</v>
@@ -12486,7 +12501,7 @@
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12495,9 +12510,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B401" s="6" t="s">
         <v>613</v>
@@ -12510,7 +12525,7 @@
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12521,7 +12536,7 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B402" s="6" t="s">
         <v>613</v>
@@ -12534,20 +12549,18 @@
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
-      <c r="I402" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I402" s="6"/>
       <c r="J402" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B403" s="6" t="s">
         <v>613</v>
@@ -12560,18 +12573,20 @@
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
-      <c r="I403" s="6"/>
+      <c r="I403" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J403" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B404" s="6" t="s">
         <v>613</v>
@@ -12584,7 +12599,7 @@
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
@@ -12593,9 +12608,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="405" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B405" s="6" t="s">
         <v>613</v>
@@ -12608,7 +12623,7 @@
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12617,9 +12632,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B406" s="6" t="s">
         <v>613</v>
@@ -12632,7 +12647,7 @@
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12643,7 +12658,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B407" s="6" t="s">
         <v>613</v>
@@ -12652,11 +12667,11 @@
         <v>11</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12667,7 +12682,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B408" s="6" t="s">
         <v>613</v>
@@ -12680,7 +12695,7 @@
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
-        <v>97</v>
+        <v>672</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
@@ -12691,7 +12706,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B409" s="6" t="s">
         <v>613</v>
@@ -12704,7 +12719,7 @@
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
@@ -12715,7 +12730,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B410" s="6" t="s">
         <v>613</v>
@@ -12727,8 +12742,8 @@
         <v>671</v>
       </c>
       <c r="E410" s="6"/>
-      <c r="F410" s="10" t="s">
-        <v>676</v>
+      <c r="F410" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12739,7 +12754,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B411" s="6" t="s">
         <v>613</v>
@@ -12751,8 +12766,8 @@
         <v>671</v>
       </c>
       <c r="E411" s="6"/>
-      <c r="F411" s="6" t="s">
-        <v>89</v>
+      <c r="F411" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12763,7 +12778,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B412" s="6" t="s">
         <v>613</v>
@@ -12776,7 +12791,7 @@
       </c>
       <c r="E412" s="6"/>
       <c r="F412" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12787,7 +12802,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>613</v>
@@ -12799,8 +12814,8 @@
         <v>671</v>
       </c>
       <c r="E413" s="6"/>
-      <c r="F413" s="10" t="s">
-        <v>680</v>
+      <c r="F413" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12811,7 +12826,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>613</v>
@@ -12823,8 +12838,8 @@
         <v>671</v>
       </c>
       <c r="E414" s="6"/>
-      <c r="F414" s="6" t="s">
-        <v>93</v>
+      <c r="F414" s="10" t="s">
+        <v>680</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
@@ -12834,16 +12849,28 @@
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A415" s="6"/>
-      <c r="B415" s="6"/>
-      <c r="C415" s="6"/>
-      <c r="D415" s="6"/>
+      <c r="A415" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C415" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D415" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E415" s="6"/>
-      <c r="F415" s="6"/>
+      <c r="F415" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
       <c r="I415" s="6"/>
-      <c r="J415" s="6"/>
+      <c r="J415" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="6"/>
@@ -12882,30 +12909,20 @@
       <c r="J418" s="6"/>
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A419" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B419" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C419" s="10" t="s">
-        <v>399</v>
-      </c>
+      <c r="A419" s="6"/>
+      <c r="B419" s="6"/>
+      <c r="C419" s="6"/>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
-      <c r="F419" s="6" t="s">
-        <v>194</v>
-      </c>
+      <c r="F419" s="6"/>
       <c r="G419" s="6"/>
       <c r="H419" s="6"/>
       <c r="I419" s="6"/>
-      <c r="J419" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J419" s="6"/>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B420" s="6" t="s">
         <v>613</v>
@@ -12916,7 +12933,7 @@
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>684</v>
+        <v>194</v>
       </c>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
@@ -12927,7 +12944,7 @@
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B421" s="6" t="s">
         <v>613</v>
@@ -12938,7 +12955,7 @@
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12949,7 +12966,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B422" s="6" t="s">
         <v>613</v>
@@ -12960,7 +12977,7 @@
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
       <c r="F422" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12971,7 +12988,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B423" s="6" t="s">
         <v>613</v>
@@ -12982,7 +12999,7 @@
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -12993,18 +13010,18 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B424" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C424" s="10" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13015,18 +13032,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B425" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C425" s="6" t="s">
-        <v>585</v>
+      <c r="C425" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13037,7 +13054,7 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B426" s="6" t="s">
         <v>613</v>
@@ -13048,7 +13065,7 @@
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13057,9 +13074,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="427" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B427" s="6" t="s">
         <v>613</v>
@@ -13070,7 +13087,7 @@
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13079,44 +13096,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B428" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C428" s="10" t="s">
-        <v>700</v>
+      <c r="C428" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
-      <c r="I428" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I428" s="6"/>
       <c r="J428" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B429" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C429" s="6" t="s">
-        <v>437</v>
+      <c r="C429" s="10" t="s">
+        <v>700</v>
       </c>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
@@ -13129,7 +13144,7 @@
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B430" s="6" t="s">
         <v>613</v>
@@ -13140,18 +13155,20 @@
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
       <c r="F430" s="6" t="s">
-        <v>412</v>
+        <v>703</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
-      <c r="I430" s="6"/>
+      <c r="I430" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J430" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B431" s="6" t="s">
         <v>613</v>
@@ -13162,28 +13179,38 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
-      <c r="I431" s="10" t="s">
-        <v>926</v>
-      </c>
+      <c r="I431" s="6"/>
       <c r="J431" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A432" s="6"/>
-      <c r="B432" s="6"/>
-      <c r="C432" s="6"/>
+    <row r="432" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A432" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
-      <c r="F432" s="6"/>
+      <c r="F432" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
-      <c r="I432" s="6"/>
-      <c r="J432" s="6"/>
+      <c r="I432" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="J432" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="6"/>
@@ -13234,30 +13261,20 @@
       <c r="J436" s="6"/>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A437" s="6" t="s">
-        <v>706</v>
-      </c>
-      <c r="B437" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C437" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A437" s="6"/>
+      <c r="B437" s="6"/>
+      <c r="C437" s="6"/>
       <c r="D437" s="6"/>
       <c r="E437" s="6"/>
-      <c r="F437" s="6" t="s">
-        <v>707</v>
-      </c>
+      <c r="F437" s="6"/>
       <c r="G437" s="6"/>
       <c r="H437" s="6"/>
       <c r="I437" s="6"/>
-      <c r="J437" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J437" s="6"/>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B438" s="6" t="s">
         <v>613</v>
@@ -13268,7 +13285,7 @@
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
@@ -13279,7 +13296,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B439" s="6" t="s">
         <v>613</v>
@@ -13290,7 +13307,7 @@
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13301,7 +13318,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B440" s="6" t="s">
         <v>613</v>
@@ -13312,7 +13329,7 @@
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13323,7 +13340,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B441" s="6" t="s">
         <v>613</v>
@@ -13334,7 +13351,7 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13345,18 +13362,18 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B442" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13367,7 +13384,7 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B443" s="6" t="s">
         <v>613</v>
@@ -13378,7 +13395,7 @@
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13387,9 +13404,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="444" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B444" s="6" t="s">
         <v>613</v>
@@ -13400,7 +13417,7 @@
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
@@ -13409,9 +13426,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B445" s="6" t="s">
         <v>613</v>
@@ -13422,7 +13439,7 @@
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
       <c r="F445" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
@@ -13431,9 +13448,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B446" s="6" t="s">
         <v>613</v>
@@ -13444,7 +13461,7 @@
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
       <c r="F446" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
@@ -13453,9 +13470,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B447" s="6" t="s">
         <v>613</v>
@@ -13466,7 +13483,7 @@
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
       <c r="F447" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
@@ -13477,7 +13494,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B448" s="6" t="s">
         <v>613</v>
@@ -13488,7 +13505,7 @@
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
       <c r="F448" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
@@ -13497,9 +13514,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B449" s="6" t="s">
         <v>613</v>
@@ -13510,7 +13527,7 @@
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13519,9 +13536,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B450" s="6" t="s">
         <v>613</v>
@@ -13532,7 +13549,7 @@
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13543,7 +13560,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B451" s="6" t="s">
         <v>613</v>
@@ -13554,7 +13571,7 @@
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13563,9 +13580,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B452" s="6" t="s">
         <v>613</v>
@@ -13575,29 +13592,39 @@
       </c>
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
-      <c r="F452" s="10" t="s">
-        <v>737</v>
+      <c r="F452" s="6" t="s">
+        <v>735</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
-      <c r="I452" s="10" t="s">
-        <v>738</v>
-      </c>
+      <c r="I452" s="6"/>
       <c r="J452" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A453" s="6"/>
-      <c r="B453" s="6"/>
-      <c r="C453" s="6"/>
+    <row r="453" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A453" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C453" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="6"/>
+      <c r="F453" s="10" t="s">
+        <v>737</v>
+      </c>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
-      <c r="I453" s="6"/>
-      <c r="J453" s="6"/>
+      <c r="I453" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J453" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="6"/>
@@ -13612,30 +13639,20 @@
       <c r="J454" s="6"/>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A455" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="B455" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C455" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A455" s="6"/>
+      <c r="B455" s="6"/>
+      <c r="C455" s="6"/>
       <c r="D455" s="6"/>
       <c r="E455" s="6"/>
-      <c r="F455" s="6" t="s">
-        <v>740</v>
-      </c>
+      <c r="F455" s="6"/>
       <c r="G455" s="6"/>
       <c r="H455" s="6"/>
       <c r="I455" s="6"/>
-      <c r="J455" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J455" s="6"/>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B456" s="6" t="s">
         <v>613</v>
@@ -13646,7 +13663,7 @@
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
       <c r="F456" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
@@ -13657,7 +13674,7 @@
     </row>
     <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B457" s="6" t="s">
         <v>613</v>
@@ -13668,7 +13685,7 @@
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13677,20 +13694,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B458" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C458" s="10" t="s">
-        <v>746</v>
+      <c r="C458" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13701,7 +13718,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B459" s="6" t="s">
         <v>613</v>
@@ -13712,42 +13729,42 @@
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
-      <c r="I459" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I459" s="6"/>
       <c r="J459" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B460" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C460" s="10" t="s">
-        <v>506</v>
+        <v>746</v>
       </c>
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
-      <c r="I460" s="6"/>
+      <c r="I460" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J460" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B461" s="6" t="s">
         <v>613</v>
@@ -13758,7 +13775,7 @@
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>509</v>
+        <v>751</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -13769,7 +13786,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B462" s="6" t="s">
         <v>613</v>
@@ -13780,7 +13797,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>104</v>
+        <v>509</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -13791,7 +13808,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B463" s="6" t="s">
         <v>613</v>
@@ -13802,7 +13819,7 @@
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
       <c r="F463" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
@@ -13813,7 +13830,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B464" s="6" t="s">
         <v>613</v>
@@ -13823,8 +13840,8 @@
       </c>
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
-      <c r="F464" s="10" t="s">
-        <v>756</v>
+      <c r="F464" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
@@ -13835,7 +13852,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B465" s="6" t="s">
         <v>613</v>
@@ -13845,8 +13862,8 @@
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="6" t="s">
-        <v>110</v>
+      <c r="F465" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
@@ -13857,7 +13874,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B466" s="6" t="s">
         <v>613</v>
@@ -13868,7 +13885,7 @@
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
       <c r="F466" s="6" t="s">
-        <v>759</v>
+        <v>110</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13879,7 +13896,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B467" s="6" t="s">
         <v>613</v>
@@ -13890,7 +13907,7 @@
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13901,7 +13918,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B468" s="6" t="s">
         <v>613</v>
@@ -13912,7 +13929,7 @@
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13921,9 +13938,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="469" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B469" s="6" t="s">
         <v>613</v>
@@ -13934,7 +13951,7 @@
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13943,9 +13960,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B470" s="6" t="s">
         <v>613</v>
@@ -13956,7 +13973,7 @@
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13967,18 +13984,18 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B471" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C471" s="6" t="s">
+      <c r="C471" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
@@ -13989,7 +14006,7 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B472" s="6" t="s">
         <v>613</v>
@@ -14000,7 +14017,7 @@
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -14011,7 +14028,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B473" s="6" t="s">
         <v>613</v>
@@ -14022,7 +14039,7 @@
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14033,7 +14050,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B474" s="6" t="s">
         <v>613</v>
@@ -14044,7 +14061,7 @@
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14055,7 +14072,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B475" s="6" t="s">
         <v>613</v>
@@ -14066,7 +14083,7 @@
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14077,7 +14094,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B476" s="6" t="s">
         <v>613</v>
@@ -14088,7 +14105,7 @@
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
       <c r="F476" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14099,7 +14116,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B477" s="6" t="s">
         <v>613</v>
@@ -14110,7 +14127,7 @@
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14121,7 +14138,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B478" s="6" t="s">
         <v>613</v>
@@ -14132,7 +14149,7 @@
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14143,7 +14160,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B479" s="6" t="s">
         <v>613</v>
@@ -14154,7 +14171,7 @@
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14165,7 +14182,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B480" s="6" t="s">
         <v>613</v>
@@ -14176,7 +14193,7 @@
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14187,7 +14204,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B481" s="6" t="s">
         <v>613</v>
@@ -14198,7 +14215,7 @@
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14209,7 +14226,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B482" s="6" t="s">
         <v>613</v>
@@ -14220,7 +14237,7 @@
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14231,7 +14248,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B483" s="6" t="s">
         <v>613</v>
@@ -14242,7 +14259,7 @@
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14253,7 +14270,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B484" s="6" t="s">
         <v>613</v>
@@ -14264,7 +14281,7 @@
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>541</v>
+        <v>793</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14275,7 +14292,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B485" s="6" t="s">
         <v>613</v>
@@ -14286,7 +14303,7 @@
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>796</v>
+        <v>541</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14297,7 +14314,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B486" s="6" t="s">
         <v>613</v>
@@ -14308,7 +14325,7 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14317,41 +14334,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="487" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B487" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C487" s="10" t="s">
+      <c r="C487" s="6" t="s">
         <v>506</v>
       </c>
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
-      <c r="F487" s="10" t="s">
-        <v>800</v>
+      <c r="F487" s="6" t="s">
+        <v>798</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
-      <c r="I487" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I487" s="6"/>
       <c r="J487" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A488" s="6"/>
-      <c r="B488" s="6"/>
-      <c r="C488" s="6"/>
+    <row r="488" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A488" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B488" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C488" s="10" t="s">
+        <v>506</v>
+      </c>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="6"/>
+      <c r="F488" s="10" t="s">
+        <v>800</v>
+      </c>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
-      <c r="I488" s="6"/>
-      <c r="J488" s="6"/>
+      <c r="I488" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J488" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="6"/>
@@ -14594,30 +14621,20 @@
       <c r="J508" s="6"/>
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A509" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="B509" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C509" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A509" s="6"/>
+      <c r="B509" s="6"/>
+      <c r="C509" s="6"/>
       <c r="D509" s="6"/>
       <c r="E509" s="6"/>
-      <c r="F509" s="6" t="s">
-        <v>803</v>
-      </c>
+      <c r="F509" s="6"/>
       <c r="G509" s="6"/>
       <c r="H509" s="6"/>
       <c r="I509" s="6"/>
-      <c r="J509" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="510" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J509" s="6"/>
+    </row>
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B510" s="6" t="s">
         <v>613</v>
@@ -14628,7 +14645,7 @@
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
       <c r="F510" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
@@ -14637,9 +14654,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B511" s="6" t="s">
         <v>613</v>
@@ -14650,7 +14667,7 @@
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
       <c r="F511" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
@@ -14661,7 +14678,7 @@
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B512" s="6" t="s">
         <v>613</v>
@@ -14672,7 +14689,7 @@
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
       <c r="F512" s="6" t="s">
-        <v>425</v>
+        <v>807</v>
       </c>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
@@ -14681,41 +14698,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="513" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B513" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C513" s="10" t="s">
+      <c r="C513" s="6" t="s">
         <v>524</v>
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
-      <c r="F513" s="10" t="s">
-        <v>810</v>
+      <c r="F513" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
-      <c r="I513" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I513" s="6"/>
       <c r="J513" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A514" s="6"/>
-      <c r="B514" s="6"/>
-      <c r="C514" s="6"/>
+    <row r="514" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A514" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B514" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C514" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="6"/>
+      <c r="F514" s="10" t="s">
+        <v>810</v>
+      </c>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
-      <c r="I514" s="6"/>
-      <c r="J514" s="6"/>
+      <c r="I514" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J514" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="6"/>
@@ -14957,41 +14984,41 @@
       <c r="I534" s="6"/>
       <c r="J534" s="6"/>
     </row>
-    <row r="535" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A535" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="B535" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C535" s="10" t="s">
-        <v>524</v>
-      </c>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A535" s="6"/>
+      <c r="B535" s="6"/>
+      <c r="C535" s="6"/>
       <c r="D535" s="6"/>
       <c r="E535" s="6"/>
-      <c r="F535" s="10" t="s">
-        <v>812</v>
-      </c>
+      <c r="F535" s="6"/>
       <c r="G535" s="6"/>
       <c r="H535" s="6"/>
-      <c r="I535" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J535" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A536" s="6"/>
-      <c r="B536" s="6"/>
-      <c r="C536" s="6"/>
+      <c r="I535" s="6"/>
+      <c r="J535" s="6"/>
+    </row>
+    <row r="536" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A536" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B536" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C536" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="6"/>
+      <c r="F536" s="10" t="s">
+        <v>812</v>
+      </c>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
-      <c r="I536" s="6"/>
-      <c r="J536" s="6"/>
+      <c r="I536" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="J536" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="6"/>
@@ -15078,30 +15105,20 @@
       <c r="J543" s="6"/>
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A544" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="B544" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C544" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A544" s="6"/>
+      <c r="B544" s="6"/>
+      <c r="C544" s="6"/>
       <c r="D544" s="6"/>
       <c r="E544" s="6"/>
-      <c r="F544" s="6" t="s">
-        <v>814</v>
-      </c>
+      <c r="F544" s="6"/>
       <c r="G544" s="6"/>
       <c r="H544" s="6"/>
       <c r="I544" s="6"/>
-      <c r="J544" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="545" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J544" s="6"/>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B545" s="6" t="s">
         <v>613</v>
@@ -15112,7 +15129,7 @@
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
       <c r="F545" s="6" t="s">
-        <v>206</v>
+        <v>814</v>
       </c>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
@@ -15123,7 +15140,7 @@
     </row>
     <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B546" s="6" t="s">
         <v>613</v>
@@ -15134,7 +15151,7 @@
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>817</v>
+        <v>206</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15143,9 +15160,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B547" s="6" t="s">
         <v>613</v>
@@ -15156,7 +15173,7 @@
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
       <c r="F547" s="6" t="s">
-        <v>210</v>
+        <v>817</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
@@ -15167,7 +15184,7 @@
     </row>
     <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B548" s="6" t="s">
         <v>613</v>
@@ -15178,7 +15195,7 @@
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="6" t="s">
-        <v>820</v>
+        <v>210</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
@@ -15189,7 +15206,7 @@
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B549" s="6" t="s">
         <v>613</v>
@@ -15200,7 +15217,7 @@
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
       <c r="F549" s="6" t="s">
-        <v>717</v>
+        <v>820</v>
       </c>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
@@ -15209,9 +15226,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="550" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B550" s="6" t="s">
         <v>613</v>
@@ -15221,88 +15238,110 @@
       </c>
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
-      <c r="F550" s="10" t="s">
-        <v>823</v>
+      <c r="F550" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
-      <c r="I550" s="10" t="s">
-        <v>824</v>
-      </c>
+      <c r="I550" s="6"/>
       <c r="J550" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A551" s="6"/>
-      <c r="B551" s="6"/>
-      <c r="C551" s="6"/>
+    <row r="551" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A551" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="B551" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C551" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="6"/>
+      <c r="F551" s="10" t="s">
+        <v>823</v>
+      </c>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
-      <c r="I551" s="6"/>
-      <c r="J551" s="6"/>
+      <c r="I551" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="J551" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A552" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="B552" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C552" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A552" s="6"/>
+      <c r="B552" s="6"/>
+      <c r="C552" s="6"/>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
-      <c r="F552" s="6" t="s">
-        <v>826</v>
-      </c>
+      <c r="F552" s="6"/>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
       <c r="I552" s="6"/>
-      <c r="J552" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="553" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="J552" s="6"/>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B553" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>828</v>
+        <v>524</v>
       </c>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
       <c r="F553" s="6" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
-      <c r="I553" s="10" t="s">
+      <c r="I553" s="6"/>
+      <c r="J553" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A554" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B554" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C554" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D554" s="6"/>
+      <c r="E554" s="6"/>
+      <c r="F554" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="G554" s="6"/>
+      <c r="H554" s="6"/>
+      <c r="I554" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="J553" s="6" t="s">
+      <c r="J554" s="6" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H377 H379:H946" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H380:H947 H2:H378" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J377 J379:J946" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J380:J947 J2:J378" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C487:C508 C513:C543 C419:C424 C428 C432:C436 C554:C946 C2:C377 C458:C470 C379:C414" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798EA734-DBAD-4125-A394-7790864A913D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E343CC8-E0DB-418E-8C24-E0F6C5A58064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="929">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2986,10 +2986,7 @@
     <t>BR-0112</t>
   </si>
   <si>
-    <t>Block Tray Layout</t>
-  </si>
-  <si>
-    <t>(Keyword: Chock)</t>
+    <t>BLOCK TRAY LAYOUT - CHOCKS</t>
   </si>
 </sst>
 </file>
@@ -5026,9 +5023,7 @@
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5" t="s">
-        <v>929</v>
-      </c>
+      <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
         <v>14</v>
       </c>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E343CC8-E0DB-418E-8C24-E0F6C5A58064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EEFE29-C15E-4A4A-BD8E-B35E39FE99B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="932">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2987,6 +2987,15 @@
   </si>
   <si>
     <t>BLOCK TRAY LAYOUT - CHOCKS</t>
+  </si>
+  <si>
+    <t>test edit</t>
+  </si>
+  <si>
+    <t>test add</t>
+  </si>
+  <si>
+    <t>BR-1136</t>
   </si>
 </sst>
 </file>
@@ -3319,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P554"/>
+  <dimension ref="A1:P555"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3393,7 +3402,9 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>929</v>
+      </c>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
@@ -3406,7 +3417,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>931</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -3419,11 +3430,13 @@
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>16</v>
+        <v>930</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>929</v>
+      </c>
       <c r="J3" s="5" t="s">
         <v>14</v>
       </c>
@@ -3436,7 +3449,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>10</v>
@@ -3449,7 +3462,7 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -3466,7 +3479,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>10</v>
@@ -3475,11 +3488,11 @@
         <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -3496,7 +3509,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>
@@ -3509,7 +3522,7 @@
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -3526,7 +3539,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>10</v>
@@ -3539,7 +3552,7 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -3556,7 +3569,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>10</v>
@@ -3569,7 +3582,7 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -3586,7 +3599,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
@@ -3599,7 +3612,7 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -3616,7 +3629,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
@@ -3629,7 +3642,7 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -3646,7 +3659,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
@@ -3659,7 +3672,7 @@
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -3676,7 +3689,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
@@ -3689,7 +3702,7 @@
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -3706,7 +3719,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
@@ -3715,11 +3728,11 @@
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3736,7 +3749,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
@@ -3749,7 +3762,7 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -3766,7 +3779,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
@@ -3779,7 +3792,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -3796,7 +3809,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
@@ -3809,7 +3822,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -3826,7 +3839,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
@@ -3839,7 +3852,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -3856,7 +3869,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
@@ -3869,7 +3882,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -3886,7 +3899,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
@@ -3899,7 +3912,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -3916,7 +3929,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
@@ -3929,7 +3942,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -3944,9 +3957,9 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
@@ -3959,13 +3972,11 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
         <v>14</v>
       </c>
@@ -3976,9 +3987,9 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
@@ -3987,15 +3998,17 @@
         <v>11</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="J22" s="5" t="s">
         <v>14</v>
       </c>
@@ -4008,7 +4021,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
@@ -4021,7 +4034,7 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -4038,7 +4051,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
@@ -4051,7 +4064,7 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -4068,7 +4081,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
@@ -4081,7 +4094,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -4098,7 +4111,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
@@ -4111,7 +4124,7 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -4128,7 +4141,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -4141,7 +4154,7 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -4158,7 +4171,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
@@ -4171,7 +4184,7 @@
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -4188,7 +4201,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
@@ -4201,7 +4214,7 @@
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -4218,7 +4231,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
@@ -4231,7 +4244,7 @@
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -4248,7 +4261,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
@@ -4261,7 +4274,7 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -4278,7 +4291,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
@@ -4291,7 +4304,7 @@
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -4308,7 +4321,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
@@ -4321,7 +4334,7 @@
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -4338,7 +4351,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
@@ -4351,7 +4364,7 @@
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -4368,7 +4381,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
@@ -4381,7 +4394,7 @@
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -4398,7 +4411,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
@@ -4411,7 +4424,7 @@
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -4426,9 +4439,9 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
@@ -4441,13 +4454,11 @@
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
         <v>14</v>
       </c>
@@ -4458,9 +4469,9 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
@@ -4473,11 +4484,13 @@
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="J38" s="5" t="s">
         <v>14</v>
       </c>
@@ -4490,7 +4503,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
@@ -4503,7 +4516,7 @@
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4520,7 +4533,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
@@ -4533,7 +4546,7 @@
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4550,7 +4563,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
@@ -4563,7 +4576,7 @@
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4580,7 +4593,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
@@ -4593,7 +4606,7 @@
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -4610,7 +4623,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
@@ -4623,7 +4636,7 @@
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4640,7 +4653,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>10</v>
@@ -4653,7 +4666,7 @@
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4670,7 +4683,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>10</v>
@@ -4683,7 +4696,7 @@
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4700,18 +4713,20 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4728,7 +4743,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>10</v>
@@ -4739,7 +4754,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4756,7 +4771,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>10</v>
@@ -4767,7 +4782,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4784,7 +4799,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>10</v>
@@ -4795,7 +4810,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4812,7 +4827,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>10</v>
@@ -4823,7 +4838,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4840,7 +4855,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>10</v>
@@ -4851,7 +4866,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4868,7 +4883,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>10</v>
@@ -4879,7 +4894,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4896,7 +4911,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
@@ -4907,7 +4922,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4924,7 +4939,7 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>10</v>
@@ -4935,7 +4950,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4952,7 +4967,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>10</v>
@@ -4963,7 +4978,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4980,7 +4995,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
@@ -4991,7 +5006,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -5008,18 +5023,18 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>927</v>
+        <v>123</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>928</v>
+        <v>124</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5036,7 +5051,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>125</v>
+        <v>927</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
@@ -5044,12 +5059,10 @@
       <c r="C58" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>128</v>
+        <v>928</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -5066,7 +5079,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
@@ -5079,7 +5092,7 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5096,7 +5109,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
@@ -5109,7 +5122,7 @@
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5126,7 +5139,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
@@ -5139,7 +5152,7 @@
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5156,7 +5169,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
@@ -5169,7 +5182,7 @@
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5186,7 +5199,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
@@ -5199,7 +5212,7 @@
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5216,7 +5229,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
@@ -5229,7 +5242,7 @@
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -5246,7 +5259,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
@@ -5255,11 +5268,11 @@
         <v>126</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -5276,7 +5289,7 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
@@ -5289,7 +5302,7 @@
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5306,7 +5319,7 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
@@ -5319,7 +5332,7 @@
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5336,7 +5349,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
@@ -5349,7 +5362,7 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5366,7 +5379,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
@@ -5375,11 +5388,11 @@
         <v>126</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5396,7 +5409,7 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -5409,7 +5422,7 @@
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5426,7 +5439,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
@@ -5435,11 +5448,11 @@
         <v>126</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5456,7 +5469,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
@@ -5469,7 +5482,7 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5486,7 +5499,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
@@ -5499,7 +5512,7 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5516,7 +5529,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
@@ -5529,7 +5542,7 @@
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5546,7 +5559,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
@@ -5559,7 +5572,7 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5576,7 +5589,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
@@ -5589,7 +5602,7 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5606,7 +5619,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
@@ -5619,7 +5632,7 @@
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5636,7 +5649,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
@@ -5645,11 +5658,11 @@
         <v>126</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5666,7 +5679,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
@@ -5679,7 +5692,7 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5696,7 +5709,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
@@ -5709,7 +5722,7 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5726,7 +5739,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
@@ -5739,7 +5752,7 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5756,7 +5769,7 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
@@ -5769,7 +5782,7 @@
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5786,18 +5799,20 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D83" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5814,18 +5829,18 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5842,7 +5857,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
@@ -5853,7 +5868,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5870,7 +5885,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
@@ -5881,7 +5896,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5898,7 +5913,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>10</v>
@@ -5909,7 +5924,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5926,7 +5941,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
@@ -5937,7 +5952,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5954,7 +5969,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>10</v>
@@ -5965,7 +5980,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5982,7 +5997,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>10</v>
@@ -5993,7 +6008,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -6010,7 +6025,7 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>10</v>
@@ -6021,7 +6036,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -6038,7 +6053,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>10</v>
@@ -6049,7 +6064,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6066,7 +6081,7 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
@@ -6077,7 +6092,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -6092,9 +6107,9 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>10</v>
@@ -6105,7 +6120,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -6120,9 +6135,9 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>10</v>
@@ -6133,7 +6148,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -6150,7 +6165,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>10</v>
@@ -6161,7 +6176,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -6178,7 +6193,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>10</v>
@@ -6189,7 +6204,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -6206,7 +6221,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>10</v>
@@ -6217,7 +6232,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -6234,7 +6249,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>10</v>
@@ -6245,7 +6260,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -6262,7 +6277,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
@@ -6273,7 +6288,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -6290,7 +6305,7 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>10</v>
@@ -6301,7 +6316,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -6318,7 +6333,7 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
@@ -6329,7 +6344,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -6346,7 +6361,7 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
@@ -6357,7 +6372,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -6374,7 +6389,7 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
@@ -6385,7 +6400,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -6402,7 +6417,7 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
@@ -6413,7 +6428,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -6430,7 +6445,7 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
@@ -6441,7 +6456,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -6458,7 +6473,7 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
@@ -6469,7 +6484,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6486,7 +6501,7 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -6497,7 +6512,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6514,7 +6529,7 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -6525,7 +6540,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -6540,9 +6555,9 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -6553,13 +6568,11 @@
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
-      <c r="I110" s="5" t="s">
-        <v>239</v>
-      </c>
+      <c r="I110" s="5"/>
       <c r="J110" s="5" t="s">
         <v>14</v>
       </c>
@@ -6570,9 +6583,9 @@
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
@@ -6583,12 +6596,12 @@
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5" t="s">
-        <v>923</v>
+        <v>239</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>14</v>
@@ -6602,24 +6615,24 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>244</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D112" s="5"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
+      <c r="I112" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="J112" s="5" t="s">
         <v>14</v>
       </c>
@@ -6632,7 +6645,7 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
@@ -6645,7 +6658,7 @@
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6662,7 +6675,7 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>10</v>
@@ -6675,7 +6688,7 @@
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6692,7 +6705,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>10</v>
@@ -6705,7 +6718,7 @@
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6722,7 +6735,7 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
@@ -6735,7 +6748,7 @@
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6750,9 +6763,9 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>10</v>
@@ -6765,7 +6778,7 @@
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6780,9 +6793,9 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>10</v>
@@ -6791,11 +6804,11 @@
         <v>243</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6812,7 +6825,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>10</v>
@@ -6825,7 +6838,7 @@
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6842,7 +6855,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>10</v>
@@ -6855,7 +6868,7 @@
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -6872,7 +6885,7 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
@@ -6885,7 +6898,7 @@
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
@@ -6902,7 +6915,7 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
@@ -6915,7 +6928,7 @@
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
@@ -6932,7 +6945,7 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>10</v>
@@ -6945,7 +6958,7 @@
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
@@ -6962,7 +6975,7 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
@@ -6975,7 +6988,7 @@
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -6992,7 +7005,7 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
@@ -7005,7 +7018,7 @@
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -7022,7 +7035,7 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>10</v>
@@ -7035,7 +7048,7 @@
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -7052,7 +7065,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>10</v>
@@ -7065,7 +7078,7 @@
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -7082,7 +7095,7 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>10</v>
@@ -7095,7 +7108,7 @@
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
@@ -7110,9 +7123,9 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>10</v>
@@ -7121,17 +7134,15 @@
         <v>243</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
-      <c r="I129" s="5" t="s">
-        <v>282</v>
-      </c>
+      <c r="I129" s="5"/>
       <c r="J129" s="5" t="s">
         <v>14</v>
       </c>
@@ -7142,9 +7153,9 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>10</v>
@@ -7157,11 +7168,13 @@
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
-      <c r="I130" s="5"/>
+      <c r="I130" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="J130" s="5" t="s">
         <v>14</v>
       </c>
@@ -7174,7 +7187,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>10</v>
@@ -7187,7 +7200,7 @@
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -7204,7 +7217,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>10</v>
@@ -7217,7 +7230,7 @@
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -7234,7 +7247,7 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>10</v>
@@ -7247,7 +7260,7 @@
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -7262,9 +7275,9 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>10</v>
@@ -7277,7 +7290,7 @@
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7292,9 +7305,9 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>10</v>
@@ -7307,7 +7320,7 @@
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7324,18 +7337,20 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D136" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7352,7 +7367,7 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
@@ -7363,7 +7378,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7380,7 +7395,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -7391,7 +7406,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -7408,7 +7423,7 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -7419,7 +7434,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7436,7 +7451,7 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -7447,7 +7462,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7464,7 +7479,7 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -7475,7 +7490,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7492,7 +7507,7 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -7503,7 +7518,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7520,7 +7535,7 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -7531,7 +7546,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -7548,7 +7563,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -7559,7 +7574,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7576,7 +7591,7 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -7587,7 +7602,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7604,7 +7619,7 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -7615,7 +7630,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -7632,7 +7647,7 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>10</v>
@@ -7643,7 +7658,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -7658,51 +7673,55 @@
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
     </row>
-    <row r="148" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="7"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-      <c r="H148" s="7"/>
-      <c r="I148" s="7"/>
-      <c r="J148" s="7"/>
-      <c r="K148" s="7"/>
-      <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
-      <c r="N148" s="7"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="7"/>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A149" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5"/>
+      <c r="P148" s="5"/>
+    </row>
+    <row r="149" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+      <c r="M149" s="7"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="7"/>
+      <c r="P149" s="7"/>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>321</v>
@@ -7715,7 +7734,7 @@
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -7726,7 +7745,7 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>321</v>
@@ -7739,7 +7758,7 @@
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -7750,7 +7769,7 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>321</v>
@@ -7759,11 +7778,11 @@
         <v>11</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -7774,7 +7793,7 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>321</v>
@@ -7787,7 +7806,7 @@
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -7798,7 +7817,7 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>321</v>
@@ -7811,7 +7830,7 @@
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -7822,7 +7841,7 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>321</v>
@@ -7835,7 +7854,7 @@
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -7846,7 +7865,7 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>321</v>
@@ -7859,7 +7878,7 @@
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -7870,7 +7889,7 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>321</v>
@@ -7883,7 +7902,7 @@
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -7894,7 +7913,7 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>321</v>
@@ -7907,7 +7926,7 @@
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -7918,7 +7937,7 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>321</v>
@@ -7931,7 +7950,7 @@
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>42</v>
+        <v>337</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -7942,7 +7961,7 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>321</v>
@@ -7955,7 +7974,7 @@
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>340</v>
+        <v>42</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7966,7 +7985,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
@@ -7979,7 +7998,7 @@
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -7990,7 +8009,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>321</v>
@@ -8003,7 +8022,7 @@
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8014,7 +8033,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>321</v>
@@ -8027,7 +8046,7 @@
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8038,7 +8057,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>321</v>
@@ -8051,7 +8070,7 @@
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8062,7 +8081,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>321</v>
@@ -8075,7 +8094,7 @@
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>44</v>
+        <v>348</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
@@ -8084,9 +8103,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>321</v>
@@ -8099,28 +8118,40 @@
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>351</v>
+        <v>44</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="6" t="s">
-        <v>352</v>
-      </c>
+      <c r="I166" s="6"/>
       <c r="J166" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
+    <row r="167" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
+      <c r="F167" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
+      <c r="I167" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
@@ -8170,43 +8201,43 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A172" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" s="6"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6"/>
       <c r="E172" s="6"/>
-      <c r="F172" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="J172" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
+      <c r="I172" s="6"/>
+      <c r="J172" s="6"/>
+    </row>
+    <row r="173" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A173" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
+      <c r="I173" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J173" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
@@ -8257,32 +8288,20 @@
       <c r="J177" s="6"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C178" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="6" t="s">
-        <v>356</v>
-      </c>
+      <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
-      <c r="J178" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J178" s="6"/>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>321</v>
@@ -8295,7 +8314,7 @@
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -8306,7 +8325,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>321</v>
@@ -8319,7 +8338,7 @@
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -8330,7 +8349,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>321</v>
@@ -8343,7 +8362,7 @@
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
@@ -8352,9 +8371,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>321</v>
@@ -8365,29 +8384,41 @@
       <c r="D182" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="E182" s="6"/>
       <c r="F182" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="I182" s="6"/>
       <c r="J182" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
+    <row r="183" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
+      <c r="I183" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
@@ -8438,32 +8469,20 @@
       <c r="J187" s="6"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A188" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C188" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>367</v>
-      </c>
+      <c r="A188" s="6"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="6" t="s">
-        <v>368</v>
-      </c>
+      <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
-      <c r="J188" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J188" s="6"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>321</v>
@@ -8476,7 +8495,7 @@
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
@@ -8487,7 +8506,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>321</v>
@@ -8500,20 +8519,18 @@
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I190" s="6"/>
       <c r="J190" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>321</v>
@@ -8526,18 +8543,20 @@
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
+      <c r="I191" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J191" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>321</v>
@@ -8550,7 +8569,7 @@
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8559,9 +8578,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>321</v>
@@ -8574,7 +8593,7 @@
       </c>
       <c r="E193" s="6"/>
       <c r="F193" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -8585,7 +8604,7 @@
     </row>
     <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>321</v>
@@ -8598,7 +8617,7 @@
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -8609,7 +8628,7 @@
     </row>
     <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>321</v>
@@ -8622,7 +8641,7 @@
       </c>
       <c r="E195" s="6"/>
       <c r="F195" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -8631,9 +8650,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>321</v>
@@ -8646,7 +8665,7 @@
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -8657,7 +8676,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>321</v>
@@ -8670,7 +8689,7 @@
       </c>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -8681,7 +8700,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>321</v>
@@ -8694,7 +8713,7 @@
       </c>
       <c r="E198" s="6"/>
       <c r="F198" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -8705,7 +8724,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>321</v>
@@ -8718,7 +8737,7 @@
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8729,7 +8748,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>321</v>
@@ -8742,7 +8761,7 @@
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>387</v>
+        <v>97</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8753,7 +8772,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>321</v>
@@ -8766,7 +8785,7 @@
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>93</v>
+        <v>387</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -8777,7 +8796,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>321</v>
@@ -8790,7 +8809,7 @@
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>390</v>
+        <v>93</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8801,7 +8820,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>321</v>
@@ -8814,7 +8833,7 @@
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8825,7 +8844,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>321</v>
@@ -8838,7 +8857,7 @@
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>76</v>
+        <v>392</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8849,7 +8868,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>321</v>
@@ -8862,7 +8881,7 @@
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>395</v>
+        <v>76</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8873,7 +8892,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>321</v>
@@ -8886,7 +8905,7 @@
       </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
@@ -8897,31 +8916,31 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D207" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="6" t="s">
-        <v>401</v>
-      </c>
+      <c r="I207" s="6"/>
       <c r="J207" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>321</v>
@@ -8932,18 +8951,20 @@
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
+      <c r="I208" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="J208" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>321</v>
@@ -8954,7 +8975,7 @@
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8965,18 +8986,18 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -8985,9 +9006,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>321</v>
@@ -8998,7 +9019,7 @@
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -9007,9 +9028,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>321</v>
@@ -9020,7 +9041,7 @@
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
@@ -9029,9 +9050,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>321</v>
@@ -9040,29 +9061,39 @@
         <v>407</v>
       </c>
       <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
       <c r="F213" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="6" t="s">
-        <v>415</v>
-      </c>
+      <c r="I213" s="6"/>
       <c r="J213" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="6"/>
+    <row r="214" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A214" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="D214" s="6"/>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
+      <c r="F214" s="6" t="s">
+        <v>414</v>
+      </c>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
-      <c r="I214" s="6"/>
-      <c r="J214" s="6"/>
+      <c r="I214" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="J214" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
@@ -9149,30 +9180,20 @@
       <c r="J221" s="6"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A222" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>407</v>
-      </c>
+      <c r="A222" s="6"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="6"/>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="6" t="s">
-        <v>417</v>
-      </c>
+      <c r="F222" s="6"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
-      <c r="J222" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J222" s="6"/>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>321</v>
@@ -9183,7 +9204,7 @@
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9194,7 +9215,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>321</v>
@@ -9205,7 +9226,7 @@
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
@@ -9216,7 +9237,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>321</v>
@@ -9227,7 +9248,7 @@
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
@@ -9238,7 +9259,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>321</v>
@@ -9249,7 +9270,7 @@
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
@@ -9260,7 +9281,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>321</v>
@@ -9271,20 +9292,18 @@
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="6" t="s">
-        <v>924</v>
-      </c>
+      <c r="I227" s="6"/>
       <c r="J227" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>321</v>
@@ -9295,18 +9314,20 @@
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
-      <c r="I228" s="6"/>
+      <c r="I228" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J228" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>321</v>
@@ -9317,7 +9338,7 @@
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
@@ -9328,7 +9349,7 @@
     </row>
     <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>321</v>
@@ -9339,7 +9360,7 @@
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
@@ -9348,9 +9369,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>321</v>
@@ -9361,7 +9382,7 @@
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
@@ -9372,18 +9393,18 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -9394,7 +9415,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>321</v>
@@ -9405,7 +9426,7 @@
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
@@ -9416,7 +9437,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>321</v>
@@ -9427,20 +9448,18 @@
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
-      <c r="I234" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I234" s="6"/>
       <c r="J234" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>321</v>
@@ -9451,7 +9470,7 @@
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
@@ -9464,7 +9483,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>321</v>
@@ -9475,18 +9494,20 @@
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
-      <c r="I236" s="6"/>
+      <c r="I236" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J236" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>321</v>
@@ -9497,7 +9518,7 @@
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9506,9 +9527,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>321</v>
@@ -9519,7 +9540,7 @@
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
@@ -9530,7 +9551,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>321</v>
@@ -9541,7 +9562,7 @@
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9552,7 +9573,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>321</v>
@@ -9563,7 +9584,7 @@
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
@@ -9574,7 +9595,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>321</v>
@@ -9585,20 +9606,18 @@
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
-      <c r="I241" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I241" s="6"/>
       <c r="J241" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>321</v>
@@ -9609,7 +9628,7 @@
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
@@ -9620,9 +9639,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>321</v>
@@ -9633,28 +9652,40 @@
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
       <c r="I243" s="6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J243" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="6"/>
+    <row r="244" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A244" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
+      <c r="F244" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
-      <c r="I244" s="6"/>
-      <c r="J244" s="6"/>
+      <c r="I244" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="J244" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
@@ -9716,31 +9747,21 @@
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
     </row>
-    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A250" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C250" s="6" t="s">
-        <v>462</v>
-      </c>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A250" s="6"/>
+      <c r="B250" s="6"/>
+      <c r="C250" s="6"/>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
-      <c r="F250" s="6" t="s">
-        <v>463</v>
-      </c>
+      <c r="F250" s="6"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
-      <c r="J250" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J250" s="6"/>
+    </row>
+    <row r="251" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
@@ -9751,7 +9772,7 @@
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
@@ -9760,9 +9781,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>321</v>
@@ -9771,29 +9792,39 @@
         <v>462</v>
       </c>
       <c r="D252" s="6"/>
+      <c r="E252" s="6"/>
       <c r="F252" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
-      <c r="I252" s="6" t="s">
-        <v>468</v>
-      </c>
+      <c r="I252" s="6"/>
       <c r="J252" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="6"/>
+    <row r="253" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A253" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D253" s="6"/>
-      <c r="E253" s="6"/>
-      <c r="F253" s="6"/>
+      <c r="F253" s="6" t="s">
+        <v>467</v>
+      </c>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
-      <c r="I253" s="6"/>
-      <c r="J253" s="6"/>
+      <c r="I253" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J253" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
@@ -9820,30 +9851,20 @@
       <c r="J255" s="6"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A256" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C256" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="6"/>
+      <c r="C256" s="6"/>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="F256" s="6"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
-      <c r="J256" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J256" s="6"/>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>321</v>
@@ -9854,7 +9875,7 @@
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9865,7 +9886,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>321</v>
@@ -9876,7 +9897,7 @@
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9885,9 +9906,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>321</v>
@@ -9898,7 +9919,7 @@
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9909,7 +9930,7 @@
     </row>
     <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>321</v>
@@ -9920,7 +9941,7 @@
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9929,9 +9950,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
@@ -9942,7 +9963,7 @@
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9951,9 +9972,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
@@ -9964,7 +9985,7 @@
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9975,7 +9996,7 @@
     </row>
     <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
@@ -9986,7 +10007,7 @@
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -9997,7 +10018,7 @@
     </row>
     <row r="264" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>321</v>
@@ -10008,7 +10029,7 @@
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -10017,9 +10038,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>321</v>
@@ -10030,7 +10051,7 @@
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
@@ -10041,7 +10062,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>321</v>
@@ -10052,7 +10073,7 @@
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10063,7 +10084,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
@@ -10074,7 +10095,7 @@
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10083,9 +10104,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
@@ -10096,7 +10117,7 @@
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10105,9 +10126,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
@@ -10118,7 +10139,7 @@
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10129,18 +10150,18 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10151,7 +10172,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
@@ -10162,7 +10183,7 @@
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10173,7 +10194,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
@@ -10184,7 +10205,7 @@
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10195,18 +10216,18 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10217,7 +10238,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
@@ -10228,7 +10249,7 @@
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10239,7 +10260,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
@@ -10250,7 +10271,7 @@
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
@@ -10261,7 +10282,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
@@ -10272,7 +10293,7 @@
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>108</v>
+        <v>511</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10283,7 +10304,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
@@ -10294,7 +10315,7 @@
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10305,7 +10326,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
@@ -10316,7 +10337,7 @@
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10327,7 +10348,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
@@ -10338,7 +10359,7 @@
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10349,7 +10370,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
@@ -10360,7 +10381,7 @@
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10371,7 +10392,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
@@ -10382,7 +10403,7 @@
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
@@ -10391,66 +10412,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D282" s="6"/>
+      <c r="E282" s="6"/>
       <c r="F282" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="6" t="s">
-        <v>526</v>
-      </c>
+      <c r="I282" s="6"/>
       <c r="J282" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A283" s="6"/>
-      <c r="B283" s="6"/>
-      <c r="C283" s="6"/>
+    <row r="283" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A283" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D283" s="6"/>
-      <c r="E283" s="6"/>
-      <c r="F283" s="6"/>
+      <c r="F283" s="6" t="s">
+        <v>525</v>
+      </c>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
-      <c r="I283" s="6"/>
-      <c r="J283" s="6"/>
-    </row>
-    <row r="284" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A284" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="I283" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A284" s="6"/>
+      <c r="B284" s="6"/>
+      <c r="C284" s="6"/>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
-      <c r="F284" s="6" t="s">
-        <v>528</v>
-      </c>
+      <c r="F284" s="6"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
-      <c r="J284" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J284" s="6"/>
+    </row>
+    <row r="285" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
@@ -10461,7 +10482,7 @@
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10472,7 +10493,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
@@ -10483,7 +10504,7 @@
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10494,18 +10515,18 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10516,7 +10537,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
@@ -10527,7 +10548,7 @@
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10538,7 +10559,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
@@ -10549,7 +10570,7 @@
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10560,7 +10581,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
@@ -10571,7 +10592,7 @@
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10582,7 +10603,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
@@ -10593,7 +10614,7 @@
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10602,9 +10623,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
@@ -10615,7 +10636,7 @@
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10624,9 +10645,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
@@ -10637,7 +10658,7 @@
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
@@ -10648,7 +10669,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>321</v>
@@ -10659,7 +10680,7 @@
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
@@ -10670,7 +10691,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
@@ -10681,7 +10702,7 @@
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
@@ -10690,9 +10711,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>321</v>
@@ -10701,29 +10722,39 @@
         <v>534</v>
       </c>
       <c r="D296" s="6"/>
+      <c r="E296" s="6"/>
       <c r="F296" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="6" t="s">
-        <v>554</v>
-      </c>
+      <c r="I296" s="6"/>
       <c r="J296" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A297" s="6"/>
-      <c r="B297" s="6"/>
-      <c r="C297" s="6"/>
+    <row r="297" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A297" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D297" s="6"/>
-      <c r="E297" s="6"/>
-      <c r="F297" s="6"/>
+      <c r="F297" s="6" t="s">
+        <v>553</v>
+      </c>
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
-      <c r="I297" s="6"/>
-      <c r="J297" s="6"/>
+      <c r="I297" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="J297" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
@@ -10773,41 +10804,41 @@
       <c r="I301" s="6"/>
       <c r="J301" s="6"/>
     </row>
-    <row r="302" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A302" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="B302" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C302" s="6" t="s">
-        <v>534</v>
-      </c>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" s="6"/>
+      <c r="B302" s="6"/>
+      <c r="C302" s="6"/>
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
-      <c r="F302" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="F302" s="6"/>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
-      <c r="I302" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="J302" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A303" s="6"/>
-      <c r="B303" s="6"/>
-      <c r="C303" s="6"/>
+      <c r="I302" s="6"/>
+      <c r="J302" s="6"/>
+    </row>
+    <row r="303" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A303" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D303" s="6"/>
       <c r="E303" s="6"/>
-      <c r="F303" s="6"/>
+      <c r="F303" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="G303" s="6"/>
       <c r="H303" s="6"/>
-      <c r="I303" s="6"/>
-      <c r="J303" s="6"/>
+      <c r="I303" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J303" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
@@ -11122,30 +11153,20 @@
       <c r="J329" s="6"/>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A330" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C330" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="A330" s="6"/>
+      <c r="B330" s="6"/>
+      <c r="C330" s="6"/>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
-      <c r="F330" s="6" t="s">
-        <v>559</v>
-      </c>
+      <c r="F330" s="6"/>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
       <c r="I330" s="6"/>
-      <c r="J330" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J330" s="6"/>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>321</v>
@@ -11156,7 +11177,7 @@
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>255</v>
+        <v>559</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11165,9 +11186,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>321</v>
@@ -11178,7 +11199,7 @@
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>562</v>
+        <v>255</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11189,7 +11210,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>321</v>
@@ -11200,7 +11221,7 @@
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11211,7 +11232,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>321</v>
@@ -11222,7 +11243,7 @@
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11233,18 +11254,18 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11255,7 +11276,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>321</v>
@@ -11266,7 +11287,7 @@
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11277,18 +11298,18 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11299,7 +11320,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>321</v>
@@ -11310,7 +11331,7 @@
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11321,7 +11342,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>321</v>
@@ -11332,7 +11353,7 @@
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11343,18 +11364,18 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>504</v>
+        <v>578</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11365,7 +11386,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
@@ -11376,7 +11397,7 @@
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
       <c r="F341" s="6" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
@@ -11387,7 +11408,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
@@ -11398,7 +11419,7 @@
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>307</v>
+        <v>582</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11409,18 +11430,18 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>586</v>
+        <v>307</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11431,7 +11452,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
@@ -11442,7 +11463,7 @@
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11453,7 +11474,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
@@ -11464,7 +11485,7 @@
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11475,7 +11496,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
@@ -11486,7 +11507,7 @@
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11495,9 +11516,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
@@ -11508,7 +11529,7 @@
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11517,20 +11538,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11541,7 +11562,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
@@ -11552,7 +11573,7 @@
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11563,7 +11584,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
@@ -11574,7 +11595,7 @@
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11585,7 +11606,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
@@ -11596,7 +11617,7 @@
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11607,7 +11628,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
@@ -11618,7 +11639,7 @@
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11629,7 +11650,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
@@ -11640,7 +11661,7 @@
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11649,9 +11670,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
@@ -11662,7 +11683,7 @@
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11671,9 +11692,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A355" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B355" s="6" t="s">
         <v>321</v>
@@ -11684,7 +11705,7 @@
       <c r="D355" s="6"/>
       <c r="E355" s="6"/>
       <c r="F355" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G355" s="6"/>
       <c r="H355" s="6"/>
@@ -11693,45 +11714,43 @@
         <v>14</v>
       </c>
     </row>
-    <row r="356" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="9"/>
-      <c r="B356" s="9"/>
-      <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="F356" s="9"/>
-      <c r="G356" s="9"/>
-      <c r="H356" s="9"/>
-      <c r="I356" s="9"/>
-      <c r="J356" s="9"/>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A357" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B357" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C357" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D357" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E357" s="6"/>
-      <c r="F357" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G357" s="6"/>
-      <c r="H357" s="6"/>
-      <c r="I357" s="6"/>
-      <c r="J357" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A356" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="D356" s="6"/>
+      <c r="E356" s="6"/>
+      <c r="F356" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G356" s="6"/>
+      <c r="H356" s="6"/>
+      <c r="I356" s="6"/>
+      <c r="J356" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A357" s="9"/>
+      <c r="B357" s="9"/>
+      <c r="C357" s="9"/>
+      <c r="D357" s="9"/>
+      <c r="E357" s="9"/>
+      <c r="F357" s="9"/>
+      <c r="G357" s="9"/>
+      <c r="H357" s="9"/>
+      <c r="I357" s="9"/>
+      <c r="J357" s="9"/>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B358" s="6" t="s">
         <v>613</v>
@@ -11744,7 +11763,7 @@
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11755,7 +11774,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B359" s="6" t="s">
         <v>613</v>
@@ -11764,11 +11783,11 @@
         <v>11</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="6" t="s">
-        <v>616</v>
+        <v>18</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
@@ -11777,9 +11796,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B360" s="6" t="s">
         <v>613</v>
@@ -11791,29 +11810,41 @@
         <v>37</v>
       </c>
       <c r="E360" s="6"/>
-      <c r="F360" s="10" t="s">
-        <v>618</v>
+      <c r="F360" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
-      <c r="I360" s="10" t="s">
-        <v>619</v>
-      </c>
+      <c r="I360" s="6"/>
       <c r="J360" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A361" s="6"/>
-      <c r="B361" s="6"/>
-      <c r="C361" s="6"/>
-      <c r="D361" s="6"/>
+    <row r="361" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A361" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="E361" s="6"/>
-      <c r="F361" s="6"/>
+      <c r="F361" s="10" t="s">
+        <v>618</v>
+      </c>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
-      <c r="I361" s="6"/>
-      <c r="J361" s="6"/>
+      <c r="I361" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="J361" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
@@ -11864,32 +11895,20 @@
       <c r="J365" s="6"/>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A366" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="B366" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C366" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D366" s="10" t="s">
-        <v>20</v>
-      </c>
+      <c r="A366" s="6"/>
+      <c r="B366" s="6"/>
+      <c r="C366" s="6"/>
+      <c r="D366" s="6"/>
       <c r="E366" s="6"/>
-      <c r="F366" s="6" t="s">
-        <v>621</v>
-      </c>
+      <c r="F366" s="6"/>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
       <c r="I366" s="6"/>
-      <c r="J366" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J366" s="6"/>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B367" s="6" t="s">
         <v>613</v>
@@ -11902,7 +11921,7 @@
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
@@ -11913,7 +11932,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B368" s="6" t="s">
         <v>613</v>
@@ -11926,7 +11945,7 @@
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>329</v>
+        <v>623</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11937,7 +11956,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B369" s="6" t="s">
         <v>613</v>
@@ -11950,7 +11969,7 @@
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>626</v>
+        <v>329</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11961,7 +11980,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B370" s="6" t="s">
         <v>613</v>
@@ -11974,7 +11993,7 @@
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11985,7 +12004,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B371" s="6" t="s">
         <v>613</v>
@@ -11998,7 +12017,7 @@
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -12009,7 +12028,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B372" s="6" t="s">
         <v>613</v>
@@ -12022,7 +12041,7 @@
       </c>
       <c r="E372" s="6"/>
       <c r="F372" s="6" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
@@ -12033,7 +12052,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B373" s="6" t="s">
         <v>613</v>
@@ -12046,7 +12065,7 @@
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>42</v>
+        <v>632</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12055,9 +12074,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B374" s="6" t="s">
         <v>613</v>
@@ -12070,7 +12089,7 @@
       </c>
       <c r="E374" s="6"/>
       <c r="F374" s="6" t="s">
-        <v>635</v>
+        <v>42</v>
       </c>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
@@ -12079,9 +12098,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B375" s="6" t="s">
         <v>613</v>
@@ -12094,7 +12113,7 @@
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>342</v>
+        <v>635</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12105,7 +12124,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B376" s="6" t="s">
         <v>613</v>
@@ -12118,7 +12137,7 @@
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>638</v>
+        <v>342</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12129,7 +12148,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B377" s="6" t="s">
         <v>613</v>
@@ -12142,7 +12161,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12153,7 +12172,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B378" s="6" t="s">
         <v>613</v>
@@ -12166,7 +12185,7 @@
       </c>
       <c r="E378" s="6"/>
       <c r="F378" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G378" s="6"/>
       <c r="H378" s="6"/>
@@ -12175,33 +12194,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="10" t="s">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A379" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D379" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E379" s="6"/>
+      <c r="F379" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="G379" s="6"/>
+      <c r="H379" s="6"/>
+      <c r="I379" s="6"/>
+      <c r="J379" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A381" s="10" t="s">
         <v>643</v>
-      </c>
-      <c r="B380" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C380" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D380" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E380" s="6"/>
-      <c r="F380" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="G380" s="6"/>
-      <c r="H380" s="6"/>
-      <c r="I380" s="6"/>
-      <c r="J380" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A381" s="6" t="s">
-        <v>645</v>
       </c>
       <c r="B381" s="6" t="s">
         <v>613</v>
@@ -12214,28 +12233,40 @@
       </c>
       <c r="E381" s="6"/>
       <c r="F381" s="10" t="s">
-        <v>351</v>
+        <v>644</v>
       </c>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
-      <c r="I381" s="10" t="s">
-        <v>646</v>
-      </c>
+      <c r="I381" s="6"/>
       <c r="J381" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A382" s="6"/>
-      <c r="B382" s="6"/>
-      <c r="C382" s="6"/>
-      <c r="D382" s="6"/>
+    <row r="382" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A382" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D382" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E382" s="6"/>
-      <c r="F382" s="6"/>
+      <c r="F382" s="10" t="s">
+        <v>351</v>
+      </c>
       <c r="G382" s="6"/>
       <c r="H382" s="6"/>
-      <c r="I382" s="6"/>
-      <c r="J382" s="6"/>
+      <c r="I382" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="J382" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
@@ -12261,43 +12292,43 @@
       <c r="I384" s="6"/>
       <c r="J384" s="6"/>
     </row>
-    <row r="385" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A385" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B385" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C385" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D385" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A385" s="6"/>
+      <c r="B385" s="6"/>
+      <c r="C385" s="6"/>
+      <c r="D385" s="6"/>
       <c r="E385" s="6"/>
-      <c r="F385" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="F385" s="6"/>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
-      <c r="I385" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="J385" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A386" s="6"/>
-      <c r="B386" s="6"/>
-      <c r="C386" s="6"/>
-      <c r="D386" s="6"/>
+      <c r="I385" s="6"/>
+      <c r="J385" s="6"/>
+    </row>
+    <row r="386" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A386" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D386" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E386" s="6"/>
-      <c r="F386" s="6"/>
+      <c r="F386" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G386" s="6"/>
       <c r="H386" s="6"/>
-      <c r="I386" s="6"/>
-      <c r="J386" s="6"/>
+      <c r="I386" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="J386" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
@@ -12371,43 +12402,43 @@
       <c r="I392" s="6"/>
       <c r="J392" s="6"/>
     </row>
-    <row r="393" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A393" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B393" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C393" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D393" s="6" t="s">
-        <v>650</v>
-      </c>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A393" s="6"/>
+      <c r="B393" s="6"/>
+      <c r="C393" s="6"/>
+      <c r="D393" s="6"/>
       <c r="E393" s="6"/>
-      <c r="F393" s="6" t="s">
-        <v>651</v>
-      </c>
+      <c r="F393" s="6"/>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
-      <c r="I393" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="J393" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A394" s="6"/>
-      <c r="B394" s="6"/>
-      <c r="C394" s="6"/>
-      <c r="D394" s="6"/>
+      <c r="I393" s="6"/>
+      <c r="J393" s="6"/>
+    </row>
+    <row r="394" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A394" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E394" s="6"/>
-      <c r="F394" s="6"/>
+      <c r="F394" s="6" t="s">
+        <v>651</v>
+      </c>
       <c r="G394" s="6"/>
       <c r="H394" s="6"/>
-      <c r="I394" s="6"/>
-      <c r="J394" s="6"/>
+      <c r="I394" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="J394" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
@@ -12458,32 +12489,20 @@
       <c r="J398" s="6"/>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A399" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B399" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C399" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D399" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="A399" s="6"/>
+      <c r="B399" s="6"/>
+      <c r="C399" s="6"/>
+      <c r="D399" s="6"/>
       <c r="E399" s="6"/>
-      <c r="F399" s="6" t="s">
-        <v>62</v>
-      </c>
+      <c r="F399" s="6"/>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
       <c r="I399" s="6"/>
-      <c r="J399" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J399" s="6"/>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>613</v>
@@ -12496,7 +12515,7 @@
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>655</v>
+        <v>62</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12505,9 +12524,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B401" s="6" t="s">
         <v>613</v>
@@ -12520,7 +12539,7 @@
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12529,9 +12548,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B402" s="6" t="s">
         <v>613</v>
@@ -12544,7 +12563,7 @@
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
@@ -12555,7 +12574,7 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B403" s="6" t="s">
         <v>613</v>
@@ -12568,20 +12587,18 @@
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
-      <c r="I403" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I403" s="6"/>
       <c r="J403" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B404" s="6" t="s">
         <v>613</v>
@@ -12594,18 +12611,20 @@
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
-      <c r="I404" s="6"/>
+      <c r="I404" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J404" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B405" s="6" t="s">
         <v>613</v>
@@ -12618,7 +12637,7 @@
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12627,9 +12646,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B406" s="6" t="s">
         <v>613</v>
@@ -12642,7 +12661,7 @@
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12651,9 +12670,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B407" s="6" t="s">
         <v>613</v>
@@ -12666,7 +12685,7 @@
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12677,7 +12696,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B408" s="6" t="s">
         <v>613</v>
@@ -12686,11 +12705,11 @@
         <v>11</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
@@ -12701,7 +12720,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B409" s="6" t="s">
         <v>613</v>
@@ -12714,7 +12733,7 @@
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
-        <v>97</v>
+        <v>672</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
@@ -12725,7 +12744,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B410" s="6" t="s">
         <v>613</v>
@@ -12738,7 +12757,7 @@
       </c>
       <c r="E410" s="6"/>
       <c r="F410" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12749,7 +12768,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B411" s="6" t="s">
         <v>613</v>
@@ -12761,8 +12780,8 @@
         <v>671</v>
       </c>
       <c r="E411" s="6"/>
-      <c r="F411" s="10" t="s">
-        <v>676</v>
+      <c r="F411" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12773,7 +12792,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B412" s="6" t="s">
         <v>613</v>
@@ -12785,8 +12804,8 @@
         <v>671</v>
       </c>
       <c r="E412" s="6"/>
-      <c r="F412" s="6" t="s">
-        <v>89</v>
+      <c r="F412" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12797,7 +12816,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>613</v>
@@ -12810,7 +12829,7 @@
       </c>
       <c r="E413" s="6"/>
       <c r="F413" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12821,7 +12840,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>613</v>
@@ -12833,8 +12852,8 @@
         <v>671</v>
       </c>
       <c r="E414" s="6"/>
-      <c r="F414" s="10" t="s">
-        <v>680</v>
+      <c r="F414" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
@@ -12845,7 +12864,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B415" s="6" t="s">
         <v>613</v>
@@ -12857,8 +12876,8 @@
         <v>671</v>
       </c>
       <c r="E415" s="6"/>
-      <c r="F415" s="6" t="s">
-        <v>93</v>
+      <c r="F415" s="10" t="s">
+        <v>680</v>
       </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
@@ -12868,16 +12887,28 @@
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A416" s="6"/>
-      <c r="B416" s="6"/>
-      <c r="C416" s="6"/>
-      <c r="D416" s="6"/>
+      <c r="A416" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D416" s="6" t="s">
+        <v>671</v>
+      </c>
       <c r="E416" s="6"/>
-      <c r="F416" s="6"/>
+      <c r="F416" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="G416" s="6"/>
       <c r="H416" s="6"/>
       <c r="I416" s="6"/>
-      <c r="J416" s="6"/>
+      <c r="J416" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
@@ -12916,30 +12947,20 @@
       <c r="J419" s="6"/>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A420" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B420" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C420" s="10" t="s">
-        <v>399</v>
-      </c>
+      <c r="A420" s="6"/>
+      <c r="B420" s="6"/>
+      <c r="C420" s="6"/>
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
-      <c r="F420" s="6" t="s">
-        <v>194</v>
-      </c>
+      <c r="F420" s="6"/>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
       <c r="I420" s="6"/>
-      <c r="J420" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J420" s="6"/>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B421" s="6" t="s">
         <v>613</v>
@@ -12950,7 +12971,7 @@
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>684</v>
+        <v>194</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12961,7 +12982,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B422" s="6" t="s">
         <v>613</v>
@@ -12972,7 +12993,7 @@
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
       <c r="F422" s="6" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12983,7 +13004,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B423" s="6" t="s">
         <v>613</v>
@@ -12994,7 +13015,7 @@
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -13005,7 +13026,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B424" s="6" t="s">
         <v>613</v>
@@ -13016,7 +13037,7 @@
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13027,18 +13048,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B425" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13049,18 +13070,18 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B426" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C426" s="6" t="s">
-        <v>585</v>
+      <c r="C426" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13071,7 +13092,7 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B427" s="6" t="s">
         <v>613</v>
@@ -13082,7 +13103,7 @@
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13091,9 +13112,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B428" s="6" t="s">
         <v>613</v>
@@ -13104,7 +13125,7 @@
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
@@ -13113,44 +13134,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B429" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C429" s="10" t="s">
-        <v>700</v>
+      <c r="C429" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
-      <c r="I429" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I429" s="6"/>
       <c r="J429" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B430" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C430" s="6" t="s">
-        <v>437</v>
+      <c r="C430" s="10" t="s">
+        <v>700</v>
       </c>
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
       <c r="F430" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
@@ -13163,7 +13182,7 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B431" s="6" t="s">
         <v>613</v>
@@ -13174,18 +13193,20 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>412</v>
+        <v>703</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
-      <c r="I431" s="6"/>
+      <c r="I431" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J431" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="432" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B432" s="6" t="s">
         <v>613</v>
@@ -13196,28 +13217,38 @@
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>460</v>
+        <v>412</v>
       </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
-      <c r="I432" s="10" t="s">
-        <v>926</v>
-      </c>
+      <c r="I432" s="6"/>
       <c r="J432" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A433" s="6"/>
-      <c r="B433" s="6"/>
-      <c r="C433" s="6"/>
+    <row r="433" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A433" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C433" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D433" s="6"/>
       <c r="E433" s="6"/>
-      <c r="F433" s="6"/>
+      <c r="F433" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
-      <c r="I433" s="6"/>
-      <c r="J433" s="6"/>
+      <c r="I433" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="J433" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
@@ -13268,30 +13299,20 @@
       <c r="J437" s="6"/>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A438" s="6" t="s">
-        <v>706</v>
-      </c>
-      <c r="B438" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C438" s="6" t="s">
-        <v>437</v>
-      </c>
+      <c r="A438" s="6"/>
+      <c r="B438" s="6"/>
+      <c r="C438" s="6"/>
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
-      <c r="F438" s="6" t="s">
-        <v>707</v>
-      </c>
+      <c r="F438" s="6"/>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
       <c r="I438" s="6"/>
-      <c r="J438" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J438" s="6"/>
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B439" s="6" t="s">
         <v>613</v>
@@ -13302,7 +13323,7 @@
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13313,7 +13334,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B440" s="6" t="s">
         <v>613</v>
@@ -13324,7 +13345,7 @@
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13335,7 +13356,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B441" s="6" t="s">
         <v>613</v>
@@ -13346,7 +13367,7 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13357,7 +13378,7 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B442" s="6" t="s">
         <v>613</v>
@@ -13368,7 +13389,7 @@
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13379,18 +13400,18 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B443" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13401,7 +13422,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B444" s="6" t="s">
         <v>613</v>
@@ -13412,7 +13433,7 @@
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
@@ -13421,9 +13442,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="445" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B445" s="6" t="s">
         <v>613</v>
@@ -13434,7 +13455,7 @@
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
       <c r="F445" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
@@ -13443,9 +13464,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B446" s="6" t="s">
         <v>613</v>
@@ -13456,7 +13477,7 @@
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
       <c r="F446" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
@@ -13465,9 +13486,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="447" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B447" s="6" t="s">
         <v>613</v>
@@ -13478,7 +13499,7 @@
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
       <c r="F447" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
@@ -13487,9 +13508,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B448" s="6" t="s">
         <v>613</v>
@@ -13500,7 +13521,7 @@
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
       <c r="F448" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
@@ -13511,7 +13532,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B449" s="6" t="s">
         <v>613</v>
@@ -13522,7 +13543,7 @@
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13531,9 +13552,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="450" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B450" s="6" t="s">
         <v>613</v>
@@ -13544,7 +13565,7 @@
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13553,9 +13574,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B451" s="6" t="s">
         <v>613</v>
@@ -13566,7 +13587,7 @@
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13577,7 +13598,7 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B452" s="6" t="s">
         <v>613</v>
@@ -13588,7 +13609,7 @@
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
       <c r="F452" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
@@ -13597,9 +13618,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="453" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B453" s="6" t="s">
         <v>613</v>
@@ -13609,29 +13630,39 @@
       </c>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="10" t="s">
-        <v>737</v>
+      <c r="F453" s="6" t="s">
+        <v>735</v>
       </c>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
-      <c r="I453" s="10" t="s">
-        <v>738</v>
-      </c>
+      <c r="I453" s="6"/>
       <c r="J453" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A454" s="6"/>
-      <c r="B454" s="6"/>
-      <c r="C454" s="6"/>
+    <row r="454" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A454" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D454" s="6"/>
       <c r="E454" s="6"/>
-      <c r="F454" s="6"/>
+      <c r="F454" s="10" t="s">
+        <v>737</v>
+      </c>
       <c r="G454" s="6"/>
       <c r="H454" s="6"/>
-      <c r="I454" s="6"/>
-      <c r="J454" s="6"/>
+      <c r="I454" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J454" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
@@ -13646,30 +13677,20 @@
       <c r="J455" s="6"/>
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A456" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="B456" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C456" s="6" t="s">
-        <v>462</v>
-      </c>
+      <c r="A456" s="6"/>
+      <c r="B456" s="6"/>
+      <c r="C456" s="6"/>
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
-      <c r="F456" s="6" t="s">
-        <v>740</v>
-      </c>
+      <c r="F456" s="6"/>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
       <c r="I456" s="6"/>
-      <c r="J456" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J456" s="6"/>
+    </row>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B457" s="6" t="s">
         <v>613</v>
@@ -13680,7 +13701,7 @@
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13691,7 +13712,7 @@
     </row>
     <row r="458" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B458" s="6" t="s">
         <v>613</v>
@@ -13702,7 +13723,7 @@
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13711,20 +13732,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B459" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C459" s="10" t="s">
-        <v>746</v>
+      <c r="C459" s="6" t="s">
+        <v>462</v>
       </c>
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
@@ -13735,7 +13756,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B460" s="6" t="s">
         <v>613</v>
@@ -13746,42 +13767,42 @@
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
-      <c r="I460" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I460" s="6"/>
       <c r="J460" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B461" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>506</v>
+        <v>746</v>
       </c>
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
-      <c r="I461" s="6"/>
+      <c r="I461" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J461" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B462" s="6" t="s">
         <v>613</v>
@@ -13792,7 +13813,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>509</v>
+        <v>751</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -13803,7 +13824,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B463" s="6" t="s">
         <v>613</v>
@@ -13814,7 +13835,7 @@
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
       <c r="F463" s="6" t="s">
-        <v>104</v>
+        <v>509</v>
       </c>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
@@ -13825,7 +13846,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B464" s="6" t="s">
         <v>613</v>
@@ -13836,7 +13857,7 @@
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
       <c r="F464" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
@@ -13847,7 +13868,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B465" s="6" t="s">
         <v>613</v>
@@ -13857,8 +13878,8 @@
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="10" t="s">
-        <v>756</v>
+      <c r="F465" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
@@ -13869,7 +13890,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B466" s="6" t="s">
         <v>613</v>
@@ -13879,8 +13900,8 @@
       </c>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
-      <c r="F466" s="6" t="s">
-        <v>110</v>
+      <c r="F466" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13891,7 +13912,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B467" s="6" t="s">
         <v>613</v>
@@ -13902,7 +13923,7 @@
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>759</v>
+        <v>110</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13913,7 +13934,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B468" s="6" t="s">
         <v>613</v>
@@ -13924,7 +13945,7 @@
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13935,7 +13956,7 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B469" s="6" t="s">
         <v>613</v>
@@ -13946,7 +13967,7 @@
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13955,9 +13976,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B470" s="6" t="s">
         <v>613</v>
@@ -13968,7 +13989,7 @@
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13977,9 +13998,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B471" s="6" t="s">
         <v>613</v>
@@ -13990,7 +14011,7 @@
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
@@ -14001,18 +14022,18 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B472" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C472" s="6" t="s">
+      <c r="C472" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -14023,7 +14044,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B473" s="6" t="s">
         <v>613</v>
@@ -14034,7 +14055,7 @@
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14045,7 +14066,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B474" s="6" t="s">
         <v>613</v>
@@ -14056,7 +14077,7 @@
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14067,7 +14088,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B475" s="6" t="s">
         <v>613</v>
@@ -14078,7 +14099,7 @@
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14089,7 +14110,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B476" s="6" t="s">
         <v>613</v>
@@ -14100,7 +14121,7 @@
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
       <c r="F476" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14111,7 +14132,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B477" s="6" t="s">
         <v>613</v>
@@ -14122,7 +14143,7 @@
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14133,7 +14154,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B478" s="6" t="s">
         <v>613</v>
@@ -14144,7 +14165,7 @@
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14155,7 +14176,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B479" s="6" t="s">
         <v>613</v>
@@ -14166,7 +14187,7 @@
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14177,7 +14198,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B480" s="6" t="s">
         <v>613</v>
@@ -14188,7 +14209,7 @@
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14199,7 +14220,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B481" s="6" t="s">
         <v>613</v>
@@ -14210,7 +14231,7 @@
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14221,7 +14242,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B482" s="6" t="s">
         <v>613</v>
@@ -14232,7 +14253,7 @@
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14243,7 +14264,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B483" s="6" t="s">
         <v>613</v>
@@ -14254,7 +14275,7 @@
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14265,7 +14286,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B484" s="6" t="s">
         <v>613</v>
@@ -14276,7 +14297,7 @@
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14287,7 +14308,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B485" s="6" t="s">
         <v>613</v>
@@ -14298,7 +14319,7 @@
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>541</v>
+        <v>793</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14309,7 +14330,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B486" s="6" t="s">
         <v>613</v>
@@ -14320,7 +14341,7 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>796</v>
+        <v>541</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14331,7 +14352,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B487" s="6" t="s">
         <v>613</v>
@@ -14342,7 +14363,7 @@
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
       <c r="F487" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
@@ -14351,41 +14372,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B488" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C488" s="10" t="s">
+      <c r="C488" s="6" t="s">
         <v>506</v>
       </c>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="10" t="s">
-        <v>800</v>
+      <c r="F488" s="6" t="s">
+        <v>798</v>
       </c>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
-      <c r="I488" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I488" s="6"/>
       <c r="J488" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A489" s="6"/>
-      <c r="B489" s="6"/>
-      <c r="C489" s="6"/>
+    <row r="489" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A489" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="B489" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C489" s="10" t="s">
+        <v>506</v>
+      </c>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
-      <c r="F489" s="6"/>
+      <c r="F489" s="10" t="s">
+        <v>800</v>
+      </c>
       <c r="G489" s="6"/>
       <c r="H489" s="6"/>
-      <c r="I489" s="6"/>
-      <c r="J489" s="6"/>
+      <c r="I489" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J489" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
@@ -14628,30 +14659,20 @@
       <c r="J509" s="6"/>
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A510" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="B510" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C510" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A510" s="6"/>
+      <c r="B510" s="6"/>
+      <c r="C510" s="6"/>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
-      <c r="F510" s="6" t="s">
-        <v>803</v>
-      </c>
+      <c r="F510" s="6"/>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
       <c r="I510" s="6"/>
-      <c r="J510" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="511" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J510" s="6"/>
+    </row>
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B511" s="6" t="s">
         <v>613</v>
@@ -14662,7 +14683,7 @@
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
       <c r="F511" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
@@ -14671,9 +14692,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B512" s="6" t="s">
         <v>613</v>
@@ -14684,7 +14705,7 @@
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
       <c r="F512" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
@@ -14695,7 +14716,7 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B513" s="6" t="s">
         <v>613</v>
@@ -14706,7 +14727,7 @@
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
       <c r="F513" s="6" t="s">
-        <v>425</v>
+        <v>807</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
@@ -14715,41 +14736,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="514" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B514" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C514" s="10" t="s">
+      <c r="C514" s="6" t="s">
         <v>524</v>
       </c>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="10" t="s">
-        <v>810</v>
+      <c r="F514" s="6" t="s">
+        <v>425</v>
       </c>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
-      <c r="I514" s="10" t="s">
-        <v>801</v>
-      </c>
+      <c r="I514" s="6"/>
       <c r="J514" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A515" s="6"/>
-      <c r="B515" s="6"/>
-      <c r="C515" s="6"/>
+    <row r="515" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A515" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="B515" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C515" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D515" s="6"/>
       <c r="E515" s="6"/>
-      <c r="F515" s="6"/>
+      <c r="F515" s="10" t="s">
+        <v>810</v>
+      </c>
       <c r="G515" s="6"/>
       <c r="H515" s="6"/>
-      <c r="I515" s="6"/>
-      <c r="J515" s="6"/>
+      <c r="I515" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="J515" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="6"/>
@@ -14991,41 +15022,41 @@
       <c r="I535" s="6"/>
       <c r="J535" s="6"/>
     </row>
-    <row r="536" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A536" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="B536" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C536" s="10" t="s">
-        <v>524</v>
-      </c>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A536" s="6"/>
+      <c r="B536" s="6"/>
+      <c r="C536" s="6"/>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="10" t="s">
-        <v>812</v>
-      </c>
+      <c r="F536" s="6"/>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
-      <c r="I536" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J536" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A537" s="6"/>
-      <c r="B537" s="6"/>
-      <c r="C537" s="6"/>
+      <c r="I536" s="6"/>
+      <c r="J536" s="6"/>
+    </row>
+    <row r="537" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A537" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B537" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C537" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D537" s="6"/>
       <c r="E537" s="6"/>
-      <c r="F537" s="6"/>
+      <c r="F537" s="10" t="s">
+        <v>812</v>
+      </c>
       <c r="G537" s="6"/>
       <c r="H537" s="6"/>
-      <c r="I537" s="6"/>
-      <c r="J537" s="6"/>
+      <c r="I537" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="J537" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" s="6"/>
@@ -15112,30 +15143,20 @@
       <c r="J544" s="6"/>
     </row>
     <row r="545" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A545" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="B545" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C545" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A545" s="6"/>
+      <c r="B545" s="6"/>
+      <c r="C545" s="6"/>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
-      <c r="F545" s="6" t="s">
-        <v>814</v>
-      </c>
+      <c r="F545" s="6"/>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
       <c r="I545" s="6"/>
-      <c r="J545" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J545" s="6"/>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B546" s="6" t="s">
         <v>613</v>
@@ -15146,7 +15167,7 @@
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>206</v>
+        <v>814</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15157,7 +15178,7 @@
     </row>
     <row r="547" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B547" s="6" t="s">
         <v>613</v>
@@ -15168,7 +15189,7 @@
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
       <c r="F547" s="6" t="s">
-        <v>817</v>
+        <v>206</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
@@ -15177,9 +15198,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B548" s="6" t="s">
         <v>613</v>
@@ -15190,7 +15211,7 @@
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="6" t="s">
-        <v>210</v>
+        <v>817</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
@@ -15201,7 +15222,7 @@
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B549" s="6" t="s">
         <v>613</v>
@@ -15212,7 +15233,7 @@
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
       <c r="F549" s="6" t="s">
-        <v>820</v>
+        <v>210</v>
       </c>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
@@ -15223,7 +15244,7 @@
     </row>
     <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B550" s="6" t="s">
         <v>613</v>
@@ -15234,7 +15255,7 @@
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
       <c r="F550" s="6" t="s">
-        <v>717</v>
+        <v>820</v>
       </c>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
@@ -15243,9 +15264,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="551" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B551" s="6" t="s">
         <v>613</v>
@@ -15255,88 +15276,110 @@
       </c>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="10" t="s">
-        <v>823</v>
+      <c r="F551" s="6" t="s">
+        <v>717</v>
       </c>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
-      <c r="I551" s="10" t="s">
-        <v>824</v>
-      </c>
+      <c r="I551" s="6"/>
       <c r="J551" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A552" s="6"/>
-      <c r="B552" s="6"/>
-      <c r="C552" s="6"/>
+    <row r="552" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A552" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="B552" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C552" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
-      <c r="F552" s="6"/>
+      <c r="F552" s="10" t="s">
+        <v>823</v>
+      </c>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
-      <c r="I552" s="6"/>
-      <c r="J552" s="6"/>
+      <c r="I552" s="10" t="s">
+        <v>824</v>
+      </c>
+      <c r="J552" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="553" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A553" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="B553" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C553" s="6" t="s">
-        <v>524</v>
-      </c>
+      <c r="A553" s="6"/>
+      <c r="B553" s="6"/>
+      <c r="C553" s="6"/>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
-      <c r="F553" s="6" t="s">
-        <v>826</v>
-      </c>
+      <c r="F553" s="6"/>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
       <c r="I553" s="6"/>
-      <c r="J553" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="554" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="J553" s="6"/>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A554" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B554" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>828</v>
+        <v>524</v>
       </c>
       <c r="D554" s="6"/>
       <c r="E554" s="6"/>
       <c r="F554" s="6" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="G554" s="6"/>
       <c r="H554" s="6"/>
-      <c r="I554" s="10" t="s">
+      <c r="I554" s="6"/>
+      <c r="J554" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A555" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="B555" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C555" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D555" s="6"/>
+      <c r="E555" s="6"/>
+      <c r="F555" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="G555" s="6"/>
+      <c r="H555" s="6"/>
+      <c r="I555" s="10" t="s">
         <v>830</v>
       </c>
-      <c r="J554" s="6" t="s">
+      <c r="J555" s="6" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C489:C510 C515:C545 C421:C426 C430 C434:C438 C556:C948 C381:C416 C460:C472 C2:C379" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H380:H947 H2:H378" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H381:H948 H2:H379" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J380:J947 J2:J378" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J381:J948 J2:J379" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C489:C510 C515:C545 C421:C426 C430 C434:C438 C556:C948 C381:C416 C460:C472 C2:C379" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EEFE29-C15E-4A4A-BD8E-B35E39FE99B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B5B52B-34BB-4017-8CAB-21BFA296EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="929">
   <si>
     <t>Item_ID</t>
   </si>
@@ -2987,15 +2987,6 @@
   </si>
   <si>
     <t>BLOCK TRAY LAYOUT - CHOCKS</t>
-  </si>
-  <si>
-    <t>test edit</t>
-  </si>
-  <si>
-    <t>test add</t>
-  </si>
-  <si>
-    <t>BR-1136</t>
   </si>
 </sst>
 </file>
@@ -3402,9 +3393,7 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
-        <v>929</v>
-      </c>
+      <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
@@ -3416,30 +3405,16 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>931</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
-        <v>930</v>
-      </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
-        <v>929</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>

--- a/Blackwood_CFS_Master_Inventory.xlsx
+++ b/Blackwood_CFS_Master_Inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\OneDrive\HOME\Documents\GitHub\Blackwood-CFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B5B52B-34BB-4017-8CAB-21BFA296EECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E343CC8-E0DB-418E-8C24-E0F6C5A58064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3319,7 +3319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P555"/>
+  <dimension ref="A1:P554"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3405,16 +3405,28 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -3424,7 +3436,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>10</v>
@@ -3437,7 +3449,7 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -3454,7 +3466,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>10</v>
@@ -3463,11 +3475,11 @@
         <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
@@ -3484,7 +3496,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>
@@ -3497,7 +3509,7 @@
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -3514,7 +3526,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>10</v>
@@ -3527,7 +3539,7 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -3544,7 +3556,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>10</v>
@@ -3557,7 +3569,7 @@
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -3574,7 +3586,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
@@ -3587,7 +3599,7 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -3604,7 +3616,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
@@ -3617,7 +3629,7 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -3634,7 +3646,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
@@ -3647,7 +3659,7 @@
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -3664,7 +3676,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
@@ -3677,7 +3689,7 @@
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -3694,7 +3706,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
@@ -3703,11 +3715,11 @@
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3724,7 +3736,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
@@ -3737,7 +3749,7 @@
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -3754,7 +3766,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
@@ -3767,7 +3779,7 @@
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -3784,7 +3796,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
@@ -3797,7 +3809,7 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -3814,7 +3826,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
@@ -3827,7 +3839,7 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -3844,7 +3856,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
@@ -3857,7 +3869,7 @@
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -3874,7 +3886,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
@@ -3887,7 +3899,7 @@
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -3904,7 +3916,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
@@ -3917,7 +3929,7 @@
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -3932,9 +3944,9 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
@@ -3947,11 +3959,13 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="J21" s="5" t="s">
         <v>14</v>
       </c>
@@ -3962,9 +3976,9 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
     </row>
-    <row r="22" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
@@ -3973,17 +3987,15 @@
         <v>11</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
         <v>14</v>
       </c>
@@ -3996,7 +4008,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
@@ -4009,7 +4021,7 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -4026,7 +4038,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
@@ -4039,7 +4051,7 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
@@ -4056,7 +4068,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
@@ -4069,7 +4081,7 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -4086,7 +4098,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
@@ -4099,7 +4111,7 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
@@ -4116,7 +4128,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -4129,7 +4141,7 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -4146,7 +4158,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
@@ -4159,7 +4171,7 @@
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -4176,7 +4188,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
@@ -4189,7 +4201,7 @@
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
@@ -4206,7 +4218,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
@@ -4219,7 +4231,7 @@
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -4236,7 +4248,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
@@ -4249,7 +4261,7 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -4266,7 +4278,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
@@ -4279,7 +4291,7 @@
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -4296,7 +4308,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
@@ -4309,7 +4321,7 @@
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -4326,7 +4338,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
@@ -4339,7 +4351,7 @@
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -4356,7 +4368,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
@@ -4369,7 +4381,7 @@
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -4386,7 +4398,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
@@ -4399,7 +4411,7 @@
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -4414,9 +4426,9 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
@@ -4429,11 +4441,13 @@
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="J37" s="5" t="s">
         <v>14</v>
       </c>
@@ -4444,9 +4458,9 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
@@ -4459,13 +4473,11 @@
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
         <v>14</v>
       </c>
@@ -4478,7 +4490,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
@@ -4491,7 +4503,7 @@
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -4508,7 +4520,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
@@ -4521,7 +4533,7 @@
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -4538,7 +4550,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
@@ -4551,7 +4563,7 @@
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -4568,7 +4580,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
@@ -4581,7 +4593,7 @@
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
@@ -4598,7 +4610,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
@@ -4611,7 +4623,7 @@
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -4628,7 +4640,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>10</v>
@@ -4641,7 +4653,7 @@
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
@@ -4658,7 +4670,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>10</v>
@@ -4671,7 +4683,7 @@
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -4688,20 +4700,18 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="D46" s="5"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -4718,7 +4728,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>10</v>
@@ -4729,7 +4739,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -4746,7 +4756,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>10</v>
@@ -4757,7 +4767,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -4774,7 +4784,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>10</v>
@@ -4785,7 +4795,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -4802,7 +4812,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>10</v>
@@ -4813,7 +4823,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -4830,7 +4840,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>10</v>
@@ -4841,7 +4851,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
@@ -4858,7 +4868,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>10</v>
@@ -4869,7 +4879,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -4886,7 +4896,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
@@ -4897,7 +4907,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -4914,7 +4924,7 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>10</v>
@@ -4925,7 +4935,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -4942,7 +4952,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>10</v>
@@ -4953,7 +4963,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -4970,7 +4980,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
@@ -4981,7 +4991,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -4998,18 +5008,18 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>123</v>
+        <v>927</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>124</v>
+        <v>928</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5026,7 +5036,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>927</v>
+        <v>125</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>10</v>
@@ -5034,10 +5044,12 @@
       <c r="C58" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="5"/>
+      <c r="D58" s="5" t="s">
+        <v>127</v>
+      </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>928</v>
+        <v>128</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -5054,7 +5066,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
@@ -5067,7 +5079,7 @@
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -5084,7 +5096,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>10</v>
@@ -5097,7 +5109,7 @@
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
@@ -5114,7 +5126,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
@@ -5127,7 +5139,7 @@
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5144,7 +5156,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>10</v>
@@ -5157,7 +5169,7 @@
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5174,7 +5186,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
@@ -5187,7 +5199,7 @@
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5204,7 +5216,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
@@ -5217,7 +5229,7 @@
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -5234,7 +5246,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
@@ -5243,11 +5255,11 @@
         <v>126</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
@@ -5264,7 +5276,7 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
@@ -5277,7 +5289,7 @@
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -5294,7 +5306,7 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
@@ -5307,7 +5319,7 @@
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -5324,7 +5336,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
@@ -5337,7 +5349,7 @@
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -5354,7 +5366,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
@@ -5363,11 +5375,11 @@
         <v>126</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5"/>
@@ -5384,7 +5396,7 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -5397,7 +5409,7 @@
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
@@ -5414,7 +5426,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
@@ -5423,11 +5435,11 @@
         <v>126</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -5444,7 +5456,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
@@ -5457,7 +5469,7 @@
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5474,7 +5486,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
@@ -5487,7 +5499,7 @@
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -5504,7 +5516,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
@@ -5517,7 +5529,7 @@
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -5534,7 +5546,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
@@ -5547,7 +5559,7 @@
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -5564,7 +5576,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
@@ -5577,7 +5589,7 @@
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -5594,7 +5606,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
@@ -5607,7 +5619,7 @@
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -5624,7 +5636,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>10</v>
@@ -5633,11 +5645,11 @@
         <v>126</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
@@ -5654,7 +5666,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>10</v>
@@ -5667,7 +5679,7 @@
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -5684,7 +5696,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>10</v>
@@ -5697,7 +5709,7 @@
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -5714,7 +5726,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
@@ -5727,7 +5739,7 @@
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
@@ -5744,7 +5756,7 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>10</v>
@@ -5757,7 +5769,7 @@
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -5774,20 +5786,18 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -5804,18 +5814,18 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
@@ -5832,7 +5842,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
@@ -5843,7 +5853,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -5860,7 +5870,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
@@ -5871,7 +5881,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -5888,7 +5898,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>10</v>
@@ -5899,7 +5909,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -5916,7 +5926,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
@@ -5927,7 +5937,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -5944,7 +5954,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>10</v>
@@ -5955,7 +5965,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
@@ -5972,7 +5982,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>10</v>
@@ -5983,7 +5993,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
@@ -6000,7 +6010,7 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>10</v>
@@ -6011,7 +6021,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
@@ -6028,7 +6038,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>10</v>
@@ -6039,7 +6049,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -6056,7 +6066,7 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
@@ -6067,7 +6077,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -6082,9 +6092,9 @@
       <c r="O93" s="5"/>
       <c r="P93" s="5"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>10</v>
@@ -6095,7 +6105,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -6110,9 +6120,9 @@
       <c r="O94" s="5"/>
       <c r="P94" s="5"/>
     </row>
-    <row r="95" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>10</v>
@@ -6123,7 +6133,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -6140,7 +6150,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>10</v>
@@ -6151,7 +6161,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
@@ -6168,7 +6178,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>10</v>
@@ -6179,7 +6189,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -6196,7 +6206,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>10</v>
@@ -6207,7 +6217,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -6224,7 +6234,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>10</v>
@@ -6235,7 +6245,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
@@ -6252,7 +6262,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
@@ -6263,7 +6273,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
       <c r="F100" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -6280,7 +6290,7 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>10</v>
@@ -6291,7 +6301,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -6308,7 +6318,7 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
@@ -6319,7 +6329,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -6336,7 +6346,7 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
@@ -6347,7 +6357,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
@@ -6364,7 +6374,7 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
@@ -6375,7 +6385,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
@@ -6392,7 +6402,7 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
@@ -6403,7 +6413,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
@@ -6420,7 +6430,7 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
@@ -6431,7 +6441,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
@@ -6448,7 +6458,7 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
@@ -6459,7 +6469,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6476,7 +6486,7 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
@@ -6487,7 +6497,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6504,7 +6514,7 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
@@ -6515,7 +6525,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
@@ -6530,9 +6540,9 @@
       <c r="O109" s="5"/>
       <c r="P109" s="5"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
@@ -6543,11 +6553,13 @@
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
+      <c r="I110" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="J110" s="5" t="s">
         <v>14</v>
       </c>
@@ -6558,9 +6570,9 @@
       <c r="O110" s="5"/>
       <c r="P110" s="5"/>
     </row>
-    <row r="111" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
@@ -6571,12 +6583,12 @@
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5" t="s">
-        <v>239</v>
+        <v>923</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>14</v>
@@ -6590,24 +6602,24 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D112" s="5"/>
+        <v>243</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="E112" s="5"/>
       <c r="F112" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
-      <c r="I112" s="5" t="s">
-        <v>923</v>
-      </c>
+      <c r="I112" s="5"/>
       <c r="J112" s="5" t="s">
         <v>14</v>
       </c>
@@ -6620,7 +6632,7 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
@@ -6633,7 +6645,7 @@
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6650,7 +6662,7 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>10</v>
@@ -6663,7 +6675,7 @@
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6680,7 +6692,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>10</v>
@@ -6693,7 +6705,7 @@
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6710,7 +6722,7 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
@@ -6723,7 +6735,7 @@
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6738,9 +6750,9 @@
       <c r="O116" s="5"/>
       <c r="P116" s="5"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>10</v>
@@ -6753,7 +6765,7 @@
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6768,9 +6780,9 @@
       <c r="O117" s="5"/>
       <c r="P117" s="5"/>
     </row>
-    <row r="118" spans="1:16" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>10</v>
@@ -6779,11 +6791,11 @@
         <v>243</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6800,7 +6812,7 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>10</v>
@@ -6813,7 +6825,7 @@
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6830,7 +6842,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>10</v>
@@ -6843,7 +6855,7 @@
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -6860,7 +6872,7 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
@@ -6873,7 +6885,7 @@
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
@@ -6890,7 +6902,7 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
@@ -6903,7 +6915,7 @@
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
@@ -6920,7 +6932,7 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>10</v>
@@ -6933,7 +6945,7 @@
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
@@ -6950,7 +6962,7 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
@@ -6963,7 +6975,7 @@
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
@@ -6980,7 +6992,7 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
@@ -6993,7 +7005,7 @@
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -7010,7 +7022,7 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>10</v>
@@ -7023,7 +7035,7 @@
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -7040,7 +7052,7 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>10</v>
@@ -7053,7 +7065,7 @@
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
@@ -7070,7 +7082,7 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>10</v>
@@ -7083,7 +7095,7 @@
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
@@ -7098,9 +7110,9 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>10</v>
@@ -7109,15 +7121,17 @@
         <v>243</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
+      <c r="I129" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="J129" s="5" t="s">
         <v>14</v>
       </c>
@@ -7128,9 +7142,9 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
     </row>
-    <row r="130" spans="1:16" ht="262.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>10</v>
@@ -7143,13 +7157,11 @@
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
-      <c r="I130" s="5" t="s">
-        <v>282</v>
-      </c>
+      <c r="I130" s="5"/>
       <c r="J130" s="5" t="s">
         <v>14</v>
       </c>
@@ -7162,7 +7174,7 @@
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>10</v>
@@ -7175,7 +7187,7 @@
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
@@ -7192,7 +7204,7 @@
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>10</v>
@@ -7205,7 +7217,7 @@
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
@@ -7222,7 +7234,7 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>10</v>
@@ -7235,7 +7247,7 @@
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -7250,9 +7262,9 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>10</v>
@@ -7265,7 +7277,7 @@
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7280,9 +7292,9 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
     </row>
-    <row r="135" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>10</v>
@@ -7295,7 +7307,7 @@
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7312,20 +7324,18 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>280</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7342,7 +7352,7 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
@@ -7353,7 +7363,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7370,7 +7380,7 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -7381,7 +7391,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -7398,7 +7408,7 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -7409,7 +7419,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
       <c r="F139" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7426,7 +7436,7 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -7437,7 +7447,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7454,7 +7464,7 @@
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -7465,7 +7475,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7482,7 +7492,7 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -7493,7 +7503,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7510,7 +7520,7 @@
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -7521,7 +7531,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -7538,7 +7548,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -7549,7 +7559,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7566,7 +7576,7 @@
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -7577,7 +7587,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7594,7 +7604,7 @@
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -7605,7 +7615,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -7622,7 +7632,7 @@
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>10</v>
@@ -7633,7 +7643,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -7648,55 +7658,51 @@
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
-      <c r="J148" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K148" s="5"/>
-      <c r="L148" s="5"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="5"/>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
-    </row>
-    <row r="149" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="7"/>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-      <c r="I149" s="7"/>
-      <c r="J149" s="7"/>
-      <c r="K149" s="7"/>
-      <c r="L149" s="7"/>
-      <c r="M149" s="7"/>
-      <c r="N149" s="7"/>
-      <c r="O149" s="7"/>
-      <c r="P149" s="7"/>
+    <row r="148" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
+      <c r="M148" s="7"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="7"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A149" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6"/>
+      <c r="J149" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>321</v>
@@ -7709,7 +7715,7 @@
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
@@ -7720,7 +7726,7 @@
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>321</v>
@@ -7733,7 +7739,7 @@
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
@@ -7744,7 +7750,7 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>321</v>
@@ -7753,11 +7759,11 @@
         <v>11</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6" t="s">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
@@ -7768,7 +7774,7 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>321</v>
@@ -7781,7 +7787,7 @@
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
@@ -7792,7 +7798,7 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>321</v>
@@ -7805,7 +7811,7 @@
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
@@ -7816,7 +7822,7 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>321</v>
@@ -7829,7 +7835,7 @@
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
@@ -7840,7 +7846,7 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>321</v>
@@ -7853,7 +7859,7 @@
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
@@ -7864,7 +7870,7 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>321</v>
@@ -7877,7 +7883,7 @@
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
@@ -7888,7 +7894,7 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>321</v>
@@ -7901,7 +7907,7 @@
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
@@ -7912,7 +7918,7 @@
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>321</v>
@@ -7925,7 +7931,7 @@
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>337</v>
+        <v>42</v>
       </c>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
@@ -7936,7 +7942,7 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>321</v>
@@ -7949,7 +7955,7 @@
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>42</v>
+        <v>340</v>
       </c>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
@@ -7960,7 +7966,7 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>321</v>
@@ -7973,7 +7979,7 @@
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
@@ -7984,7 +7990,7 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>321</v>
@@ -7997,7 +8003,7 @@
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
@@ -8008,7 +8014,7 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>321</v>
@@ -8021,7 +8027,7 @@
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
@@ -8032,7 +8038,7 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>321</v>
@@ -8045,7 +8051,7 @@
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
@@ -8056,7 +8062,7 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>321</v>
@@ -8069,7 +8075,7 @@
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>348</v>
+        <v>44</v>
       </c>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
@@ -8078,9 +8084,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>321</v>
@@ -8093,40 +8099,28 @@
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>44</v>
+        <v>351</v>
       </c>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
+      <c r="I166" s="6" t="s">
+        <v>352</v>
+      </c>
       <c r="J166" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" s="6"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
       <c r="E167" s="6"/>
-      <c r="F167" s="6" t="s">
-        <v>351</v>
-      </c>
+      <c r="F167" s="6"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
-      <c r="I167" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="J167" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I167" s="6"/>
+      <c r="J167" s="6"/>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
@@ -8176,43 +8170,43 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
+    <row r="172" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
+      <c r="F172" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-    </row>
-    <row r="173" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A173" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="I172" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" s="6"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
-      <c r="I173" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="J173" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I173" s="6"/>
+      <c r="J173" s="6"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
@@ -8263,20 +8257,32 @@
       <c r="J177" s="6"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
+      <c r="A178" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
+      <c r="F178" s="6" t="s">
+        <v>356</v>
+      </c>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
       <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
+      <c r="J178" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>321</v>
@@ -8289,7 +8295,7 @@
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
@@ -8300,7 +8306,7 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>321</v>
@@ -8313,7 +8319,7 @@
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
@@ -8324,7 +8330,7 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>321</v>
@@ -8337,7 +8343,7 @@
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
@@ -8346,9 +8352,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>321</v>
@@ -8359,41 +8365,29 @@
       <c r="D182" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E182" s="6"/>
       <c r="F182" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
+      <c r="I182" s="6" t="s">
+        <v>365</v>
+      </c>
       <c r="J182" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A183" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F183" s="6" t="s">
-        <v>364</v>
-      </c>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" s="6"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="6"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
-      <c r="I183" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="J183" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I183" s="6"/>
+      <c r="J183" s="6"/>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
@@ -8444,20 +8438,32 @@
       <c r="J187" s="6"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
+      <c r="A188" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
+      <c r="F188" s="6" t="s">
+        <v>368</v>
+      </c>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
       <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
+      <c r="J188" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>321</v>
@@ -8470,7 +8476,7 @@
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
@@ -8481,7 +8487,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>321</v>
@@ -8494,18 +8500,20 @@
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
+      <c r="I190" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J190" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>321</v>
@@ -8518,20 +8526,18 @@
       </c>
       <c r="E191" s="6"/>
       <c r="F191" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
-      <c r="I191" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I191" s="6"/>
       <c r="J191" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>321</v>
@@ -8544,7 +8550,7 @@
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
@@ -8553,9 +8559,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>321</v>
@@ -8568,7 +8574,7 @@
       </c>
       <c r="E193" s="6"/>
       <c r="F193" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
@@ -8579,7 +8585,7 @@
     </row>
     <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>321</v>
@@ -8592,7 +8598,7 @@
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
@@ -8603,7 +8609,7 @@
     </row>
     <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>321</v>
@@ -8616,7 +8622,7 @@
       </c>
       <c r="E195" s="6"/>
       <c r="F195" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
@@ -8625,9 +8631,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>321</v>
@@ -8640,7 +8646,7 @@
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="6" t="s">
-        <v>381</v>
+        <v>91</v>
       </c>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
@@ -8651,7 +8657,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>321</v>
@@ -8664,7 +8670,7 @@
       </c>
       <c r="E197" s="6"/>
       <c r="F197" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
@@ -8675,7 +8681,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>321</v>
@@ -8688,7 +8694,7 @@
       </c>
       <c r="E198" s="6"/>
       <c r="F198" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
@@ -8699,7 +8705,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>321</v>
@@ -8712,7 +8718,7 @@
       </c>
       <c r="E199" s="6"/>
       <c r="F199" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
@@ -8723,7 +8729,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>321</v>
@@ -8736,7 +8742,7 @@
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="6" t="s">
-        <v>97</v>
+        <v>387</v>
       </c>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
@@ -8747,7 +8753,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>321</v>
@@ -8760,7 +8766,7 @@
       </c>
       <c r="E201" s="6"/>
       <c r="F201" s="6" t="s">
-        <v>387</v>
+        <v>93</v>
       </c>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
@@ -8771,7 +8777,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>321</v>
@@ -8784,7 +8790,7 @@
       </c>
       <c r="E202" s="6"/>
       <c r="F202" s="6" t="s">
-        <v>93</v>
+        <v>390</v>
       </c>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
@@ -8795,7 +8801,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>321</v>
@@ -8808,7 +8814,7 @@
       </c>
       <c r="E203" s="6"/>
       <c r="F203" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
@@ -8819,7 +8825,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>321</v>
@@ -8832,7 +8838,7 @@
       </c>
       <c r="E204" s="6"/>
       <c r="F204" s="6" t="s">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
@@ -8843,7 +8849,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>321</v>
@@ -8856,7 +8862,7 @@
       </c>
       <c r="E205" s="6"/>
       <c r="F205" s="6" t="s">
-        <v>76</v>
+        <v>395</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
@@ -8867,7 +8873,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>321</v>
@@ -8880,7 +8886,7 @@
       </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
@@ -8891,31 +8897,31 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>367</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
+      <c r="I207" s="6" t="s">
+        <v>401</v>
+      </c>
       <c r="J207" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>321</v>
@@ -8926,20 +8932,18 @@
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
-      <c r="I208" s="6" t="s">
-        <v>401</v>
-      </c>
+      <c r="I208" s="6"/>
       <c r="J208" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>321</v>
@@ -8950,7 +8954,7 @@
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
@@ -8961,18 +8965,18 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
@@ -8981,9 +8985,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>321</v>
@@ -8994,7 +8998,7 @@
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
@@ -9003,9 +9007,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>321</v>
@@ -9016,7 +9020,7 @@
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
@@ -9025,9 +9029,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>321</v>
@@ -9036,39 +9040,29 @@
         <v>407</v>
       </c>
       <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
       <c r="F213" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
+      <c r="I213" s="6" t="s">
+        <v>415</v>
+      </c>
       <c r="J213" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A214" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C214" s="6" t="s">
-        <v>407</v>
-      </c>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="6"/>
       <c r="D214" s="6"/>
-      <c r="F214" s="6" t="s">
-        <v>414</v>
-      </c>
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
-      <c r="I214" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="J214" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I214" s="6"/>
+      <c r="J214" s="6"/>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
@@ -9155,20 +9149,30 @@
       <c r="J221" s="6"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="6"/>
+      <c r="A222" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>407</v>
+      </c>
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
+      <c r="F222" s="6" t="s">
+        <v>417</v>
+      </c>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
       <c r="I222" s="6"/>
-      <c r="J222" s="6"/>
+      <c r="J222" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>321</v>
@@ -9179,7 +9183,7 @@
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
@@ -9190,7 +9194,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>321</v>
@@ -9201,7 +9205,7 @@
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
@@ -9212,7 +9216,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>321</v>
@@ -9223,7 +9227,7 @@
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
@@ -9234,7 +9238,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>321</v>
@@ -9245,7 +9249,7 @@
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
@@ -9256,7 +9260,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>321</v>
@@ -9267,18 +9271,20 @@
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="6"/>
+      <c r="I227" s="6" t="s">
+        <v>924</v>
+      </c>
       <c r="J227" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>321</v>
@@ -9289,20 +9295,18 @@
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
-      <c r="I228" s="6" t="s">
-        <v>924</v>
-      </c>
+      <c r="I228" s="6"/>
       <c r="J228" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>321</v>
@@ -9313,7 +9317,7 @@
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
@@ -9324,7 +9328,7 @@
     </row>
     <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>321</v>
@@ -9335,7 +9339,7 @@
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
@@ -9344,9 +9348,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>321</v>
@@ -9357,7 +9361,7 @@
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
@@ -9368,18 +9372,18 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
@@ -9390,7 +9394,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>321</v>
@@ -9401,7 +9405,7 @@
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
@@ -9412,7 +9416,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>321</v>
@@ -9423,18 +9427,20 @@
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
-      <c r="I234" s="6"/>
+      <c r="I234" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J234" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>321</v>
@@ -9445,7 +9451,7 @@
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
@@ -9458,7 +9464,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>321</v>
@@ -9469,20 +9475,18 @@
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
-      <c r="I236" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I236" s="6"/>
       <c r="J236" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>321</v>
@@ -9493,7 +9497,7 @@
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
@@ -9502,9 +9506,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>321</v>
@@ -9515,7 +9519,7 @@
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
@@ -9526,7 +9530,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>321</v>
@@ -9537,7 +9541,7 @@
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
@@ -9548,7 +9552,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>321</v>
@@ -9559,7 +9563,7 @@
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
@@ -9570,7 +9574,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>321</v>
@@ -9581,18 +9585,20 @@
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
-      <c r="I241" s="6"/>
+      <c r="I241" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J241" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>321</v>
@@ -9603,7 +9609,7 @@
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
@@ -9614,9 +9620,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>321</v>
@@ -9627,40 +9633,28 @@
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
       <c r="I243" s="6" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="J243" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A244" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C244" s="6" t="s">
-        <v>437</v>
-      </c>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A244" s="6"/>
+      <c r="B244" s="6"/>
+      <c r="C244" s="6"/>
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
-      <c r="F244" s="6" t="s">
-        <v>460</v>
-      </c>
+      <c r="F244" s="6"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
-      <c r="I244" s="6" t="s">
-        <v>925</v>
-      </c>
-      <c r="J244" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I244" s="6"/>
+      <c r="J244" s="6"/>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
@@ -9722,21 +9716,31 @@
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="6"/>
+    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A250" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
-      <c r="F250" s="6"/>
+      <c r="F250" s="6" t="s">
+        <v>463</v>
+      </c>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
       <c r="I250" s="6"/>
-      <c r="J250" s="6"/>
-    </row>
-    <row r="251" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J250" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>321</v>
@@ -9747,7 +9751,7 @@
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
@@ -9756,9 +9760,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>321</v>
@@ -9767,39 +9771,29 @@
         <v>462</v>
       </c>
       <c r="D252" s="6"/>
-      <c r="E252" s="6"/>
       <c r="F252" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
-      <c r="I252" s="6"/>
+      <c r="I252" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="J252" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A253" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C253" s="6" t="s">
-        <v>462</v>
-      </c>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A253" s="6"/>
+      <c r="B253" s="6"/>
+      <c r="C253" s="6"/>
       <c r="D253" s="6"/>
-      <c r="F253" s="6" t="s">
-        <v>467</v>
-      </c>
+      <c r="E253" s="6"/>
+      <c r="F253" s="6"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
-      <c r="I253" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="J253" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I253" s="6"/>
+      <c r="J253" s="6"/>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
@@ -9826,20 +9820,30 @@
       <c r="J255" s="6"/>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="6"/>
+      <c r="A256" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>470</v>
+      </c>
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
-      <c r="F256" s="6"/>
+      <c r="F256" s="6" t="s">
+        <v>471</v>
+      </c>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
       <c r="I256" s="6"/>
-      <c r="J256" s="6"/>
+      <c r="J256" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>321</v>
@@ -9850,7 +9854,7 @@
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
@@ -9861,7 +9865,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>321</v>
@@ -9872,7 +9876,7 @@
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
@@ -9881,9 +9885,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>321</v>
@@ -9894,7 +9898,7 @@
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
@@ -9905,7 +9909,7 @@
     </row>
     <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>321</v>
@@ -9916,7 +9920,7 @@
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
@@ -9925,9 +9929,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>321</v>
@@ -9938,7 +9942,7 @@
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
@@ -9947,9 +9951,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>321</v>
@@ -9960,7 +9964,7 @@
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
@@ -9971,7 +9975,7 @@
     </row>
     <row r="263" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>321</v>
@@ -9982,7 +9986,7 @@
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
@@ -9993,7 +9997,7 @@
     </row>
     <row r="264" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>321</v>
@@ -10004,7 +10008,7 @@
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
@@ -10013,9 +10017,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>321</v>
@@ -10026,7 +10030,7 @@
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
@@ -10037,7 +10041,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>321</v>
@@ -10048,7 +10052,7 @@
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
@@ -10059,7 +10063,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>321</v>
@@ -10070,7 +10074,7 @@
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
@@ -10079,9 +10083,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>321</v>
@@ -10092,7 +10096,7 @@
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
@@ -10101,9 +10105,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>321</v>
@@ -10114,7 +10118,7 @@
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
@@ -10125,18 +10129,18 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
@@ -10147,7 +10151,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>321</v>
@@ -10158,7 +10162,7 @@
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
@@ -10169,7 +10173,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>321</v>
@@ -10180,7 +10184,7 @@
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
@@ -10191,18 +10195,18 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
@@ -10213,7 +10217,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>321</v>
@@ -10224,7 +10228,7 @@
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
@@ -10235,7 +10239,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>321</v>
@@ -10246,7 +10250,7 @@
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
@@ -10257,7 +10261,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>321</v>
@@ -10268,7 +10272,7 @@
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6" t="s">
-        <v>511</v>
+        <v>108</v>
       </c>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
@@ -10279,7 +10283,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>321</v>
@@ -10290,7 +10294,7 @@
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6" t="s">
-        <v>108</v>
+        <v>514</v>
       </c>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
@@ -10301,7 +10305,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>321</v>
@@ -10312,7 +10316,7 @@
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
@@ -10323,7 +10327,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>321</v>
@@ -10334,7 +10338,7 @@
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
@@ -10345,7 +10349,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>321</v>
@@ -10356,7 +10360,7 @@
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
@@ -10367,7 +10371,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>321</v>
@@ -10378,7 +10382,7 @@
       <c r="D281" s="6"/>
       <c r="E281" s="6"/>
       <c r="F281" s="6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
@@ -10387,66 +10391,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="D282" s="6"/>
-      <c r="E282" s="6"/>
       <c r="F282" s="6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="6"/>
+      <c r="I282" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="J282" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A283" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>524</v>
-      </c>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283" s="6"/>
+      <c r="B283" s="6"/>
+      <c r="C283" s="6"/>
       <c r="D283" s="6"/>
-      <c r="F283" s="6" t="s">
-        <v>525</v>
-      </c>
+      <c r="E283" s="6"/>
+      <c r="F283" s="6"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
-      <c r="I283" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="J283" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A284" s="6"/>
-      <c r="B284" s="6"/>
-      <c r="C284" s="6"/>
+      <c r="I283" s="6"/>
+      <c r="J283" s="6"/>
+    </row>
+    <row r="284" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A284" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D284" s="6"/>
       <c r="E284" s="6"/>
-      <c r="F284" s="6"/>
+      <c r="F284" s="6" t="s">
+        <v>528</v>
+      </c>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
       <c r="I284" s="6"/>
-      <c r="J284" s="6"/>
-    </row>
-    <row r="285" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J284" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>321</v>
@@ -10457,7 +10461,7 @@
       <c r="D285" s="6"/>
       <c r="E285" s="6"/>
       <c r="F285" s="6" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
@@ -10468,7 +10472,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>321</v>
@@ -10479,7 +10483,7 @@
       <c r="D286" s="6"/>
       <c r="E286" s="6"/>
       <c r="F286" s="6" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
@@ -10490,18 +10494,18 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D287" s="6"/>
       <c r="E287" s="6"/>
       <c r="F287" s="6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
@@ -10512,7 +10516,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>321</v>
@@ -10523,7 +10527,7 @@
       <c r="D288" s="6"/>
       <c r="E288" s="6"/>
       <c r="F288" s="6" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
@@ -10534,7 +10538,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>321</v>
@@ -10545,7 +10549,7 @@
       <c r="D289" s="6"/>
       <c r="E289" s="6"/>
       <c r="F289" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
@@ -10556,7 +10560,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>321</v>
@@ -10567,7 +10571,7 @@
       <c r="D290" s="6"/>
       <c r="E290" s="6"/>
       <c r="F290" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
@@ -10578,7 +10582,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>321</v>
@@ -10589,7 +10593,7 @@
       <c r="D291" s="6"/>
       <c r="E291" s="6"/>
       <c r="F291" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
@@ -10598,9 +10602,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>321</v>
@@ -10611,7 +10615,7 @@
       <c r="D292" s="6"/>
       <c r="E292" s="6"/>
       <c r="F292" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
@@ -10620,9 +10624,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>321</v>
@@ -10633,7 +10637,7 @@
       <c r="D293" s="6"/>
       <c r="E293" s="6"/>
       <c r="F293" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
@@ -10644,7 +10648,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>321</v>
@@ -10655,7 +10659,7 @@
       <c r="D294" s="6"/>
       <c r="E294" s="6"/>
       <c r="F294" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
@@ -10666,7 +10670,7 @@
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>321</v>
@@ -10677,7 +10681,7 @@
       <c r="D295" s="6"/>
       <c r="E295" s="6"/>
       <c r="F295" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
@@ -10686,9 +10690,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>321</v>
@@ -10697,39 +10701,29 @@
         <v>534</v>
       </c>
       <c r="D296" s="6"/>
-      <c r="E296" s="6"/>
       <c r="F296" s="6" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="6"/>
+      <c r="I296" s="6" t="s">
+        <v>554</v>
+      </c>
       <c r="J296" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A297" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C297" s="6" t="s">
-        <v>534</v>
-      </c>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" s="6"/>
+      <c r="B297" s="6"/>
+      <c r="C297" s="6"/>
       <c r="D297" s="6"/>
-      <c r="F297" s="6" t="s">
-        <v>553</v>
-      </c>
+      <c r="E297" s="6"/>
+      <c r="F297" s="6"/>
       <c r="G297" s="6"/>
       <c r="H297" s="6"/>
-      <c r="I297" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="J297" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I297" s="6"/>
+      <c r="J297" s="6"/>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="6"/>
@@ -10779,41 +10773,41 @@
       <c r="I301" s="6"/>
       <c r="J301" s="6"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A302" s="6"/>
-      <c r="B302" s="6"/>
-      <c r="C302" s="6"/>
+    <row r="302" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A302" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D302" s="6"/>
       <c r="E302" s="6"/>
-      <c r="F302" s="6"/>
+      <c r="F302" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="G302" s="6"/>
       <c r="H302" s="6"/>
-      <c r="I302" s="6"/>
-      <c r="J302" s="6"/>
-    </row>
-    <row r="303" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A303" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="B303" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C303" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="I302" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="J302" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A303" s="6"/>
+      <c r="B303" s="6"/>
+      <c r="C303" s="6"/>
       <c r="D303" s="6"/>
       <c r="E303" s="6"/>
-      <c r="F303" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="F303" s="6"/>
       <c r="G303" s="6"/>
       <c r="H303" s="6"/>
-      <c r="I303" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="J303" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I303" s="6"/>
+      <c r="J303" s="6"/>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
@@ -11128,20 +11122,30 @@
       <c r="J329" s="6"/>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A330" s="6"/>
-      <c r="B330" s="6"/>
-      <c r="C330" s="6"/>
+      <c r="A330" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="D330" s="6"/>
       <c r="E330" s="6"/>
-      <c r="F330" s="6"/>
+      <c r="F330" s="6" t="s">
+        <v>559</v>
+      </c>
       <c r="G330" s="6"/>
       <c r="H330" s="6"/>
       <c r="I330" s="6"/>
-      <c r="J330" s="6"/>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J330" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A331" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B331" s="6" t="s">
         <v>321</v>
@@ -11152,7 +11156,7 @@
       <c r="D331" s="6"/>
       <c r="E331" s="6"/>
       <c r="F331" s="6" t="s">
-        <v>559</v>
+        <v>255</v>
       </c>
       <c r="G331" s="6"/>
       <c r="H331" s="6"/>
@@ -11161,9 +11165,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B332" s="6" t="s">
         <v>321</v>
@@ -11174,7 +11178,7 @@
       <c r="D332" s="6"/>
       <c r="E332" s="6"/>
       <c r="F332" s="6" t="s">
-        <v>255</v>
+        <v>562</v>
       </c>
       <c r="G332" s="6"/>
       <c r="H332" s="6"/>
@@ -11185,7 +11189,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B333" s="6" t="s">
         <v>321</v>
@@ -11196,7 +11200,7 @@
       <c r="D333" s="6"/>
       <c r="E333" s="6"/>
       <c r="F333" s="6" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G333" s="6"/>
       <c r="H333" s="6"/>
@@ -11207,7 +11211,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B334" s="6" t="s">
         <v>321</v>
@@ -11218,7 +11222,7 @@
       <c r="D334" s="6"/>
       <c r="E334" s="6"/>
       <c r="F334" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G334" s="6"/>
       <c r="H334" s="6"/>
@@ -11229,18 +11233,18 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B335" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>534</v>
+        <v>568</v>
       </c>
       <c r="D335" s="6"/>
       <c r="E335" s="6"/>
       <c r="F335" s="6" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G335" s="6"/>
       <c r="H335" s="6"/>
@@ -11251,7 +11255,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="6" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B336" s="6" t="s">
         <v>321</v>
@@ -11262,7 +11266,7 @@
       <c r="D336" s="6"/>
       <c r="E336" s="6"/>
       <c r="F336" s="6" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G336" s="6"/>
       <c r="H336" s="6"/>
@@ -11273,18 +11277,18 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B337" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D337" s="6"/>
       <c r="E337" s="6"/>
       <c r="F337" s="6" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G337" s="6"/>
       <c r="H337" s="6"/>
@@ -11295,7 +11299,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="6" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B338" s="6" t="s">
         <v>321</v>
@@ -11306,7 +11310,7 @@
       <c r="D338" s="6"/>
       <c r="E338" s="6"/>
       <c r="F338" s="6" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G338" s="6"/>
       <c r="H338" s="6"/>
@@ -11317,7 +11321,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="6" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B339" s="6" t="s">
         <v>321</v>
@@ -11328,7 +11332,7 @@
       <c r="D339" s="6"/>
       <c r="E339" s="6"/>
       <c r="F339" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G339" s="6"/>
       <c r="H339" s="6"/>
@@ -11339,18 +11343,18 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B340" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="D340" s="6"/>
       <c r="E340" s="6"/>
       <c r="F340" s="6" t="s">
-        <v>578</v>
+        <v>504</v>
       </c>
       <c r="G340" s="6"/>
       <c r="H340" s="6"/>
@@ -11361,7 +11365,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B341" s="6" t="s">
         <v>321</v>
@@ -11372,7 +11376,7 @@
       <c r="D341" s="6"/>
       <c r="E341" s="6"/>
       <c r="F341" s="6" t="s">
-        <v>504</v>
+        <v>582</v>
       </c>
       <c r="G341" s="6"/>
       <c r="H341" s="6"/>
@@ -11383,7 +11387,7 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B342" s="6" t="s">
         <v>321</v>
@@ -11394,7 +11398,7 @@
       <c r="D342" s="6"/>
       <c r="E342" s="6"/>
       <c r="F342" s="6" t="s">
-        <v>582</v>
+        <v>307</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -11405,18 +11409,18 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B343" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D343" s="6"/>
       <c r="E343" s="6"/>
       <c r="F343" s="6" t="s">
-        <v>307</v>
+        <v>586</v>
       </c>
       <c r="G343" s="6"/>
       <c r="H343" s="6"/>
@@ -11427,7 +11431,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B344" s="6" t="s">
         <v>321</v>
@@ -11438,7 +11442,7 @@
       <c r="D344" s="6"/>
       <c r="E344" s="6"/>
       <c r="F344" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G344" s="6"/>
       <c r="H344" s="6"/>
@@ -11449,7 +11453,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="6" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B345" s="6" t="s">
         <v>321</v>
@@ -11460,7 +11464,7 @@
       <c r="D345" s="6"/>
       <c r="E345" s="6"/>
       <c r="F345" s="6" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G345" s="6"/>
       <c r="H345" s="6"/>
@@ -11471,7 +11475,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B346" s="6" t="s">
         <v>321</v>
@@ -11482,7 +11486,7 @@
       <c r="D346" s="6"/>
       <c r="E346" s="6"/>
       <c r="F346" s="6" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G346" s="6"/>
       <c r="H346" s="6"/>
@@ -11491,9 +11495,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="6" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B347" s="6" t="s">
         <v>321</v>
@@ -11504,7 +11508,7 @@
       <c r="D347" s="6"/>
       <c r="E347" s="6"/>
       <c r="F347" s="6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G347" s="6"/>
       <c r="H347" s="6"/>
@@ -11513,20 +11517,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="6" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B348" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="6"/>
       <c r="F348" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G348" s="6"/>
       <c r="H348" s="6"/>
@@ -11537,7 +11541,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="6" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B349" s="6" t="s">
         <v>321</v>
@@ -11548,7 +11552,7 @@
       <c r="D349" s="6"/>
       <c r="E349" s="6"/>
       <c r="F349" s="6" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="6"/>
@@ -11559,7 +11563,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B350" s="6" t="s">
         <v>321</v>
@@ -11570,7 +11574,7 @@
       <c r="D350" s="6"/>
       <c r="E350" s="6"/>
       <c r="F350" s="6" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="6"/>
@@ -11581,7 +11585,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B351" s="6" t="s">
         <v>321</v>
@@ -11592,7 +11596,7 @@
       <c r="D351" s="6"/>
       <c r="E351" s="6"/>
       <c r="F351" s="6" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="6"/>
@@ -11603,7 +11607,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="6" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B352" s="6" t="s">
         <v>321</v>
@@ -11614,7 +11618,7 @@
       <c r="D352" s="6"/>
       <c r="E352" s="6"/>
       <c r="F352" s="6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G352" s="6"/>
       <c r="H352" s="6"/>
@@ -11625,7 +11629,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B353" s="6" t="s">
         <v>321</v>
@@ -11636,7 +11640,7 @@
       <c r="D353" s="6"/>
       <c r="E353" s="6"/>
       <c r="F353" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G353" s="6"/>
       <c r="H353" s="6"/>
@@ -11645,9 +11649,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A354" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B354" s="6" t="s">
         <v>321</v>
@@ -11658,7 +11662,7 @@
       <c r="D354" s="6"/>
       <c r="E354" s="6"/>
       <c r="F354" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G354" s="6"/>
       <c r="H354" s="6"/>
@@ -11667,9 +11671,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B355" s="6" t="s">
         <v>321</v>
@@ -11680,7 +11684,7 @@
       <c r="D355" s="6"/>
       <c r="E355" s="6"/>
       <c r="F355" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="G355" s="6"/>
       <c r="H355" s="6"/>
@@ -11689,43 +11693,45 @@
         <v>14</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A356" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="B356" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C356" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="D356" s="6"/>
-      <c r="E356" s="6"/>
-      <c r="F356" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="G356" s="6"/>
-      <c r="H356" s="6"/>
-      <c r="I356" s="6"/>
-      <c r="J356" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="9"/>
-      <c r="B357" s="9"/>
-      <c r="C357" s="9"/>
-      <c r="D357" s="9"/>
-      <c r="E357" s="9"/>
-      <c r="F357" s="9"/>
-      <c r="G357" s="9"/>
-      <c r="H357" s="9"/>
-      <c r="I357" s="9"/>
-      <c r="J357" s="9"/>
+    <row r="356" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A356" s="9"/>
+      <c r="B356" s="9"/>
+      <c r="C356" s="9"/>
+      <c r="D356" s="9"/>
+      <c r="E356" s="9"/>
+      <c r="F356" s="9"/>
+      <c r="G356" s="9"/>
+      <c r="H356" s="9"/>
+      <c r="I356" s="9"/>
+      <c r="J356" s="9"/>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A357" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E357" s="6"/>
+      <c r="F357" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G357" s="6"/>
+      <c r="H357" s="6"/>
+      <c r="I357" s="6"/>
+      <c r="J357" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B358" s="6" t="s">
         <v>613</v>
@@ -11738,7 +11744,7 @@
       </c>
       <c r="E358" s="6"/>
       <c r="F358" s="6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G358" s="6"/>
       <c r="H358" s="6"/>
@@ -11749,7 +11755,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B359" s="6" t="s">
         <v>613</v>
@@ -11758,11 +11764,11 @@
         <v>11</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E359" s="6"/>
       <c r="F359" s="6" t="s">
-        <v>18</v>
+        <v>616</v>
       </c>
       <c r="G359" s="6"/>
       <c r="H359" s="6"/>
@@ -11771,9 +11777,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A360" s="6" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B360" s="6" t="s">
         <v>613</v>
@@ -11785,41 +11791,29 @@
         <v>37</v>
       </c>
       <c r="E360" s="6"/>
-      <c r="F360" s="6" t="s">
-        <v>616</v>
+      <c r="F360" s="10" t="s">
+        <v>618</v>
       </c>
       <c r="G360" s="6"/>
       <c r="H360" s="6"/>
-      <c r="I360" s="6"/>
+      <c r="I360" s="10" t="s">
+        <v>619</v>
+      </c>
       <c r="J360" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A361" s="6" t="s">
-        <v>617</v>
-      </c>
-      <c r="B361" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C361" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D361" s="6" t="s">
-        <v>37</v>
-      </c>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A361" s="6"/>
+      <c r="B361" s="6"/>
+      <c r="C361" s="6"/>
+      <c r="D361" s="6"/>
       <c r="E361" s="6"/>
-      <c r="F361" s="10" t="s">
-        <v>618</v>
-      </c>
+      <c r="F361" s="6"/>
       <c r="G361" s="6"/>
       <c r="H361" s="6"/>
-      <c r="I361" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="J361" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I361" s="6"/>
+      <c r="J361" s="6"/>
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
@@ -11870,20 +11864,32 @@
       <c r="J365" s="6"/>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A366" s="6"/>
-      <c r="B366" s="6"/>
-      <c r="C366" s="6"/>
-      <c r="D366" s="6"/>
+      <c r="A366" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D366" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E366" s="6"/>
-      <c r="F366" s="6"/>
+      <c r="F366" s="6" t="s">
+        <v>621</v>
+      </c>
       <c r="G366" s="6"/>
       <c r="H366" s="6"/>
       <c r="I366" s="6"/>
-      <c r="J366" s="6"/>
+      <c r="J366" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="6" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B367" s="6" t="s">
         <v>613</v>
@@ -11896,7 +11902,7 @@
       </c>
       <c r="E367" s="6"/>
       <c r="F367" s="6" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G367" s="6"/>
       <c r="H367" s="6"/>
@@ -11907,7 +11913,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="6" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B368" s="6" t="s">
         <v>613</v>
@@ -11920,7 +11926,7 @@
       </c>
       <c r="E368" s="6"/>
       <c r="F368" s="6" t="s">
-        <v>623</v>
+        <v>329</v>
       </c>
       <c r="G368" s="6"/>
       <c r="H368" s="6"/>
@@ -11931,7 +11937,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B369" s="6" t="s">
         <v>613</v>
@@ -11944,7 +11950,7 @@
       </c>
       <c r="E369" s="6"/>
       <c r="F369" s="6" t="s">
-        <v>329</v>
+        <v>626</v>
       </c>
       <c r="G369" s="6"/>
       <c r="H369" s="6"/>
@@ -11955,7 +11961,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="6" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B370" s="6" t="s">
         <v>613</v>
@@ -11968,7 +11974,7 @@
       </c>
       <c r="E370" s="6"/>
       <c r="F370" s="6" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G370" s="6"/>
       <c r="H370" s="6"/>
@@ -11979,7 +11985,7 @@
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="6" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B371" s="6" t="s">
         <v>613</v>
@@ -11992,7 +11998,7 @@
       </c>
       <c r="E371" s="6"/>
       <c r="F371" s="6" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G371" s="6"/>
       <c r="H371" s="6"/>
@@ -12003,7 +12009,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="6" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B372" s="6" t="s">
         <v>613</v>
@@ -12016,7 +12022,7 @@
       </c>
       <c r="E372" s="6"/>
       <c r="F372" s="6" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G372" s="6"/>
       <c r="H372" s="6"/>
@@ -12027,7 +12033,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="6" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B373" s="6" t="s">
         <v>613</v>
@@ -12040,7 +12046,7 @@
       </c>
       <c r="E373" s="6"/>
       <c r="F373" s="6" t="s">
-        <v>632</v>
+        <v>42</v>
       </c>
       <c r="G373" s="6"/>
       <c r="H373" s="6"/>
@@ -12049,9 +12055,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B374" s="6" t="s">
         <v>613</v>
@@ -12064,7 +12070,7 @@
       </c>
       <c r="E374" s="6"/>
       <c r="F374" s="6" t="s">
-        <v>42</v>
+        <v>635</v>
       </c>
       <c r="G374" s="6"/>
       <c r="H374" s="6"/>
@@ -12073,9 +12079,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="6" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B375" s="6" t="s">
         <v>613</v>
@@ -12088,7 +12094,7 @@
       </c>
       <c r="E375" s="6"/>
       <c r="F375" s="6" t="s">
-        <v>635</v>
+        <v>342</v>
       </c>
       <c r="G375" s="6"/>
       <c r="H375" s="6"/>
@@ -12099,7 +12105,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B376" s="6" t="s">
         <v>613</v>
@@ -12112,7 +12118,7 @@
       </c>
       <c r="E376" s="6"/>
       <c r="F376" s="6" t="s">
-        <v>342</v>
+        <v>638</v>
       </c>
       <c r="G376" s="6"/>
       <c r="H376" s="6"/>
@@ -12123,7 +12129,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="6" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B377" s="6" t="s">
         <v>613</v>
@@ -12136,7 +12142,7 @@
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="6" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G377" s="6"/>
       <c r="H377" s="6"/>
@@ -12147,7 +12153,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B378" s="6" t="s">
         <v>613</v>
@@ -12160,7 +12166,7 @@
       </c>
       <c r="E378" s="6"/>
       <c r="F378" s="6" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G378" s="6"/>
       <c r="H378" s="6"/>
@@ -12169,33 +12175,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A379" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="B379" s="6" t="s">
+    <row r="380" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="B380" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C379" s="6" t="s">
+      <c r="C380" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D379" s="10" t="s">
+      <c r="D380" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E379" s="6"/>
-      <c r="F379" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="G379" s="6"/>
-      <c r="H379" s="6"/>
-      <c r="I379" s="6"/>
-      <c r="J379" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="10" t="s">
-        <v>643</v>
+      <c r="E380" s="6"/>
+      <c r="F380" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="G380" s="6"/>
+      <c r="H380" s="6"/>
+      <c r="I380" s="6"/>
+      <c r="J380" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A381" s="6" t="s">
+        <v>645</v>
       </c>
       <c r="B381" s="6" t="s">
         <v>613</v>
@@ -12208,40 +12214,28 @@
       </c>
       <c r="E381" s="6"/>
       <c r="F381" s="10" t="s">
-        <v>644</v>
+        <v>351</v>
       </c>
       <c r="G381" s="6"/>
       <c r="H381" s="6"/>
-      <c r="I381" s="6"/>
+      <c r="I381" s="10" t="s">
+        <v>646</v>
+      </c>
       <c r="J381" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A382" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="B382" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C382" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D382" s="10" t="s">
-        <v>20</v>
-      </c>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A382" s="6"/>
+      <c r="B382" s="6"/>
+      <c r="C382" s="6"/>
+      <c r="D382" s="6"/>
       <c r="E382" s="6"/>
-      <c r="F382" s="10" t="s">
-        <v>351</v>
-      </c>
+      <c r="F382" s="6"/>
       <c r="G382" s="6"/>
       <c r="H382" s="6"/>
-      <c r="I382" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="J382" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I382" s="6"/>
+      <c r="J382" s="6"/>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
@@ -12267,43 +12261,43 @@
       <c r="I384" s="6"/>
       <c r="J384" s="6"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A385" s="6"/>
-      <c r="B385" s="6"/>
-      <c r="C385" s="6"/>
-      <c r="D385" s="6"/>
+    <row r="385" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A385" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D385" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="E385" s="6"/>
-      <c r="F385" s="6"/>
+      <c r="F385" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="G385" s="6"/>
       <c r="H385" s="6"/>
-      <c r="I385" s="6"/>
-      <c r="J385" s="6"/>
-    </row>
-    <row r="386" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A386" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B386" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C386" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D386" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="I385" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="J385" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A386" s="6"/>
+      <c r="B386" s="6"/>
+      <c r="C386" s="6"/>
+      <c r="D386" s="6"/>
       <c r="E386" s="6"/>
-      <c r="F386" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="F386" s="6"/>
       <c r="G386" s="6"/>
       <c r="H386" s="6"/>
-      <c r="I386" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="J386" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I386" s="6"/>
+      <c r="J386" s="6"/>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
@@ -12377,43 +12371,43 @@
       <c r="I392" s="6"/>
       <c r="J392" s="6"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A393" s="6"/>
-      <c r="B393" s="6"/>
-      <c r="C393" s="6"/>
-      <c r="D393" s="6"/>
+    <row r="393" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A393" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E393" s="6"/>
-      <c r="F393" s="6"/>
+      <c r="F393" s="6" t="s">
+        <v>651</v>
+      </c>
       <c r="G393" s="6"/>
       <c r="H393" s="6"/>
-      <c r="I393" s="6"/>
-      <c r="J393" s="6"/>
-    </row>
-    <row r="394" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A394" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B394" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C394" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D394" s="6" t="s">
-        <v>650</v>
-      </c>
+      <c r="I393" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="J393" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A394" s="6"/>
+      <c r="B394" s="6"/>
+      <c r="C394" s="6"/>
+      <c r="D394" s="6"/>
       <c r="E394" s="6"/>
-      <c r="F394" s="6" t="s">
-        <v>651</v>
-      </c>
+      <c r="F394" s="6"/>
       <c r="G394" s="6"/>
       <c r="H394" s="6"/>
-      <c r="I394" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="J394" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I394" s="6"/>
+      <c r="J394" s="6"/>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="6"/>
@@ -12464,20 +12458,32 @@
       <c r="J398" s="6"/>
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A399" s="6"/>
-      <c r="B399" s="6"/>
-      <c r="C399" s="6"/>
-      <c r="D399" s="6"/>
+      <c r="A399" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B399" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C399" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D399" s="6" t="s">
+        <v>650</v>
+      </c>
       <c r="E399" s="6"/>
-      <c r="F399" s="6"/>
+      <c r="F399" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="G399" s="6"/>
       <c r="H399" s="6"/>
       <c r="I399" s="6"/>
-      <c r="J399" s="6"/>
+      <c r="J399" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>613</v>
@@ -12490,7 +12496,7 @@
       </c>
       <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
-        <v>62</v>
+        <v>655</v>
       </c>
       <c r="G400" s="6"/>
       <c r="H400" s="6"/>
@@ -12499,9 +12505,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A401" s="6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B401" s="6" t="s">
         <v>613</v>
@@ -12514,7 +12520,7 @@
       </c>
       <c r="E401" s="6"/>
       <c r="F401" s="6" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G401" s="6"/>
       <c r="H401" s="6"/>
@@ -12523,9 +12529,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="6" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B402" s="6" t="s">
         <v>613</v>
@@ -12538,7 +12544,7 @@
       </c>
       <c r="E402" s="6"/>
       <c r="F402" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G402" s="6"/>
       <c r="H402" s="6"/>
@@ -12549,7 +12555,7 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="6" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B403" s="6" t="s">
         <v>613</v>
@@ -12562,18 +12568,20 @@
       </c>
       <c r="E403" s="6"/>
       <c r="F403" s="6" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
-      <c r="I403" s="6"/>
+      <c r="I403" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J403" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="6" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B404" s="6" t="s">
         <v>613</v>
@@ -12586,20 +12594,18 @@
       </c>
       <c r="E404" s="6"/>
       <c r="F404" s="6" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G404" s="6"/>
       <c r="H404" s="6"/>
-      <c r="I404" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I404" s="6"/>
       <c r="J404" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="6" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B405" s="6" t="s">
         <v>613</v>
@@ -12612,7 +12618,7 @@
       </c>
       <c r="E405" s="6"/>
       <c r="F405" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G405" s="6"/>
       <c r="H405" s="6"/>
@@ -12621,9 +12627,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B406" s="6" t="s">
         <v>613</v>
@@ -12636,7 +12642,7 @@
       </c>
       <c r="E406" s="6"/>
       <c r="F406" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G406" s="6"/>
       <c r="H406" s="6"/>
@@ -12645,9 +12651,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="6" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B407" s="6" t="s">
         <v>613</v>
@@ -12660,7 +12666,7 @@
       </c>
       <c r="E407" s="6"/>
       <c r="F407" s="6" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="G407" s="6"/>
       <c r="H407" s="6"/>
@@ -12671,7 +12677,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="6" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B408" s="6" t="s">
         <v>613</v>
@@ -12680,11 +12686,11 @@
         <v>11</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="E408" s="6"/>
       <c r="F408" s="6" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G408" s="6"/>
       <c r="H408" s="6"/>
@@ -12695,7 +12701,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="6" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B409" s="6" t="s">
         <v>613</v>
@@ -12708,7 +12714,7 @@
       </c>
       <c r="E409" s="6"/>
       <c r="F409" s="6" t="s">
-        <v>672</v>
+        <v>97</v>
       </c>
       <c r="G409" s="6"/>
       <c r="H409" s="6"/>
@@ -12719,7 +12725,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B410" s="6" t="s">
         <v>613</v>
@@ -12732,7 +12738,7 @@
       </c>
       <c r="E410" s="6"/>
       <c r="F410" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G410" s="6"/>
       <c r="H410" s="6"/>
@@ -12743,7 +12749,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B411" s="6" t="s">
         <v>613</v>
@@ -12755,8 +12761,8 @@
         <v>671</v>
       </c>
       <c r="E411" s="6"/>
-      <c r="F411" s="6" t="s">
-        <v>99</v>
+      <c r="F411" s="10" t="s">
+        <v>676</v>
       </c>
       <c r="G411" s="6"/>
       <c r="H411" s="6"/>
@@ -12767,7 +12773,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="6" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B412" s="6" t="s">
         <v>613</v>
@@ -12779,8 +12785,8 @@
         <v>671</v>
       </c>
       <c r="E412" s="6"/>
-      <c r="F412" s="10" t="s">
-        <v>676</v>
+      <c r="F412" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="G412" s="6"/>
       <c r="H412" s="6"/>
@@ -12791,7 +12797,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>613</v>
@@ -12804,7 +12810,7 @@
       </c>
       <c r="E413" s="6"/>
       <c r="F413" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G413" s="6"/>
       <c r="H413" s="6"/>
@@ -12815,7 +12821,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="6" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>613</v>
@@ -12827,8 +12833,8 @@
         <v>671</v>
       </c>
       <c r="E414" s="6"/>
-      <c r="F414" s="6" t="s">
-        <v>91</v>
+      <c r="F414" s="10" t="s">
+        <v>680</v>
       </c>
       <c r="G414" s="6"/>
       <c r="H414" s="6"/>
@@ -12839,7 +12845,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="6" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B415" s="6" t="s">
         <v>613</v>
@@ -12851,8 +12857,8 @@
         <v>671</v>
       </c>
       <c r="E415" s="6"/>
-      <c r="F415" s="10" t="s">
-        <v>680</v>
+      <c r="F415" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="G415" s="6"/>
       <c r="H415" s="6"/>
@@ -12862,28 +12868,16 @@
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A416" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="B416" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C416" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D416" s="6" t="s">
-        <v>671</v>
-      </c>
+      <c r="A416" s="6"/>
+      <c r="B416" s="6"/>
+      <c r="C416" s="6"/>
+      <c r="D416" s="6"/>
       <c r="E416" s="6"/>
-      <c r="F416" s="6" t="s">
-        <v>93</v>
-      </c>
+      <c r="F416" s="6"/>
       <c r="G416" s="6"/>
       <c r="H416" s="6"/>
       <c r="I416" s="6"/>
-      <c r="J416" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="J416" s="6"/>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="6"/>
@@ -12922,20 +12916,30 @@
       <c r="J419" s="6"/>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A420" s="6"/>
-      <c r="B420" s="6"/>
-      <c r="C420" s="6"/>
+      <c r="A420" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C420" s="10" t="s">
+        <v>399</v>
+      </c>
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
-      <c r="F420" s="6"/>
+      <c r="F420" s="6" t="s">
+        <v>194</v>
+      </c>
       <c r="G420" s="6"/>
       <c r="H420" s="6"/>
       <c r="I420" s="6"/>
-      <c r="J420" s="6"/>
+      <c r="J420" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B421" s="6" t="s">
         <v>613</v>
@@ -12946,7 +12950,7 @@
       <c r="D421" s="6"/>
       <c r="E421" s="6"/>
       <c r="F421" s="6" t="s">
-        <v>194</v>
+        <v>684</v>
       </c>
       <c r="G421" s="6"/>
       <c r="H421" s="6"/>
@@ -12957,7 +12961,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="6" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B422" s="6" t="s">
         <v>613</v>
@@ -12968,7 +12972,7 @@
       <c r="D422" s="6"/>
       <c r="E422" s="6"/>
       <c r="F422" s="6" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G422" s="6"/>
       <c r="H422" s="6"/>
@@ -12979,7 +12983,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="6" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B423" s="6" t="s">
         <v>613</v>
@@ -12990,7 +12994,7 @@
       <c r="D423" s="6"/>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G423" s="6"/>
       <c r="H423" s="6"/>
@@ -13001,7 +13005,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="6" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B424" s="6" t="s">
         <v>613</v>
@@ -13012,7 +13016,7 @@
       <c r="D424" s="6"/>
       <c r="E424" s="6"/>
       <c r="F424" s="6" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G424" s="6"/>
       <c r="H424" s="6"/>
@@ -13023,18 +13027,18 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="6" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B425" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C425" s="10" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D425" s="6"/>
       <c r="E425" s="6"/>
       <c r="F425" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G425" s="6"/>
       <c r="H425" s="6"/>
@@ -13045,18 +13049,18 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="6" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B426" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C426" s="10" t="s">
-        <v>407</v>
+      <c r="C426" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="D426" s="6"/>
       <c r="E426" s="6"/>
       <c r="F426" s="6" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G426" s="6"/>
       <c r="H426" s="6"/>
@@ -13067,7 +13071,7 @@
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="6" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B427" s="6" t="s">
         <v>613</v>
@@ -13078,7 +13082,7 @@
       <c r="D427" s="6"/>
       <c r="E427" s="6"/>
       <c r="F427" s="6" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G427" s="6"/>
       <c r="H427" s="6"/>
@@ -13087,9 +13091,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A428" s="6" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B428" s="6" t="s">
         <v>613</v>
@@ -13100,7 +13104,7 @@
       <c r="D428" s="6"/>
       <c r="E428" s="6"/>
       <c r="F428" s="6" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G428" s="6"/>
       <c r="H428" s="6"/>
@@ -13109,42 +13113,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="429" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="6" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B429" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C429" s="6" t="s">
-        <v>585</v>
+      <c r="C429" s="10" t="s">
+        <v>700</v>
       </c>
       <c r="D429" s="6"/>
       <c r="E429" s="6"/>
       <c r="F429" s="6" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="G429" s="6"/>
       <c r="H429" s="6"/>
-      <c r="I429" s="6"/>
+      <c r="I429" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J429" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="6" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B430" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C430" s="10" t="s">
-        <v>700</v>
+      <c r="C430" s="6" t="s">
+        <v>437</v>
       </c>
       <c r="D430" s="6"/>
       <c r="E430" s="6"/>
       <c r="F430" s="6" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G430" s="6"/>
       <c r="H430" s="6"/>
@@ -13157,7 +13163,7 @@
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="6" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B431" s="6" t="s">
         <v>613</v>
@@ -13168,20 +13174,18 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>703</v>
+        <v>412</v>
       </c>
       <c r="G431" s="6"/>
       <c r="H431" s="6"/>
-      <c r="I431" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I431" s="6"/>
       <c r="J431" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A432" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B432" s="6" t="s">
         <v>613</v>
@@ -13192,38 +13196,28 @@
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="G432" s="6"/>
       <c r="H432" s="6"/>
-      <c r="I432" s="6"/>
+      <c r="I432" s="10" t="s">
+        <v>926</v>
+      </c>
       <c r="J432" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="433" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A433" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="B433" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C433" s="6" t="s">
-        <v>437</v>
-      </c>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A433" s="6"/>
+      <c r="B433" s="6"/>
+      <c r="C433" s="6"/>
       <c r="D433" s="6"/>
       <c r="E433" s="6"/>
-      <c r="F433" s="6" t="s">
-        <v>460</v>
-      </c>
+      <c r="F433" s="6"/>
       <c r="G433" s="6"/>
       <c r="H433" s="6"/>
-      <c r="I433" s="10" t="s">
-        <v>926</v>
-      </c>
-      <c r="J433" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I433" s="6"/>
+      <c r="J433" s="6"/>
     </row>
     <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="6"/>
@@ -13274,20 +13268,30 @@
       <c r="J437" s="6"/>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A438" s="6"/>
-      <c r="B438" s="6"/>
-      <c r="C438" s="6"/>
+      <c r="A438" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C438" s="6" t="s">
+        <v>437</v>
+      </c>
       <c r="D438" s="6"/>
       <c r="E438" s="6"/>
-      <c r="F438" s="6"/>
+      <c r="F438" s="6" t="s">
+        <v>707</v>
+      </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6"/>
       <c r="I438" s="6"/>
-      <c r="J438" s="6"/>
+      <c r="J438" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="6" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B439" s="6" t="s">
         <v>613</v>
@@ -13298,7 +13302,7 @@
       <c r="D439" s="6"/>
       <c r="E439" s="6"/>
       <c r="F439" s="6" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G439" s="6"/>
       <c r="H439" s="6"/>
@@ -13309,7 +13313,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="6" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B440" s="6" t="s">
         <v>613</v>
@@ -13320,7 +13324,7 @@
       <c r="D440" s="6"/>
       <c r="E440" s="6"/>
       <c r="F440" s="6" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G440" s="6"/>
       <c r="H440" s="6"/>
@@ -13331,7 +13335,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="6" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B441" s="6" t="s">
         <v>613</v>
@@ -13342,7 +13346,7 @@
       <c r="D441" s="6"/>
       <c r="E441" s="6"/>
       <c r="F441" s="6" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6"/>
@@ -13353,7 +13357,7 @@
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="6" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B442" s="6" t="s">
         <v>613</v>
@@ -13364,7 +13368,7 @@
       <c r="D442" s="6"/>
       <c r="E442" s="6"/>
       <c r="F442" s="6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6"/>
@@ -13375,18 +13379,18 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="6" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B443" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6"/>
       <c r="F443" s="6" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G443" s="6"/>
       <c r="H443" s="6"/>
@@ -13397,7 +13401,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="6" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B444" s="6" t="s">
         <v>613</v>
@@ -13408,7 +13412,7 @@
       <c r="D444" s="6"/>
       <c r="E444" s="6"/>
       <c r="F444" s="6" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6"/>
@@ -13417,9 +13421,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A445" s="6" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B445" s="6" t="s">
         <v>613</v>
@@ -13430,7 +13434,7 @@
       <c r="D445" s="6"/>
       <c r="E445" s="6"/>
       <c r="F445" s="6" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G445" s="6"/>
       <c r="H445" s="6"/>
@@ -13439,9 +13443,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B446" s="6" t="s">
         <v>613</v>
@@ -13452,7 +13456,7 @@
       <c r="D446" s="6"/>
       <c r="E446" s="6"/>
       <c r="F446" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G446" s="6"/>
       <c r="H446" s="6"/>
@@ -13461,9 +13465,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A447" s="6" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B447" s="6" t="s">
         <v>613</v>
@@ -13474,7 +13478,7 @@
       <c r="D447" s="6"/>
       <c r="E447" s="6"/>
       <c r="F447" s="6" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
@@ -13483,9 +13487,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="448" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B448" s="6" t="s">
         <v>613</v>
@@ -13496,7 +13500,7 @@
       <c r="D448" s="6"/>
       <c r="E448" s="6"/>
       <c r="F448" s="6" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6"/>
@@ -13507,7 +13511,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="6" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B449" s="6" t="s">
         <v>613</v>
@@ -13518,7 +13522,7 @@
       <c r="D449" s="6"/>
       <c r="E449" s="6"/>
       <c r="F449" s="6" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
@@ -13527,9 +13531,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A450" s="6" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B450" s="6" t="s">
         <v>613</v>
@@ -13540,7 +13544,7 @@
       <c r="D450" s="6"/>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
@@ -13549,9 +13553,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="451" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="6" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B451" s="6" t="s">
         <v>613</v>
@@ -13562,7 +13566,7 @@
       <c r="D451" s="6"/>
       <c r="E451" s="6"/>
       <c r="F451" s="6" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G451" s="6"/>
       <c r="H451" s="6"/>
@@ -13573,7 +13577,7 @@
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="6" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B452" s="6" t="s">
         <v>613</v>
@@ -13584,7 +13588,7 @@
       <c r="D452" s="6"/>
       <c r="E452" s="6"/>
       <c r="F452" s="6" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G452" s="6"/>
       <c r="H452" s="6"/>
@@ -13593,9 +13597,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A453" s="6" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B453" s="6" t="s">
         <v>613</v>
@@ -13605,39 +13609,29 @@
       </c>
       <c r="D453" s="6"/>
       <c r="E453" s="6"/>
-      <c r="F453" s="6" t="s">
-        <v>735</v>
+      <c r="F453" s="10" t="s">
+        <v>737</v>
       </c>
       <c r="G453" s="6"/>
       <c r="H453" s="6"/>
-      <c r="I453" s="6"/>
+      <c r="I453" s="10" t="s">
+        <v>738</v>
+      </c>
       <c r="J453" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="454" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A454" s="6" t="s">
-        <v>736</v>
-      </c>
-      <c r="B454" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C454" s="6" t="s">
-        <v>462</v>
-      </c>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A454" s="6"/>
+      <c r="B454" s="6"/>
+      <c r="C454" s="6"/>
       <c r="D454" s="6"/>
       <c r="E454" s="6"/>
-      <c r="F454" s="10" t="s">
-        <v>737</v>
-      </c>
+      <c r="F454" s="6"/>
       <c r="G454" s="6"/>
       <c r="H454" s="6"/>
-      <c r="I454" s="10" t="s">
-        <v>738</v>
-      </c>
-      <c r="J454" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I454" s="6"/>
+      <c r="J454" s="6"/>
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="6"/>
@@ -13652,20 +13646,30 @@
       <c r="J455" s="6"/>
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A456" s="6"/>
-      <c r="B456" s="6"/>
-      <c r="C456" s="6"/>
+      <c r="A456" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>462</v>
+      </c>
       <c r="D456" s="6"/>
       <c r="E456" s="6"/>
-      <c r="F456" s="6"/>
+      <c r="F456" s="6" t="s">
+        <v>740</v>
+      </c>
       <c r="G456" s="6"/>
       <c r="H456" s="6"/>
       <c r="I456" s="6"/>
-      <c r="J456" s="6"/>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J456" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A457" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B457" s="6" t="s">
         <v>613</v>
@@ -13676,7 +13680,7 @@
       <c r="D457" s="6"/>
       <c r="E457" s="6"/>
       <c r="F457" s="6" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G457" s="6"/>
       <c r="H457" s="6"/>
@@ -13687,7 +13691,7 @@
     </row>
     <row r="458" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B458" s="6" t="s">
         <v>613</v>
@@ -13698,7 +13702,7 @@
       <c r="D458" s="6"/>
       <c r="E458" s="6"/>
       <c r="F458" s="6" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G458" s="6"/>
       <c r="H458" s="6"/>
@@ -13707,20 +13711,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="459" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="6" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B459" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C459" s="6" t="s">
-        <v>462</v>
+      <c r="C459" s="10" t="s">
+        <v>746</v>
       </c>
       <c r="D459" s="6"/>
       <c r="E459" s="6"/>
       <c r="F459" s="6" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="G459" s="6"/>
       <c r="H459" s="6"/>
@@ -13731,7 +13735,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B460" s="6" t="s">
         <v>613</v>
@@ -13742,42 +13746,42 @@
       <c r="D460" s="6"/>
       <c r="E460" s="6"/>
       <c r="F460" s="6" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
-      <c r="I460" s="6"/>
+      <c r="I460" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="J460" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="6" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B461" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C461" s="10" t="s">
-        <v>746</v>
+        <v>506</v>
       </c>
       <c r="D461" s="6"/>
       <c r="E461" s="6"/>
       <c r="F461" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
-      <c r="I461" s="6" t="s">
-        <v>923</v>
-      </c>
+      <c r="I461" s="6"/>
       <c r="J461" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="6" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B462" s="6" t="s">
         <v>613</v>
@@ -13788,7 +13792,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>751</v>
+        <v>509</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -13799,7 +13803,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B463" s="6" t="s">
         <v>613</v>
@@ -13810,7 +13814,7 @@
       <c r="D463" s="6"/>
       <c r="E463" s="6"/>
       <c r="F463" s="6" t="s">
-        <v>509</v>
+        <v>104</v>
       </c>
       <c r="G463" s="6"/>
       <c r="H463" s="6"/>
@@ -13821,7 +13825,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="6" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B464" s="6" t="s">
         <v>613</v>
@@ -13832,7 +13836,7 @@
       <c r="D464" s="6"/>
       <c r="E464" s="6"/>
       <c r="F464" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G464" s="6"/>
       <c r="H464" s="6"/>
@@ -13843,7 +13847,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="6" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B465" s="6" t="s">
         <v>613</v>
@@ -13853,8 +13857,8 @@
       </c>
       <c r="D465" s="6"/>
       <c r="E465" s="6"/>
-      <c r="F465" s="6" t="s">
-        <v>108</v>
+      <c r="F465" s="10" t="s">
+        <v>756</v>
       </c>
       <c r="G465" s="6"/>
       <c r="H465" s="6"/>
@@ -13865,7 +13869,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="6" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B466" s="6" t="s">
         <v>613</v>
@@ -13875,8 +13879,8 @@
       </c>
       <c r="D466" s="6"/>
       <c r="E466" s="6"/>
-      <c r="F466" s="10" t="s">
-        <v>756</v>
+      <c r="F466" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G466" s="6"/>
       <c r="H466" s="6"/>
@@ -13887,7 +13891,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="6" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B467" s="6" t="s">
         <v>613</v>
@@ -13898,7 +13902,7 @@
       <c r="D467" s="6"/>
       <c r="E467" s="6"/>
       <c r="F467" s="6" t="s">
-        <v>110</v>
+        <v>759</v>
       </c>
       <c r="G467" s="6"/>
       <c r="H467" s="6"/>
@@ -13909,7 +13913,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="6" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B468" s="6" t="s">
         <v>613</v>
@@ -13920,7 +13924,7 @@
       <c r="D468" s="6"/>
       <c r="E468" s="6"/>
       <c r="F468" s="6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G468" s="6"/>
       <c r="H468" s="6"/>
@@ -13931,7 +13935,7 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="6" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B469" s="6" t="s">
         <v>613</v>
@@ -13942,7 +13946,7 @@
       <c r="D469" s="6"/>
       <c r="E469" s="6"/>
       <c r="F469" s="6" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G469" s="6"/>
       <c r="H469" s="6"/>
@@ -13951,9 +13955,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A470" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B470" s="6" t="s">
         <v>613</v>
@@ -13964,7 +13968,7 @@
       <c r="D470" s="6"/>
       <c r="E470" s="6"/>
       <c r="F470" s="6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G470" s="6"/>
       <c r="H470" s="6"/>
@@ -13973,9 +13977,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="471" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B471" s="6" t="s">
         <v>613</v>
@@ -13986,7 +13990,7 @@
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G471" s="6"/>
       <c r="H471" s="6"/>
@@ -13997,18 +14001,18 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="6" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B472" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C472" s="10" t="s">
+      <c r="C472" s="6" t="s">
         <v>506</v>
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6"/>
       <c r="F472" s="6" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G472" s="6"/>
       <c r="H472" s="6"/>
@@ -14019,7 +14023,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="6" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B473" s="6" t="s">
         <v>613</v>
@@ -14030,7 +14034,7 @@
       <c r="D473" s="6"/>
       <c r="E473" s="6"/>
       <c r="F473" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G473" s="6"/>
       <c r="H473" s="6"/>
@@ -14041,7 +14045,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="6" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B474" s="6" t="s">
         <v>613</v>
@@ -14052,7 +14056,7 @@
       <c r="D474" s="6"/>
       <c r="E474" s="6"/>
       <c r="F474" s="6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
@@ -14063,7 +14067,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="6" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B475" s="6" t="s">
         <v>613</v>
@@ -14074,7 +14078,7 @@
       <c r="D475" s="6"/>
       <c r="E475" s="6"/>
       <c r="F475" s="6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G475" s="6"/>
       <c r="H475" s="6"/>
@@ -14085,7 +14089,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B476" s="6" t="s">
         <v>613</v>
@@ -14096,7 +14100,7 @@
       <c r="D476" s="6"/>
       <c r="E476" s="6"/>
       <c r="F476" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G476" s="6"/>
       <c r="H476" s="6"/>
@@ -14107,7 +14111,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="6" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B477" s="6" t="s">
         <v>613</v>
@@ -14118,7 +14122,7 @@
       <c r="D477" s="6"/>
       <c r="E477" s="6"/>
       <c r="F477" s="6" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G477" s="6"/>
       <c r="H477" s="6"/>
@@ -14129,7 +14133,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="6" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B478" s="6" t="s">
         <v>613</v>
@@ -14140,7 +14144,7 @@
       <c r="D478" s="6"/>
       <c r="E478" s="6"/>
       <c r="F478" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
@@ -14151,7 +14155,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="6" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B479" s="6" t="s">
         <v>613</v>
@@ -14162,7 +14166,7 @@
       <c r="D479" s="6"/>
       <c r="E479" s="6"/>
       <c r="F479" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G479" s="6"/>
       <c r="H479" s="6"/>
@@ -14173,7 +14177,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="6" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B480" s="6" t="s">
         <v>613</v>
@@ -14184,7 +14188,7 @@
       <c r="D480" s="6"/>
       <c r="E480" s="6"/>
       <c r="F480" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G480" s="6"/>
       <c r="H480" s="6"/>
@@ -14195,7 +14199,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="6" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B481" s="6" t="s">
         <v>613</v>
@@ -14206,7 +14210,7 @@
       <c r="D481" s="6"/>
       <c r="E481" s="6"/>
       <c r="F481" s="6" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G481" s="6"/>
       <c r="H481" s="6"/>
@@ -14217,7 +14221,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="6" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B482" s="6" t="s">
         <v>613</v>
@@ -14228,7 +14232,7 @@
       <c r="D482" s="6"/>
       <c r="E482" s="6"/>
       <c r="F482" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="G482" s="6"/>
       <c r="H482" s="6"/>
@@ -14239,7 +14243,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="6" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B483" s="6" t="s">
         <v>613</v>
@@ -14250,7 +14254,7 @@
       <c r="D483" s="6"/>
       <c r="E483" s="6"/>
       <c r="F483" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
@@ -14261,7 +14265,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="6" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B484" s="6" t="s">
         <v>613</v>
@@ -14272,7 +14276,7 @@
       <c r="D484" s="6"/>
       <c r="E484" s="6"/>
       <c r="F484" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
@@ -14283,7 +14287,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="6" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B485" s="6" t="s">
         <v>613</v>
@@ -14294,7 +14298,7 @@
       <c r="D485" s="6"/>
       <c r="E485" s="6"/>
       <c r="F485" s="6" t="s">
-        <v>793</v>
+        <v>541</v>
       </c>
       <c r="G485" s="6"/>
       <c r="H485" s="6"/>
@@ -14305,7 +14309,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="6" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B486" s="6" t="s">
         <v>613</v>
@@ -14316,7 +14320,7 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>541</v>
+        <v>796</v>
       </c>
       <c r="G486" s="6"/>
       <c r="H486" s="6"/>
@@ -14327,7 +14331,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="6" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B487" s="6" t="s">
         <v>613</v>
@@ -14338,7 +14342,7 @@
       <c r="D487" s="6"/>
       <c r="E487" s="6"/>
       <c r="F487" s="6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G487" s="6"/>
       <c r="H487" s="6"/>
@@ -14347,51 +14351,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B488" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C488" s="6" t="s">
+      <c r="C488" s="10" t="s">
         <v>506</v>
       </c>
       <c r="D488" s="6"/>
       <c r="E488" s="6"/>
-      <c r="F488" s="6" t="s">
-        <v>798</v>
+      <c r="F488" s="10" t="s">
+        <v>800</v>
       </c>
       <c r="G488" s="6"/>
       <c r="H488" s="6"/>
-      <c r="I488" s="6"/>
+      <c r="I488" s="10" t="s">
+        <v>801</v>
+      </c>
       <c r="J488" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="489" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A489" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="B489" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C489" s="10" t="s">
-        <v>506</v>
-      </c>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A489" s="6"/>
+      <c r="B489" s="6"/>
+      <c r="C489" s="6"/>
       <c r="D489" s="6"/>
       <c r="E489" s="6"/>
-      <c r="F489" s="10" t="s">
-        <v>800</v>
-      </c>
+      <c r="F489" s="6"/>
       <c r="G489" s="6"/>
       <c r="H489" s="6"/>
-      <c r="I489" s="10" t="s">
-        <v>801</v>
-      </c>
-      <c r="J489" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I489" s="6"/>
+      <c r="J489" s="6"/>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="6"/>
@@ -14634,20 +14628,30 @@
       <c r="J509" s="6"/>
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A510" s="6"/>
-      <c r="B510" s="6"/>
-      <c r="C510" s="6"/>
+      <c r="A510" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="B510" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C510" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D510" s="6"/>
       <c r="E510" s="6"/>
-      <c r="F510" s="6"/>
+      <c r="F510" s="6" t="s">
+        <v>803</v>
+      </c>
       <c r="G510" s="6"/>
       <c r="H510" s="6"/>
       <c r="I510" s="6"/>
-      <c r="J510" s="6"/>
-    </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J510" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A511" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B511" s="6" t="s">
         <v>613</v>
@@ -14658,7 +14662,7 @@
       <c r="D511" s="6"/>
       <c r="E511" s="6"/>
       <c r="F511" s="6" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G511" s="6"/>
       <c r="H511" s="6"/>
@@ -14667,9 +14671,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="512" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="6" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B512" s="6" t="s">
         <v>613</v>
@@ -14680,7 +14684,7 @@
       <c r="D512" s="6"/>
       <c r="E512" s="6"/>
       <c r="F512" s="6" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G512" s="6"/>
       <c r="H512" s="6"/>
@@ -14691,7 +14695,7 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="6" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B513" s="6" t="s">
         <v>613</v>
@@ -14702,7 +14706,7 @@
       <c r="D513" s="6"/>
       <c r="E513" s="6"/>
       <c r="F513" s="6" t="s">
-        <v>807</v>
+        <v>425</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
@@ -14711,51 +14715,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A514" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B514" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C514" s="6" t="s">
+      <c r="C514" s="10" t="s">
         <v>524</v>
       </c>
       <c r="D514" s="6"/>
       <c r="E514" s="6"/>
-      <c r="F514" s="6" t="s">
-        <v>425</v>
+      <c r="F514" s="10" t="s">
+        <v>810</v>
       </c>
       <c r="G514" s="6"/>
       <c r="H514" s="6"/>
-      <c r="I514" s="6"/>
+      <c r="I514" s="10" t="s">
+        <v>801</v>
+      </c>
       <c r="J514" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="515" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A515" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="B515" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C515" s="10" t="s">
-        <v>524</v>
-      </c>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A515" s="6"/>
+      <c r="B515" s="6"/>
+      <c r="C515" s="6"/>
       <c r="D515" s="6"/>
       <c r="E515" s="6"/>
-      <c r="F515" s="10" t="s">
-        <v>810</v>
-      </c>
+      <c r="F515" s="6"/>
       <c r="G515" s="6"/>
       <c r="H515" s="6"/>
-      <c r="I515" s="10" t="s">
-        <v>801</v>
-      </c>
-      <c r="J515" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I515" s="6"/>
+      <c r="J515" s="6"/>
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="6"/>
@@ -14997,41 +14991,41 @@
       <c r="I535" s="6"/>
       <c r="J535" s="6"/>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A536" s="6"/>
-      <c r="B536" s="6"/>
-      <c r="C536" s="6"/>
+    <row r="536" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A536" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B536" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C536" s="10" t="s">
+        <v>524</v>
+      </c>
       <c r="D536" s="6"/>
       <c r="E536" s="6"/>
-      <c r="F536" s="6"/>
+      <c r="F536" s="10" t="s">
+        <v>812</v>
+      </c>
       <c r="G536" s="6"/>
       <c r="H536" s="6"/>
-      <c r="I536" s="6"/>
-      <c r="J536" s="6"/>
-    </row>
-    <row r="537" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A537" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="B537" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C537" s="10" t="s">
-        <v>524</v>
-      </c>
+      <c r="I536" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="J536" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A537" s="6"/>
+      <c r="B537" s="6"/>
+      <c r="C537" s="6"/>
       <c r="D537" s="6"/>
       <c r="E537" s="6"/>
-      <c r="F537" s="10" t="s">
-        <v>812</v>
-      </c>
+      <c r="F537" s="6"/>
       <c r="G537" s="6"/>
       <c r="H537" s="6"/>
-      <c r="I537" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="J537" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I537" s="6"/>
+      <c r="J537" s="6"/>
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" s="6"/>
@@ -15118,20 +15112,30 @@
       <c r="J544" s="6"/>
     </row>
     <row r="545" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A545" s="6"/>
-      <c r="B545" s="6"/>
-      <c r="C545" s="6"/>
+      <c r="A545" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="B545" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C545" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D545" s="6"/>
       <c r="E545" s="6"/>
-      <c r="F545" s="6"/>
+      <c r="F545" s="6" t="s">
+        <v>814</v>
+      </c>
       <c r="G545" s="6"/>
       <c r="H545" s="6"/>
       <c r="I545" s="6"/>
-      <c r="J545" s="6"/>
-    </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J545" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A546" s="6" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B546" s="6" t="s">
         <v>613</v>
@@ -15142,7 +15146,7 @@
       <c r="D546" s="6"/>
       <c r="E546" s="6"/>
       <c r="F546" s="6" t="s">
-        <v>814</v>
+        <v>206</v>
       </c>
       <c r="G546" s="6"/>
       <c r="H546" s="6"/>
@@ -15153,7 +15157,7 @@
     </row>
     <row r="547" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B547" s="6" t="s">
         <v>613</v>
@@ -15164,7 +15168,7 @@
       <c r="D547" s="6"/>
       <c r="E547" s="6"/>
       <c r="F547" s="6" t="s">
-        <v>206</v>
+        <v>817</v>
       </c>
       <c r="G547" s="6"/>
       <c r="H547" s="6"/>
@@ -15173,9 +15177,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="548" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="6" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B548" s="6" t="s">
         <v>613</v>
@@ -15186,7 +15190,7 @@
       <c r="D548" s="6"/>
       <c r="E548" s="6"/>
       <c r="F548" s="6" t="s">
-        <v>817</v>
+        <v>210</v>
       </c>
       <c r="G548" s="6"/>
       <c r="H548" s="6"/>
@@ -15197,7 +15201,7 @@
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B549" s="6" t="s">
         <v>613</v>
@@ -15208,7 +15212,7 @@
       <c r="D549" s="6"/>
       <c r="E549" s="6"/>
       <c r="F549" s="6" t="s">
-        <v>210</v>
+        <v>820</v>
       </c>
       <c r="G549" s="6"/>
       <c r="H549" s="6"/>
@@ -15219,7 +15223,7 @@
     </row>
     <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="6" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B550" s="6" t="s">
         <v>613</v>
@@ -15230,7 +15234,7 @@
       <c r="D550" s="6"/>
       <c r="E550" s="6"/>
       <c r="F550" s="6" t="s">
-        <v>820</v>
+        <v>717</v>
       </c>
       <c r="G550" s="6"/>
       <c r="H550" s="6"/>
@@ -15239,9 +15243,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A551" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B551" s="6" t="s">
         <v>613</v>
@@ -15251,110 +15255,88 @@
       </c>
       <c r="D551" s="6"/>
       <c r="E551" s="6"/>
-      <c r="F551" s="6" t="s">
-        <v>717</v>
+      <c r="F551" s="10" t="s">
+        <v>823</v>
       </c>
       <c r="G551" s="6"/>
       <c r="H551" s="6"/>
-      <c r="I551" s="6"/>
+      <c r="I551" s="10" t="s">
+        <v>824</v>
+      </c>
       <c r="J551" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="552" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A552" s="6" t="s">
-        <v>822</v>
-      </c>
-      <c r="B552" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C552" s="6" t="s">
-        <v>524</v>
-      </c>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A552" s="6"/>
+      <c r="B552" s="6"/>
+      <c r="C552" s="6"/>
       <c r="D552" s="6"/>
       <c r="E552" s="6"/>
-      <c r="F552" s="10" t="s">
-        <v>823</v>
-      </c>
+      <c r="F552" s="6"/>
       <c r="G552" s="6"/>
       <c r="H552" s="6"/>
-      <c r="I552" s="10" t="s">
-        <v>824</v>
-      </c>
-      <c r="J552" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="I552" s="6"/>
+      <c r="J552" s="6"/>
     </row>
     <row r="553" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A553" s="6"/>
-      <c r="B553" s="6"/>
-      <c r="C553" s="6"/>
+      <c r="A553" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="B553" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="C553" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="D553" s="6"/>
       <c r="E553" s="6"/>
-      <c r="F553" s="6"/>
+      <c r="F553" s="6" t="s">
+        <v>826</v>
+      </c>
       <c r="G553" s="6"/>
       <c r="H553" s="6"/>
       <c r="I553" s="6"/>
-      <c r="J553" s="6"/>
-    </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J553" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A554" s="6" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B554" s="6" t="s">
         <v>613</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>524</v>
+        <v>828</v>
       </c>
       <c r="D554" s="6"/>
       <c r="E554" s="6"/>
       <c r="F554" s="6" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="G554" s="6"/>
       <c r="H554" s="6"/>
-      <c r="I554" s="6"/>
+      <c r="I554" s="10" t="s">
+        <v>830</v>
+      </c>
       <c r="J554" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="555" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A555" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="B555" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="C555" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="D555" s="6"/>
-      <c r="E555" s="6"/>
-      <c r="F555" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="G555" s="6"/>
-      <c r="H555" s="6"/>
-      <c r="I555" s="10" t="s">
-        <v>830</v>
-      </c>
-      <c r="J555" s="6" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="C489:C510 C515:C545 C421:C426 C430 C434:C438 C556:C948 C381:C416 C460:C472 C2:C379" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Locker 7,Other,Pump Panel,Rear,Roof"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H381:H948 H2:H379" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H380:H947 H2:H378" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Access/Entry,BA,Battery/Charging,Communications,Electrical,Firefighting,First Aid/Medical,Hand Tools,Hydrant/Water Supply,Lighting,PPE,Rescue,Ropes/Heights,Stabilisation,Traffic/Scene Safety,Welfare,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J381:J948 J2:J379" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J380:J947 J2:J378" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"In service,Missing,Damaged,Needs replacement,Out of service,For review"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C489:C510 C515:C545 C421:C426 C430 C434:C438 C556:C948 C381:C416 C460:C472 C2:C379" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C488:C509 C514:C544 C420:C425 C429 C433:C437 C555:C947 C380:C415 C459:C471 C2:C378" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Cabin,Locker 1,Locker 2,Locker 3,Locker 4,Locker 5,Locker 6,Rear,Roof,Other"</formula1>
     </dataValidation>
   </dataValidations>
